--- a/Images_BGA/Results/Reports/PCBA1_08_inspection_report.xlsx
+++ b/Images_BGA/Results/Reports/PCBA1_08_inspection_report.xlsx
@@ -500,16 +500,16 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2056</v>
+        <v>2159</v>
       </c>
       <c r="D2">
-        <v>609</v>
+        <v>627</v>
       </c>
       <c r="E2">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F2">
-        <v>2827.43</v>
+        <v>1809.56</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -544,31 +544,31 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>717</v>
+        <v>1083</v>
       </c>
       <c r="D3">
-        <v>610</v>
+        <v>637</v>
       </c>
       <c r="E3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F3">
-        <v>1809.56</v>
+        <v>2827.43</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>11.5498</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>11.5498</v>
+        <v>0</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -588,31 +588,31 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>1687</v>
+        <v>1821</v>
       </c>
       <c r="D4">
-        <v>613</v>
+        <v>638</v>
       </c>
       <c r="E4">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F4">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>1.0598</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>1.0598</v>
+        <v>0</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -632,31 +632,31 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>983</v>
+        <v>905</v>
       </c>
       <c r="D5">
-        <v>615</v>
+        <v>644</v>
       </c>
       <c r="E5">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F5">
-        <v>2123.72</v>
+        <v>2642.08</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="I5">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="J5">
-        <v>10.5946</v>
+        <v>10.0678</v>
       </c>
       <c r="K5">
-        <v>10.5946</v>
+        <v>10.0678</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -676,31 +676,31 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>1421</v>
+        <v>750</v>
       </c>
       <c r="D6">
-        <v>615</v>
+        <v>650</v>
       </c>
       <c r="E6">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F6">
-        <v>2290.22</v>
+        <v>2123.72</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="I6">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="J6">
-        <v>2.4452</v>
+        <v>3.8141</v>
       </c>
       <c r="K6">
-        <v>2.4452</v>
+        <v>1.6481</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -720,31 +720,31 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>2160</v>
+        <v>1017</v>
       </c>
       <c r="D7">
-        <v>615</v>
+        <v>650</v>
       </c>
       <c r="E7">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F7">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1.7893</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1.7893</v>
       </c>
       <c r="L7" t="s">
         <v>15</v>
@@ -764,31 +764,31 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>1509</v>
+        <v>1195</v>
       </c>
       <c r="D8">
-        <v>616</v>
+        <v>650</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F8">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="I8">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="J8">
-        <v>2.9539</v>
+        <v>2.1189</v>
       </c>
       <c r="K8">
-        <v>2.9539</v>
+        <v>2.1189</v>
       </c>
       <c r="L8" t="s">
         <v>15</v>
@@ -808,31 +808,31 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>1770</v>
+        <v>1284</v>
       </c>
       <c r="D9">
-        <v>616</v>
+        <v>650</v>
       </c>
       <c r="E9">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="I9">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="J9">
-        <v>2.4868</v>
+        <v>1.1714</v>
       </c>
       <c r="K9">
-        <v>2.4868</v>
+        <v>1.1714</v>
       </c>
       <c r="L9" t="s">
         <v>15</v>
@@ -852,31 +852,31 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>1962</v>
+        <v>1373</v>
       </c>
       <c r="D10">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F10">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>11.2554</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>8.1487</v>
+        <v>0</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -896,16 +896,16 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>912</v>
+        <v>1462</v>
       </c>
       <c r="D11">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="E11">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F11">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -940,31 +940,31 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>819</v>
+        <v>1551</v>
       </c>
       <c r="D12">
-        <v>628</v>
+        <v>650</v>
       </c>
       <c r="E12">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F12">
-        <v>2463.01</v>
+        <v>2123.72</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>2.4485</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1.3184</v>
       </c>
       <c r="L12" t="s">
         <v>15</v>
@@ -984,31 +984,31 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>1561</v>
+        <v>1640</v>
       </c>
       <c r="D13">
-        <v>632</v>
+        <v>650</v>
       </c>
       <c r="E13">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F13">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I13">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J13">
-        <v>2.6483</v>
+        <v>2.4015</v>
       </c>
       <c r="K13">
-        <v>1.426</v>
+        <v>1.5539</v>
       </c>
       <c r="L13" t="s">
         <v>15</v>
@@ -1028,31 +1028,31 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>1083</v>
+        <v>1730</v>
       </c>
       <c r="D14">
-        <v>637</v>
+        <v>650</v>
       </c>
       <c r="E14">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F14">
-        <v>3019.07</v>
+        <v>2123.72</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1.8364</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1.8364</v>
       </c>
       <c r="L14" t="s">
         <v>15</v>
@@ -1072,16 +1072,16 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>1821</v>
+        <v>1907</v>
       </c>
       <c r="D15">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="E15">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F15">
-        <v>3019.07</v>
+        <v>2123.72</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1116,31 +1116,31 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>1195</v>
+        <v>2081</v>
       </c>
       <c r="D16">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="E16">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F16">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="I16">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="J16">
-        <v>3.2086</v>
+        <v>1.083</v>
       </c>
       <c r="K16">
-        <v>2.3428</v>
+        <v>1.083</v>
       </c>
       <c r="L16" t="s">
         <v>15</v>
@@ -1160,31 +1160,31 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>1284</v>
+        <v>818</v>
       </c>
       <c r="D17">
-        <v>641</v>
+        <v>657</v>
       </c>
       <c r="E17">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F17">
-        <v>1963.5</v>
+        <v>2827.43</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17">
-        <v>23</v>
+        <v>226</v>
       </c>
       <c r="I17">
-        <v>23</v>
+        <v>226</v>
       </c>
       <c r="J17">
-        <v>1.1714</v>
+        <v>7.9931</v>
       </c>
       <c r="K17">
-        <v>1.1714</v>
+        <v>7.9931</v>
       </c>
       <c r="L17" t="s">
         <v>15</v>
@@ -1204,31 +1204,31 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>2075</v>
+        <v>813</v>
       </c>
       <c r="D18">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E18">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F18">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>0.7427</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>0.7427</v>
       </c>
       <c r="L18" t="s">
         <v>15</v>
@@ -1248,16 +1248,16 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>2159</v>
+        <v>2075</v>
       </c>
       <c r="D19">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="E19">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F19">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>836</v>
+        <v>1015</v>
       </c>
       <c r="D21">
         <v>710</v>
@@ -1348,19 +1348,19 @@
         <v>2123.72</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="I21">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="J21">
-        <v>4.2379</v>
+        <v>1.1301</v>
       </c>
       <c r="K21">
-        <v>2.1189</v>
+        <v>1.1301</v>
       </c>
       <c r="L21" t="s">
         <v>15</v>
@@ -1380,7 +1380,7 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>1015</v>
+        <v>1195</v>
       </c>
       <c r="D22">
         <v>710</v>
@@ -1392,19 +1392,19 @@
         <v>2123.72</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>1.1301</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>1.1301</v>
+        <v>0</v>
       </c>
       <c r="L22" t="s">
         <v>15</v>
@@ -1424,7 +1424,7 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>1195</v>
+        <v>1374</v>
       </c>
       <c r="D23">
         <v>710</v>
@@ -1468,7 +1468,7 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>1285</v>
+        <v>1464</v>
       </c>
       <c r="D24">
         <v>710</v>
@@ -1480,19 +1480,19 @@
         <v>2123.72</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>0.8005</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>0.8005</v>
       </c>
       <c r="L24" t="s">
         <v>15</v>
@@ -1512,7 +1512,7 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>1374</v>
+        <v>1553</v>
       </c>
       <c r="D25">
         <v>710</v>
@@ -1556,7 +1556,7 @@
         <v>25</v>
       </c>
       <c r="C26">
-        <v>1464</v>
+        <v>1733</v>
       </c>
       <c r="D26">
         <v>710</v>
@@ -1571,16 +1571,16 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I26">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J26">
-        <v>0.8005</v>
+        <v>1.0359</v>
       </c>
       <c r="K26">
-        <v>0.8005</v>
+        <v>1.0359</v>
       </c>
       <c r="L26" t="s">
         <v>15</v>
@@ -1600,7 +1600,7 @@
         <v>26</v>
       </c>
       <c r="C27">
-        <v>1553</v>
+        <v>1822</v>
       </c>
       <c r="D27">
         <v>710</v>
@@ -1612,19 +1612,19 @@
         <v>2123.72</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>0.8005</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>0.8005</v>
       </c>
       <c r="L27" t="s">
         <v>15</v>
@@ -1644,7 +1644,7 @@
         <v>27</v>
       </c>
       <c r="C28">
-        <v>1733</v>
+        <v>1912</v>
       </c>
       <c r="D28">
         <v>710</v>
@@ -1659,16 +1659,16 @@
         <v>1</v>
       </c>
       <c r="H28">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I28">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J28">
-        <v>1.0359</v>
+        <v>0.8476</v>
       </c>
       <c r="K28">
-        <v>1.0359</v>
+        <v>0.8476</v>
       </c>
       <c r="L28" t="s">
         <v>15</v>
@@ -1688,31 +1688,31 @@
         <v>28</v>
       </c>
       <c r="C29">
-        <v>1822</v>
+        <v>2158</v>
       </c>
       <c r="D29">
         <v>710</v>
       </c>
       <c r="E29">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F29">
-        <v>2123.72</v>
+        <v>2463.01</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>0.8005</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>0.8005</v>
+        <v>0</v>
       </c>
       <c r="L29" t="s">
         <v>15</v>
@@ -1732,10 +1732,10 @@
         <v>29</v>
       </c>
       <c r="C30">
-        <v>1912</v>
+        <v>926</v>
       </c>
       <c r="D30">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E30">
         <v>52</v>
@@ -1744,19 +1744,19 @@
         <v>2123.72</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I30">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J30">
-        <v>0.8476</v>
+        <v>2.2602</v>
       </c>
       <c r="K30">
-        <v>0.8476</v>
+        <v>1.2243</v>
       </c>
       <c r="L30" t="s">
         <v>15</v>
@@ -1776,7 +1776,7 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>1645</v>
+        <v>1284</v>
       </c>
       <c r="D31">
         <v>711</v>
@@ -1820,31 +1820,31 @@
         <v>31</v>
       </c>
       <c r="C32">
-        <v>1099</v>
+        <v>1645</v>
       </c>
       <c r="D32">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E32">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F32">
-        <v>2463.01</v>
+        <v>2123.72</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>2.233</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>0.8526</v>
+        <v>0</v>
       </c>
       <c r="L32" t="s">
         <v>15</v>
@@ -1864,31 +1864,31 @@
         <v>32</v>
       </c>
       <c r="C33">
-        <v>907</v>
+        <v>1099</v>
       </c>
       <c r="D33">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="E33">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F33">
-        <v>3019.07</v>
+        <v>2463.01</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33">
-        <v>211</v>
+        <v>55</v>
       </c>
       <c r="I33">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J33">
-        <v>6.9889</v>
+        <v>2.233</v>
       </c>
       <c r="K33">
-        <v>6.3265</v>
+        <v>0.8526</v>
       </c>
       <c r="L33" t="s">
         <v>15</v>
@@ -2568,16 +2568,16 @@
         <v>48</v>
       </c>
       <c r="C49">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="D49">
         <v>777</v>
       </c>
       <c r="E49">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F49">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -3272,7 +3272,7 @@
         <v>64</v>
       </c>
       <c r="C65">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="D65">
         <v>839</v>
@@ -3360,31 +3360,31 @@
         <v>66</v>
       </c>
       <c r="C67">
-        <v>1671</v>
+        <v>1651</v>
       </c>
       <c r="D67">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="E67">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F67">
-        <v>3019.07</v>
+        <v>2290.22</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I67">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>1.1789</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>1.1789</v>
       </c>
       <c r="L67" t="s">
         <v>15</v>
@@ -4548,7 +4548,7 @@
         <v>93</v>
       </c>
       <c r="C94">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="D94">
         <v>959</v>
@@ -4560,19 +4560,19 @@
         <v>2290.22</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I94">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J94">
-        <v>0</v>
+        <v>2.7945</v>
       </c>
       <c r="K94">
-        <v>0</v>
+        <v>1.2226</v>
       </c>
       <c r="L94" t="s">
         <v>15</v>
@@ -4636,10 +4636,10 @@
         <v>95</v>
       </c>
       <c r="C96">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D96">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="E96">
         <v>56</v>
@@ -4724,31 +4724,31 @@
         <v>97</v>
       </c>
       <c r="C98">
-        <v>729</v>
+        <v>2162</v>
       </c>
       <c r="D98">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="E98">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F98">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G98">
         <v>1</v>
       </c>
       <c r="H98">
-        <v>16</v>
+        <v>247</v>
       </c>
       <c r="I98">
-        <v>16</v>
+        <v>247</v>
       </c>
       <c r="J98">
-        <v>0.6986</v>
+        <v>8.735799999999999</v>
       </c>
       <c r="K98">
-        <v>0.6986</v>
+        <v>8.735799999999999</v>
       </c>
       <c r="L98" t="s">
         <v>15</v>
@@ -4768,7 +4768,7 @@
         <v>98</v>
       </c>
       <c r="C99">
-        <v>822</v>
+        <v>729</v>
       </c>
       <c r="D99">
         <v>1023</v>
@@ -4780,19 +4780,19 @@
         <v>2290.22</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I99">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J99">
-        <v>0</v>
+        <v>0.6986</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>0.6986</v>
       </c>
       <c r="L99" t="s">
         <v>15</v>
@@ -4812,7 +4812,7 @@
         <v>99</v>
       </c>
       <c r="C100">
-        <v>915</v>
+        <v>822</v>
       </c>
       <c r="D100">
         <v>1023</v>
@@ -4856,7 +4856,7 @@
         <v>100</v>
       </c>
       <c r="C101">
-        <v>1101</v>
+        <v>915</v>
       </c>
       <c r="D101">
         <v>1023</v>
@@ -4900,7 +4900,7 @@
         <v>101</v>
       </c>
       <c r="C102">
-        <v>1750</v>
+        <v>1101</v>
       </c>
       <c r="D102">
         <v>1023</v>
@@ -4912,19 +4912,19 @@
         <v>2290.22</v>
       </c>
       <c r="G102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I102">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J102">
-        <v>0.7423</v>
+        <v>0</v>
       </c>
       <c r="K102">
-        <v>0.7423</v>
+        <v>0</v>
       </c>
       <c r="L102" t="s">
         <v>15</v>
@@ -4944,7 +4944,7 @@
         <v>102</v>
       </c>
       <c r="C103">
-        <v>1843</v>
+        <v>1750</v>
       </c>
       <c r="D103">
         <v>1023</v>
@@ -4959,16 +4959,16 @@
         <v>1</v>
       </c>
       <c r="H103">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I103">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J103">
-        <v>0.786</v>
+        <v>0.7423</v>
       </c>
       <c r="K103">
-        <v>0.786</v>
+        <v>0.7423</v>
       </c>
       <c r="L103" t="s">
         <v>15</v>
@@ -4988,7 +4988,7 @@
         <v>103</v>
       </c>
       <c r="C104">
-        <v>1936</v>
+        <v>1843</v>
       </c>
       <c r="D104">
         <v>1023</v>
@@ -5000,19 +5000,19 @@
         <v>2290.22</v>
       </c>
       <c r="G104">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H104">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="I104">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="J104">
-        <v>3.5368</v>
+        <v>0.786</v>
       </c>
       <c r="K104">
-        <v>1.7902</v>
+        <v>0.786</v>
       </c>
       <c r="L104" t="s">
         <v>15</v>
@@ -5032,10 +5032,10 @@
         <v>104</v>
       </c>
       <c r="C105">
-        <v>1010</v>
+        <v>1936</v>
       </c>
       <c r="D105">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E105">
         <v>54</v>
@@ -5044,19 +5044,19 @@
         <v>2290.22</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H105">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="I105">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="J105">
-        <v>0.7423</v>
+        <v>3.5368</v>
       </c>
       <c r="K105">
-        <v>0.7423</v>
+        <v>1.7902</v>
       </c>
       <c r="L105" t="s">
         <v>15</v>
@@ -5076,7 +5076,7 @@
         <v>105</v>
       </c>
       <c r="C106">
-        <v>1193</v>
+        <v>1010</v>
       </c>
       <c r="D106">
         <v>1024</v>
@@ -5120,7 +5120,7 @@
         <v>106</v>
       </c>
       <c r="C107">
-        <v>1658</v>
+        <v>1193</v>
       </c>
       <c r="D107">
         <v>1024</v>
@@ -5132,19 +5132,19 @@
         <v>2290.22</v>
       </c>
       <c r="G107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H107">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="I107">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J107">
-        <v>1.7902</v>
+        <v>0.7423</v>
       </c>
       <c r="K107">
-        <v>1.0479</v>
+        <v>0.7423</v>
       </c>
       <c r="L107" t="s">
         <v>15</v>
@@ -5164,31 +5164,31 @@
         <v>107</v>
       </c>
       <c r="C108">
-        <v>2161</v>
+        <v>1658</v>
       </c>
       <c r="D108">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E108">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F108">
-        <v>3019.07</v>
+        <v>2290.22</v>
       </c>
       <c r="G108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H108">
-        <v>245</v>
+        <v>41</v>
       </c>
       <c r="I108">
-        <v>245</v>
+        <v>24</v>
       </c>
       <c r="J108">
-        <v>8.1151</v>
+        <v>1.7902</v>
       </c>
       <c r="K108">
-        <v>8.1151</v>
+        <v>1.0479</v>
       </c>
       <c r="L108" t="s">
         <v>15</v>
@@ -5428,10 +5428,10 @@
         <v>113</v>
       </c>
       <c r="C114">
-        <v>2167</v>
+        <v>725</v>
       </c>
       <c r="D114">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="E114">
         <v>54</v>
@@ -5472,10 +5472,10 @@
         <v>114</v>
       </c>
       <c r="C115">
-        <v>725</v>
+        <v>819</v>
       </c>
       <c r="D115">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="E115">
         <v>54</v>
@@ -5516,7 +5516,7 @@
         <v>115</v>
       </c>
       <c r="C116">
-        <v>819</v>
+        <v>913</v>
       </c>
       <c r="D116">
         <v>1088</v>
@@ -5528,19 +5528,19 @@
         <v>2290.22</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I116">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J116">
-        <v>0</v>
+        <v>1.5282</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>0.786</v>
       </c>
       <c r="L116" t="s">
         <v>15</v>
@@ -5560,7 +5560,7 @@
         <v>116</v>
       </c>
       <c r="C117">
-        <v>913</v>
+        <v>1006</v>
       </c>
       <c r="D117">
         <v>1088</v>
@@ -5572,19 +5572,19 @@
         <v>2290.22</v>
       </c>
       <c r="G117">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I117">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J117">
-        <v>1.5282</v>
+        <v>0</v>
       </c>
       <c r="K117">
-        <v>0.786</v>
+        <v>0</v>
       </c>
       <c r="L117" t="s">
         <v>15</v>
@@ -5604,16 +5604,16 @@
         <v>117</v>
       </c>
       <c r="C118">
-        <v>1006</v>
+        <v>1099</v>
       </c>
       <c r="D118">
         <v>1088</v>
       </c>
       <c r="E118">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F118">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -5648,7 +5648,7 @@
         <v>118</v>
       </c>
       <c r="C119">
-        <v>1099</v>
+        <v>1754</v>
       </c>
       <c r="D119">
         <v>1088</v>
@@ -5660,19 +5660,19 @@
         <v>2463.01</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I119">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J119">
-        <v>0</v>
+        <v>1.3398</v>
       </c>
       <c r="K119">
-        <v>0</v>
+        <v>1.3398</v>
       </c>
       <c r="L119" t="s">
         <v>15</v>
@@ -5692,31 +5692,31 @@
         <v>119</v>
       </c>
       <c r="C120">
-        <v>1754</v>
+        <v>1847</v>
       </c>
       <c r="D120">
         <v>1088</v>
       </c>
       <c r="E120">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F120">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G120">
         <v>1</v>
       </c>
       <c r="H120">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I120">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J120">
-        <v>1.3398</v>
+        <v>0.9606</v>
       </c>
       <c r="K120">
-        <v>1.3398</v>
+        <v>0.9606</v>
       </c>
       <c r="L120" t="s">
         <v>15</v>
@@ -5736,7 +5736,7 @@
         <v>120</v>
       </c>
       <c r="C121">
-        <v>1847</v>
+        <v>1941</v>
       </c>
       <c r="D121">
         <v>1088</v>
@@ -5748,19 +5748,19 @@
         <v>2290.22</v>
       </c>
       <c r="G121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H121">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I121">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J121">
-        <v>0.9606</v>
+        <v>2.3579</v>
       </c>
       <c r="K121">
-        <v>0.9606</v>
+        <v>1.3972</v>
       </c>
       <c r="L121" t="s">
         <v>15</v>
@@ -5780,16 +5780,16 @@
         <v>121</v>
       </c>
       <c r="C122">
-        <v>1940</v>
+        <v>1193</v>
       </c>
       <c r="D122">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E122">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F122">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G122">
         <v>2</v>
@@ -5798,13 +5798,13 @@
         <v>74</v>
       </c>
       <c r="I122">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J122">
-        <v>3.4845</v>
+        <v>3.2311</v>
       </c>
       <c r="K122">
-        <v>2.4485</v>
+        <v>2.1832</v>
       </c>
       <c r="L122" t="s">
         <v>15</v>
@@ -5824,10 +5824,10 @@
         <v>122</v>
       </c>
       <c r="C123">
-        <v>1193</v>
+        <v>1660</v>
       </c>
       <c r="D123">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E123">
         <v>54</v>
@@ -5836,19 +5836,19 @@
         <v>2290.22</v>
       </c>
       <c r="G123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H123">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I123">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="J123">
-        <v>3.2311</v>
+        <v>3.4058</v>
       </c>
       <c r="K123">
-        <v>2.1832</v>
+        <v>3.4058</v>
       </c>
       <c r="L123" t="s">
         <v>15</v>
@@ -5868,31 +5868,31 @@
         <v>123</v>
       </c>
       <c r="C124">
-        <v>1660</v>
+        <v>1288</v>
       </c>
       <c r="D124">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="E124">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F124">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="I124">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="J124">
-        <v>3.4058</v>
+        <v>0</v>
       </c>
       <c r="K124">
-        <v>3.4058</v>
+        <v>0</v>
       </c>
       <c r="L124" t="s">
         <v>15</v>
@@ -5912,7 +5912,7 @@
         <v>124</v>
       </c>
       <c r="C125">
-        <v>1288</v>
+        <v>1381</v>
       </c>
       <c r="D125">
         <v>1092</v>
@@ -5956,7 +5956,7 @@
         <v>125</v>
       </c>
       <c r="C126">
-        <v>1381</v>
+        <v>1475</v>
       </c>
       <c r="D126">
         <v>1092</v>
@@ -6000,7 +6000,7 @@
         <v>126</v>
       </c>
       <c r="C127">
-        <v>1475</v>
+        <v>1568</v>
       </c>
       <c r="D127">
         <v>1092</v>
@@ -6044,31 +6044,31 @@
         <v>127</v>
       </c>
       <c r="C128">
-        <v>1568</v>
+        <v>2045</v>
       </c>
       <c r="D128">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E128">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F128">
-        <v>2827.43</v>
+        <v>1963.5</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I128">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J128">
-        <v>0</v>
+        <v>1.9353</v>
       </c>
       <c r="K128">
-        <v>0</v>
+        <v>1.1205</v>
       </c>
       <c r="L128" t="s">
         <v>15</v>
@@ -6088,31 +6088,31 @@
         <v>128</v>
       </c>
       <c r="C129">
-        <v>2045</v>
+        <v>2159</v>
       </c>
       <c r="D129">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E129">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F129">
-        <v>2123.72</v>
+        <v>2827.43</v>
       </c>
       <c r="G129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I129">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J129">
-        <v>1.0359</v>
+        <v>0</v>
       </c>
       <c r="K129">
-        <v>1.0359</v>
+        <v>0</v>
       </c>
       <c r="L129" t="s">
         <v>15</v>
@@ -6798,10 +6798,10 @@
         <v>1159</v>
       </c>
       <c r="E145">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F145">
-        <v>3019.07</v>
+        <v>2827.43</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -6836,31 +6836,31 @@
         <v>145</v>
       </c>
       <c r="C146">
-        <v>2164</v>
+        <v>1298</v>
       </c>
       <c r="D146">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E146">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="F146">
-        <v>3019.07</v>
+        <v>1963.5</v>
       </c>
       <c r="G146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H146">
-        <v>147</v>
+        <v>66</v>
       </c>
       <c r="I146">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="J146">
-        <v>4.869</v>
+        <v>3.3614</v>
       </c>
       <c r="K146">
-        <v>4.869</v>
+        <v>1.5788</v>
       </c>
       <c r="L146" t="s">
         <v>15</v>
@@ -7144,31 +7144,31 @@
         <v>152</v>
       </c>
       <c r="C153">
-        <v>1289</v>
+        <v>1478</v>
       </c>
       <c r="D153">
         <v>1221</v>
       </c>
       <c r="E153">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F153">
-        <v>3019.07</v>
+        <v>2463.01</v>
       </c>
       <c r="G153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I153">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J153">
-        <v>1.9874</v>
+        <v>0</v>
       </c>
       <c r="K153">
-        <v>1.9874</v>
+        <v>0</v>
       </c>
       <c r="L153" t="s">
         <v>15</v>
@@ -7364,16 +7364,16 @@
         <v>157</v>
       </c>
       <c r="C158">
-        <v>1385</v>
+        <v>2145</v>
       </c>
       <c r="D158">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="E158">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F158">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -7408,31 +7408,31 @@
         <v>158</v>
       </c>
       <c r="C159">
-        <v>1572</v>
+        <v>1385</v>
       </c>
       <c r="D159">
         <v>1222</v>
       </c>
       <c r="E159">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F159">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I159">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J159">
-        <v>0.7714</v>
+        <v>0</v>
       </c>
       <c r="K159">
-        <v>0.7714</v>
+        <v>0</v>
       </c>
       <c r="L159" t="s">
         <v>15</v>
@@ -7452,7 +7452,7 @@
         <v>159</v>
       </c>
       <c r="C160">
-        <v>1669</v>
+        <v>1572</v>
       </c>
       <c r="D160">
         <v>1222</v>
@@ -7467,16 +7467,16 @@
         <v>1</v>
       </c>
       <c r="H160">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="I160">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="J160">
-        <v>2.2736</v>
+        <v>0.7714</v>
       </c>
       <c r="K160">
-        <v>2.2736</v>
+        <v>0.7714</v>
       </c>
       <c r="L160" t="s">
         <v>15</v>
@@ -7496,31 +7496,31 @@
         <v>160</v>
       </c>
       <c r="C161">
-        <v>1477</v>
+        <v>1669</v>
       </c>
       <c r="D161">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="E161">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F161">
-        <v>3019.07</v>
+        <v>2463.01</v>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H161">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I161">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J161">
-        <v>0</v>
+        <v>2.2736</v>
       </c>
       <c r="K161">
-        <v>0</v>
+        <v>2.2736</v>
       </c>
       <c r="L161" t="s">
         <v>15</v>
@@ -7540,31 +7540,31 @@
         <v>161</v>
       </c>
       <c r="C162">
-        <v>2148</v>
+        <v>714</v>
       </c>
       <c r="D162">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="E162">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F162">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G162">
         <v>1</v>
       </c>
       <c r="H162">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I162">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J162">
-        <v>0.8842</v>
+        <v>0.6902</v>
       </c>
       <c r="K162">
-        <v>0.8842</v>
+        <v>0.6902</v>
       </c>
       <c r="L162" t="s">
         <v>15</v>
@@ -7584,31 +7584,31 @@
         <v>162</v>
       </c>
       <c r="C163">
-        <v>714</v>
+        <v>1853</v>
       </c>
       <c r="D163">
         <v>1288</v>
       </c>
       <c r="E163">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F163">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I163">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J163">
-        <v>0.6902</v>
+        <v>0</v>
       </c>
       <c r="K163">
-        <v>0.6902</v>
+        <v>0</v>
       </c>
       <c r="L163" t="s">
         <v>15</v>
@@ -7628,31 +7628,31 @@
         <v>163</v>
       </c>
       <c r="C164">
-        <v>1853</v>
+        <v>810</v>
       </c>
       <c r="D164">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="E164">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F164">
-        <v>3019.07</v>
+        <v>2463.01</v>
       </c>
       <c r="G164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I164">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J164">
-        <v>0</v>
+        <v>0.7714</v>
       </c>
       <c r="K164">
-        <v>0</v>
+        <v>0.7714</v>
       </c>
       <c r="L164" t="s">
         <v>15</v>
@@ -7672,31 +7672,31 @@
         <v>164</v>
       </c>
       <c r="C165">
-        <v>810</v>
+        <v>906</v>
       </c>
       <c r="D165">
         <v>1289</v>
       </c>
       <c r="E165">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F165">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H165">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I165">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J165">
-        <v>0.7714</v>
+        <v>2.0085</v>
       </c>
       <c r="K165">
-        <v>0.7714</v>
+        <v>1.0916</v>
       </c>
       <c r="L165" t="s">
         <v>15</v>
@@ -7716,31 +7716,31 @@
         <v>165</v>
       </c>
       <c r="C166">
-        <v>906</v>
+        <v>1001</v>
       </c>
       <c r="D166">
         <v>1289</v>
       </c>
       <c r="E166">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F166">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G166">
         <v>2</v>
       </c>
       <c r="H166">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="I166">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J166">
-        <v>2.0085</v>
+        <v>1.624</v>
       </c>
       <c r="K166">
-        <v>1.0916</v>
+        <v>0.8932</v>
       </c>
       <c r="L166" t="s">
         <v>15</v>
@@ -7760,7 +7760,7 @@
         <v>166</v>
       </c>
       <c r="C167">
-        <v>1001</v>
+        <v>1097</v>
       </c>
       <c r="D167">
         <v>1289</v>
@@ -7772,19 +7772,19 @@
         <v>2463.01</v>
       </c>
       <c r="G167">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I167">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J167">
-        <v>1.624</v>
+        <v>0</v>
       </c>
       <c r="K167">
-        <v>0.8932</v>
+        <v>0</v>
       </c>
       <c r="L167" t="s">
         <v>15</v>
@@ -7804,7 +7804,7 @@
         <v>167</v>
       </c>
       <c r="C168">
-        <v>1097</v>
+        <v>1192</v>
       </c>
       <c r="D168">
         <v>1289</v>
@@ -7848,7 +7848,7 @@
         <v>168</v>
       </c>
       <c r="C169">
-        <v>1192</v>
+        <v>1480</v>
       </c>
       <c r="D169">
         <v>1289</v>
@@ -7892,7 +7892,7 @@
         <v>169</v>
       </c>
       <c r="C170">
-        <v>1480</v>
+        <v>1669</v>
       </c>
       <c r="D170">
         <v>1289</v>
@@ -7904,19 +7904,19 @@
         <v>2463.01</v>
       </c>
       <c r="G170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H170">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I170">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="J170">
-        <v>0</v>
+        <v>2.9639</v>
       </c>
       <c r="K170">
-        <v>0</v>
+        <v>2.9639</v>
       </c>
       <c r="L170" t="s">
         <v>15</v>
@@ -7936,31 +7936,31 @@
         <v>170</v>
       </c>
       <c r="C171">
-        <v>1669</v>
+        <v>1766</v>
       </c>
       <c r="D171">
         <v>1289</v>
       </c>
       <c r="E171">
+        <v>54</v>
+      </c>
+      <c r="F171">
+        <v>2290.22</v>
+      </c>
+      <c r="G171">
+        <v>1</v>
+      </c>
+      <c r="H171">
         <v>56</v>
       </c>
-      <c r="F171">
-        <v>2463.01</v>
-      </c>
-      <c r="G171">
-        <v>1</v>
-      </c>
-      <c r="H171">
-        <v>73</v>
-      </c>
       <c r="I171">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="J171">
-        <v>2.9639</v>
+        <v>2.4452</v>
       </c>
       <c r="K171">
-        <v>2.9639</v>
+        <v>2.4452</v>
       </c>
       <c r="L171" t="s">
         <v>15</v>
@@ -7980,7 +7980,7 @@
         <v>171</v>
       </c>
       <c r="C172">
-        <v>1766</v>
+        <v>1956</v>
       </c>
       <c r="D172">
         <v>1289</v>
@@ -7995,16 +7995,16 @@
         <v>1</v>
       </c>
       <c r="H172">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I172">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J172">
-        <v>2.4452</v>
+        <v>2.0959</v>
       </c>
       <c r="K172">
-        <v>2.4452</v>
+        <v>2.0959</v>
       </c>
       <c r="L172" t="s">
         <v>15</v>
@@ -8024,31 +8024,31 @@
         <v>172</v>
       </c>
       <c r="C173">
-        <v>1956</v>
+        <v>2053</v>
       </c>
       <c r="D173">
         <v>1289</v>
       </c>
       <c r="E173">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F173">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G173">
         <v>1</v>
       </c>
       <c r="H173">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="I173">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="J173">
-        <v>2.0959</v>
+        <v>0.8327</v>
       </c>
       <c r="K173">
-        <v>2.0959</v>
+        <v>0.8327</v>
       </c>
       <c r="L173" t="s">
         <v>15</v>
@@ -8068,10 +8068,10 @@
         <v>173</v>
       </c>
       <c r="C174">
-        <v>1384</v>
+        <v>2151</v>
       </c>
       <c r="D174">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="E174">
         <v>56</v>
@@ -8080,19 +8080,19 @@
         <v>2463.01</v>
       </c>
       <c r="G174">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H174">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I174">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J174">
-        <v>0</v>
+        <v>1.7864</v>
       </c>
       <c r="K174">
-        <v>0</v>
+        <v>1.015</v>
       </c>
       <c r="L174" t="s">
         <v>15</v>
@@ -8112,31 +8112,31 @@
         <v>174</v>
       </c>
       <c r="C175">
-        <v>1575</v>
+        <v>1384</v>
       </c>
       <c r="D175">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="E175">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F175">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G175">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H175">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I175">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J175">
-        <v>1.7032</v>
+        <v>0</v>
       </c>
       <c r="K175">
-        <v>0.9841</v>
+        <v>0</v>
       </c>
       <c r="L175" t="s">
         <v>15</v>
@@ -8156,31 +8156,31 @@
         <v>175</v>
       </c>
       <c r="C176">
-        <v>1286</v>
+        <v>1575</v>
       </c>
       <c r="D176">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="E176">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F176">
-        <v>2827.43</v>
+        <v>2642.08</v>
       </c>
       <c r="G176">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H176">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I176">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J176">
-        <v>0</v>
+        <v>1.7032</v>
       </c>
       <c r="K176">
-        <v>0</v>
+        <v>0.9841</v>
       </c>
       <c r="L176" t="s">
         <v>15</v>
@@ -8200,31 +8200,31 @@
         <v>176</v>
       </c>
       <c r="C177">
-        <v>2052</v>
+        <v>1286</v>
       </c>
       <c r="D177">
         <v>1292</v>
       </c>
       <c r="E177">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F177">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H177">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I177">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J177">
-        <v>0.8327</v>
+        <v>0</v>
       </c>
       <c r="K177">
-        <v>0.8327</v>
+        <v>0</v>
       </c>
       <c r="L177" t="s">
         <v>15</v>
@@ -9916,31 +9916,31 @@
         <v>215</v>
       </c>
       <c r="C216">
-        <v>1289</v>
+        <v>1189</v>
       </c>
       <c r="D216">
         <v>1499</v>
       </c>
       <c r="E216">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F216">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G216">
         <v>2</v>
       </c>
       <c r="H216">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="I216">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J216">
-        <v>2.4766</v>
+        <v>2.5737</v>
       </c>
       <c r="K216">
-        <v>1.3398</v>
+        <v>1.3626</v>
       </c>
       <c r="L216" t="s">
         <v>15</v>
@@ -9960,7 +9960,7 @@
         <v>216</v>
       </c>
       <c r="C217">
-        <v>1484</v>
+        <v>1289</v>
       </c>
       <c r="D217">
         <v>1499</v>
@@ -9972,19 +9972,19 @@
         <v>2463.01</v>
       </c>
       <c r="G217">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H217">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I217">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J217">
-        <v>0</v>
+        <v>2.4766</v>
       </c>
       <c r="K217">
-        <v>0</v>
+        <v>1.3398</v>
       </c>
       <c r="L217" t="s">
         <v>15</v>
@@ -10004,7 +10004,7 @@
         <v>217</v>
       </c>
       <c r="C218">
-        <v>1582</v>
+        <v>1484</v>
       </c>
       <c r="D218">
         <v>1499</v>
@@ -10016,19 +10016,19 @@
         <v>2463.01</v>
       </c>
       <c r="G218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H218">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I218">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J218">
-        <v>0.7714</v>
+        <v>0</v>
       </c>
       <c r="K218">
-        <v>0.7714</v>
+        <v>0</v>
       </c>
       <c r="L218" t="s">
         <v>15</v>
@@ -10048,7 +10048,7 @@
         <v>218</v>
       </c>
       <c r="C219">
-        <v>1680</v>
+        <v>1582</v>
       </c>
       <c r="D219">
         <v>1499</v>
@@ -10063,16 +10063,16 @@
         <v>1</v>
       </c>
       <c r="H219">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I219">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="J219">
-        <v>1.5022</v>
+        <v>0.7714</v>
       </c>
       <c r="K219">
-        <v>1.5022</v>
+        <v>0.7714</v>
       </c>
       <c r="L219" t="s">
         <v>15</v>
@@ -10092,7 +10092,7 @@
         <v>219</v>
       </c>
       <c r="C220">
-        <v>1777</v>
+        <v>1680</v>
       </c>
       <c r="D220">
         <v>1499</v>
@@ -10104,19 +10104,19 @@
         <v>2463.01</v>
       </c>
       <c r="G220">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H220">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I220">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J220">
-        <v>1.9082</v>
+        <v>1.5022</v>
       </c>
       <c r="K220">
-        <v>0.9744</v>
+        <v>1.5022</v>
       </c>
       <c r="L220" t="s">
         <v>15</v>
@@ -10136,31 +10136,31 @@
         <v>220</v>
       </c>
       <c r="C221">
-        <v>1874</v>
+        <v>1777</v>
       </c>
       <c r="D221">
         <v>1499</v>
       </c>
       <c r="E221">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F221">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G221">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H221">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I221">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J221">
-        <v>0</v>
+        <v>1.9082</v>
       </c>
       <c r="K221">
-        <v>0</v>
+        <v>0.9744</v>
       </c>
       <c r="L221" t="s">
         <v>15</v>
@@ -10180,16 +10180,16 @@
         <v>221</v>
       </c>
       <c r="C222">
-        <v>1972</v>
+        <v>1874</v>
       </c>
       <c r="D222">
         <v>1499</v>
       </c>
       <c r="E222">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F222">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G222">
         <v>0</v>
@@ -10224,31 +10224,31 @@
         <v>222</v>
       </c>
       <c r="C223">
-        <v>2070</v>
+        <v>1972</v>
       </c>
       <c r="D223">
         <v>1499</v>
       </c>
       <c r="E223">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F223">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G223">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H223">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="I223">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="J223">
-        <v>5.7152</v>
+        <v>0</v>
       </c>
       <c r="K223">
-        <v>2.0438</v>
+        <v>0</v>
       </c>
       <c r="L223" t="s">
         <v>15</v>
@@ -10268,31 +10268,31 @@
         <v>223</v>
       </c>
       <c r="C224">
-        <v>1384</v>
+        <v>2070</v>
       </c>
       <c r="D224">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="E224">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F224">
-        <v>2827.43</v>
+        <v>2642.08</v>
       </c>
       <c r="G224">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H224">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="I224">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J224">
-        <v>2.4757</v>
+        <v>5.7152</v>
       </c>
       <c r="K224">
-        <v>1.6977</v>
+        <v>2.0438</v>
       </c>
       <c r="L224" t="s">
         <v>15</v>
@@ -10312,10 +10312,10 @@
         <v>224</v>
       </c>
       <c r="C225">
-        <v>1191</v>
+        <v>1384</v>
       </c>
       <c r="D225">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="E225">
         <v>60</v>
@@ -10324,19 +10324,19 @@
         <v>2827.43</v>
       </c>
       <c r="G225">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H225">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="I225">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J225">
-        <v>1.1318</v>
+        <v>2.4757</v>
       </c>
       <c r="K225">
-        <v>1.1318</v>
+        <v>1.6977</v>
       </c>
       <c r="L225" t="s">
         <v>15</v>
@@ -10356,7 +10356,7 @@
         <v>225</v>
       </c>
       <c r="C226">
-        <v>2177</v>
+        <v>1387</v>
       </c>
       <c r="D226">
         <v>1568</v>
@@ -10368,19 +10368,19 @@
         <v>2827.43</v>
       </c>
       <c r="G226">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H226">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="I226">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="J226">
-        <v>7.6041</v>
+        <v>0</v>
       </c>
       <c r="K226">
-        <v>3.6075</v>
+        <v>0</v>
       </c>
       <c r="L226" t="s">
         <v>15</v>
@@ -10400,31 +10400,31 @@
         <v>226</v>
       </c>
       <c r="C227">
-        <v>698</v>
+        <v>2177</v>
       </c>
       <c r="D227">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="E227">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F227">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G227">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H227">
-        <v>78</v>
+        <v>215</v>
       </c>
       <c r="I227">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="J227">
-        <v>3.1669</v>
+        <v>7.6041</v>
       </c>
       <c r="K227">
-        <v>1.6646</v>
+        <v>3.6075</v>
       </c>
       <c r="L227" t="s">
         <v>15</v>
@@ -10444,7 +10444,7 @@
         <v>227</v>
       </c>
       <c r="C228">
-        <v>797</v>
+        <v>698</v>
       </c>
       <c r="D228">
         <v>1571</v>
@@ -10459,16 +10459,16 @@
         <v>2</v>
       </c>
       <c r="H228">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="I228">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="J228">
-        <v>4.2631</v>
+        <v>3.1669</v>
       </c>
       <c r="K228">
-        <v>2.7203</v>
+        <v>1.6646</v>
       </c>
       <c r="L228" t="s">
         <v>15</v>
@@ -10488,31 +10488,31 @@
         <v>228</v>
       </c>
       <c r="C229">
-        <v>895</v>
+        <v>797</v>
       </c>
       <c r="D229">
         <v>1571</v>
       </c>
       <c r="E229">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F229">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G229">
         <v>2</v>
       </c>
       <c r="H229">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="I229">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="J229">
-        <v>2.1574</v>
+        <v>4.2631</v>
       </c>
       <c r="K229">
-        <v>1.514</v>
+        <v>2.7203</v>
       </c>
       <c r="L229" t="s">
         <v>15</v>
@@ -10532,7 +10532,7 @@
         <v>229</v>
       </c>
       <c r="C230">
-        <v>998</v>
+        <v>895</v>
       </c>
       <c r="D230">
         <v>1571</v>
@@ -10547,16 +10547,16 @@
         <v>2</v>
       </c>
       <c r="H230">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="I230">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J230">
-        <v>2.6873</v>
+        <v>2.1574</v>
       </c>
       <c r="K230">
-        <v>1.7032</v>
+        <v>1.514</v>
       </c>
       <c r="L230" t="s">
         <v>15</v>
@@ -10576,31 +10576,31 @@
         <v>230</v>
       </c>
       <c r="C231">
-        <v>1092</v>
+        <v>998</v>
       </c>
       <c r="D231">
         <v>1571</v>
       </c>
       <c r="E231">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F231">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G231">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H231">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="I231">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="J231">
-        <v>1.0556</v>
+        <v>2.6873</v>
       </c>
       <c r="K231">
-        <v>1.0556</v>
+        <v>1.7032</v>
       </c>
       <c r="L231" t="s">
         <v>15</v>
@@ -10620,7 +10620,7 @@
         <v>231</v>
       </c>
       <c r="C232">
-        <v>1192</v>
+        <v>1092</v>
       </c>
       <c r="D232">
         <v>1571</v>
@@ -10632,19 +10632,19 @@
         <v>2463.01</v>
       </c>
       <c r="G232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H232">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="I232">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J232">
-        <v>2.3548</v>
+        <v>1.0556</v>
       </c>
       <c r="K232">
-        <v>1.2992</v>
+        <v>1.0556</v>
       </c>
       <c r="L232" t="s">
         <v>15</v>
@@ -10664,7 +10664,7 @@
         <v>232</v>
       </c>
       <c r="C233">
-        <v>1290</v>
+        <v>1192</v>
       </c>
       <c r="D233">
         <v>1571</v>
@@ -10676,19 +10676,19 @@
         <v>2463.01</v>
       </c>
       <c r="G233">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H233">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="I233">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J233">
-        <v>4.6285</v>
+        <v>2.3548</v>
       </c>
       <c r="K233">
-        <v>1.1368</v>
+        <v>1.2992</v>
       </c>
       <c r="L233" t="s">
         <v>15</v>
@@ -10708,7 +10708,7 @@
         <v>233</v>
       </c>
       <c r="C234">
-        <v>1486</v>
+        <v>1290</v>
       </c>
       <c r="D234">
         <v>1571</v>
@@ -10720,19 +10720,19 @@
         <v>2463.01</v>
       </c>
       <c r="G234">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H234">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="I234">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J234">
-        <v>2.1112</v>
+        <v>4.6285</v>
       </c>
       <c r="K234">
-        <v>1.2586</v>
+        <v>1.1368</v>
       </c>
       <c r="L234" t="s">
         <v>15</v>
@@ -10752,7 +10752,7 @@
         <v>234</v>
       </c>
       <c r="C235">
-        <v>1585</v>
+        <v>1486</v>
       </c>
       <c r="D235">
         <v>1571</v>
@@ -10764,19 +10764,19 @@
         <v>2463.01</v>
       </c>
       <c r="G235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H235">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I235">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="J235">
-        <v>2.3548</v>
+        <v>2.1112</v>
       </c>
       <c r="K235">
-        <v>2.3548</v>
+        <v>1.2586</v>
       </c>
       <c r="L235" t="s">
         <v>15</v>
@@ -10796,7 +10796,7 @@
         <v>235</v>
       </c>
       <c r="C236">
-        <v>1683</v>
+        <v>1585</v>
       </c>
       <c r="D236">
         <v>1571</v>
@@ -10811,16 +10811,16 @@
         <v>1</v>
       </c>
       <c r="H236">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="I236">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="J236">
-        <v>0.7714</v>
+        <v>2.3548</v>
       </c>
       <c r="K236">
-        <v>0.7714</v>
+        <v>2.3548</v>
       </c>
       <c r="L236" t="s">
         <v>15</v>
@@ -10840,31 +10840,31 @@
         <v>236</v>
       </c>
       <c r="C237">
-        <v>1781</v>
+        <v>1683</v>
       </c>
       <c r="D237">
         <v>1571</v>
       </c>
       <c r="E237">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F237">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I237">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J237">
-        <v>0</v>
+        <v>0.7714</v>
       </c>
       <c r="K237">
-        <v>0</v>
+        <v>0.7714</v>
       </c>
       <c r="L237" t="s">
         <v>15</v>
@@ -10884,7 +10884,7 @@
         <v>237</v>
       </c>
       <c r="C238">
-        <v>1879</v>
+        <v>1781</v>
       </c>
       <c r="D238">
         <v>1571</v>
@@ -10896,19 +10896,19 @@
         <v>2642.08</v>
       </c>
       <c r="G238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H238">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I238">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J238">
-        <v>1.6654</v>
+        <v>0</v>
       </c>
       <c r="K238">
-        <v>1.6654</v>
+        <v>0</v>
       </c>
       <c r="L238" t="s">
         <v>15</v>
@@ -10928,7 +10928,7 @@
         <v>238</v>
       </c>
       <c r="C239">
-        <v>1977</v>
+        <v>1879</v>
       </c>
       <c r="D239">
         <v>1571</v>
@@ -10940,19 +10940,19 @@
         <v>2642.08</v>
       </c>
       <c r="G239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H239">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="I239">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J239">
-        <v>2.3845</v>
+        <v>1.6654</v>
       </c>
       <c r="K239">
-        <v>1.6275</v>
+        <v>1.6654</v>
       </c>
       <c r="L239" t="s">
         <v>15</v>
@@ -10972,7 +10972,7 @@
         <v>239</v>
       </c>
       <c r="C240">
-        <v>2076</v>
+        <v>1977</v>
       </c>
       <c r="D240">
         <v>1571</v>
@@ -10984,19 +10984,19 @@
         <v>2642.08</v>
       </c>
       <c r="G240">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H240">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="I240">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J240">
-        <v>4.0877</v>
+        <v>2.3845</v>
       </c>
       <c r="K240">
-        <v>1.7789</v>
+        <v>1.6275</v>
       </c>
       <c r="L240" t="s">
         <v>15</v>
@@ -11016,31 +11016,31 @@
         <v>240</v>
       </c>
       <c r="C241">
-        <v>1388</v>
+        <v>2076</v>
       </c>
       <c r="D241">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="E241">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F241">
-        <v>2827.43</v>
+        <v>2642.08</v>
       </c>
       <c r="G241">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="I241">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J241">
-        <v>0</v>
+        <v>4.0877</v>
       </c>
       <c r="K241">
-        <v>0</v>
+        <v>1.7789</v>
       </c>
       <c r="L241" t="s">
         <v>15</v>
@@ -11060,31 +11060,31 @@
         <v>241</v>
       </c>
       <c r="C242">
-        <v>1668</v>
+        <v>695</v>
       </c>
       <c r="D242">
-        <v>1635</v>
+        <v>1643</v>
       </c>
       <c r="E242">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F242">
-        <v>3019.07</v>
+        <v>2642.08</v>
       </c>
       <c r="G242">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H242">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="I242">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="J242">
-        <v>5.2003</v>
+        <v>5.261</v>
       </c>
       <c r="K242">
-        <v>5.2003</v>
+        <v>2.0438</v>
       </c>
       <c r="L242" t="s">
         <v>15</v>
@@ -11104,31 +11104,31 @@
         <v>242</v>
       </c>
       <c r="C243">
-        <v>1567</v>
+        <v>1090</v>
       </c>
       <c r="D243">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="E243">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F243">
-        <v>3019.07</v>
+        <v>2642.08</v>
       </c>
       <c r="G243">
         <v>2</v>
       </c>
       <c r="H243">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="I243">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="J243">
-        <v>2.3517</v>
+        <v>3.1036</v>
       </c>
       <c r="K243">
-        <v>1.4243</v>
+        <v>2.006</v>
       </c>
       <c r="L243" t="s">
         <v>15</v>
@@ -11148,31 +11148,31 @@
         <v>243</v>
       </c>
       <c r="C244">
-        <v>2180</v>
+        <v>1190</v>
       </c>
       <c r="D244">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="E244">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F244">
-        <v>3019.07</v>
+        <v>2642.08</v>
       </c>
       <c r="G244">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H244">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="I244">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="J244">
-        <v>4.1072</v>
+        <v>2.9901</v>
       </c>
       <c r="K244">
-        <v>2.1199</v>
+        <v>1.5518</v>
       </c>
       <c r="L244" t="s">
         <v>15</v>
@@ -11192,31 +11192,31 @@
         <v>244</v>
       </c>
       <c r="C245">
-        <v>695</v>
+        <v>2077</v>
       </c>
       <c r="D245">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="E245">
+        <v>56</v>
+      </c>
+      <c r="F245">
+        <v>2463.01</v>
+      </c>
+      <c r="G245">
+        <v>2</v>
+      </c>
+      <c r="H245">
         <v>58</v>
       </c>
-      <c r="F245">
-        <v>2642.08</v>
-      </c>
-      <c r="G245">
-        <v>4</v>
-      </c>
-      <c r="H245">
-        <v>139</v>
-      </c>
       <c r="I245">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="J245">
-        <v>5.261</v>
+        <v>2.3548</v>
       </c>
       <c r="K245">
-        <v>2.0438</v>
+        <v>1.2586</v>
       </c>
       <c r="L245" t="s">
         <v>15</v>
@@ -11236,31 +11236,31 @@
         <v>245</v>
       </c>
       <c r="C246">
-        <v>1090</v>
+        <v>2176</v>
       </c>
       <c r="D246">
         <v>1644</v>
       </c>
       <c r="E246">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F246">
-        <v>2642.08</v>
+        <v>2123.72</v>
       </c>
       <c r="G246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H246">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="I246">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="J246">
-        <v>3.1036</v>
+        <v>3.1078</v>
       </c>
       <c r="K246">
-        <v>2.006</v>
+        <v>3.1078</v>
       </c>
       <c r="L246" t="s">
         <v>15</v>
@@ -11280,31 +11280,31 @@
         <v>246</v>
       </c>
       <c r="C247">
-        <v>1190</v>
+        <v>1487</v>
       </c>
       <c r="D247">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="E247">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F247">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G247">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H247">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="I247">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J247">
-        <v>2.9901</v>
+        <v>2.4766</v>
       </c>
       <c r="K247">
-        <v>1.5518</v>
+        <v>1.5022</v>
       </c>
       <c r="L247" t="s">
         <v>15</v>
@@ -11324,31 +11324,31 @@
         <v>247</v>
       </c>
       <c r="C248">
-        <v>1971</v>
+        <v>1586</v>
       </c>
       <c r="D248">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="E248">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F248">
-        <v>1809.56</v>
+        <v>2463.01</v>
       </c>
       <c r="G248">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H248">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="I248">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="J248">
-        <v>1.3816</v>
+        <v>6.2931</v>
       </c>
       <c r="K248">
-        <v>1.3816</v>
+        <v>2.639</v>
       </c>
       <c r="L248" t="s">
         <v>15</v>
@@ -11368,31 +11368,31 @@
         <v>248</v>
       </c>
       <c r="C249">
-        <v>2078</v>
+        <v>1681</v>
       </c>
       <c r="D249">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="E249">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F249">
-        <v>2642.08</v>
+        <v>2123.72</v>
       </c>
       <c r="G249">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H249">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="I249">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J249">
-        <v>2.1952</v>
+        <v>0</v>
       </c>
       <c r="K249">
-        <v>1.1733</v>
+        <v>0</v>
       </c>
       <c r="L249" t="s">
         <v>15</v>
@@ -11412,31 +11412,31 @@
         <v>249</v>
       </c>
       <c r="C250">
-        <v>1488</v>
+        <v>1777</v>
       </c>
       <c r="D250">
         <v>1645</v>
       </c>
       <c r="E250">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F250">
-        <v>2463.01</v>
+        <v>1809.56</v>
       </c>
       <c r="G250">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H250">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="I250">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J250">
-        <v>2.0706</v>
+        <v>1.05</v>
       </c>
       <c r="K250">
-        <v>1.0962</v>
+        <v>1.05</v>
       </c>
       <c r="L250" t="s">
         <v>15</v>
@@ -11456,31 +11456,31 @@
         <v>250</v>
       </c>
       <c r="C251">
-        <v>1779</v>
+        <v>995</v>
       </c>
       <c r="D251">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="E251">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F251">
-        <v>1963.5</v>
+        <v>2827.43</v>
       </c>
       <c r="G251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H251">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="I251">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J251">
-        <v>1.1205</v>
+        <v>1.3793</v>
       </c>
       <c r="K251">
-        <v>1.1205</v>
+        <v>0.7427</v>
       </c>
       <c r="L251" t="s">
         <v>15</v>
@@ -11500,31 +11500,31 @@
         <v>251</v>
       </c>
       <c r="C252">
-        <v>1873</v>
+        <v>1895</v>
       </c>
       <c r="D252">
-        <v>1645</v>
+        <v>1653</v>
       </c>
       <c r="E252">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F252">
-        <v>1809.56</v>
+        <v>2827.43</v>
       </c>
       <c r="G252">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H252">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="I252">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="J252">
-        <v>1.1605</v>
+        <v>3.2538</v>
       </c>
       <c r="K252">
-        <v>1.1605</v>
+        <v>2.5111</v>
       </c>
       <c r="L252" t="s">
         <v>15</v>
@@ -11544,10 +11544,10 @@
         <v>252</v>
       </c>
       <c r="C253">
-        <v>995</v>
+        <v>901</v>
       </c>
       <c r="D253">
-        <v>1647</v>
+        <v>1654</v>
       </c>
       <c r="E253">
         <v>60</v>
@@ -11556,19 +11556,19 @@
         <v>2827.43</v>
       </c>
       <c r="G253">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H253">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="I253">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J253">
-        <v>1.3793</v>
+        <v>2.405</v>
       </c>
       <c r="K253">
-        <v>0.7427</v>
+        <v>0.9903</v>
       </c>
       <c r="L253" t="s">
         <v>15</v>
@@ -11588,31 +11588,31 @@
         <v>253</v>
       </c>
       <c r="C254">
-        <v>901</v>
+        <v>1399</v>
       </c>
       <c r="D254">
         <v>1654</v>
       </c>
       <c r="E254">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F254">
-        <v>3019.07</v>
+        <v>2827.43</v>
       </c>
       <c r="G254">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H254">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I254">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J254">
-        <v>2.1861</v>
+        <v>0</v>
       </c>
       <c r="K254">
-        <v>0.9274</v>
+        <v>0</v>
       </c>
       <c r="L254" t="s">
         <v>15</v>
@@ -11632,31 +11632,31 @@
         <v>254</v>
       </c>
       <c r="C255">
-        <v>1399</v>
+        <v>1277</v>
       </c>
       <c r="D255">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="E255">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F255">
-        <v>3019.07</v>
+        <v>2827.43</v>
       </c>
       <c r="G255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I255">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J255">
-        <v>0</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="K255">
-        <v>0</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="L255" t="s">
         <v>15</v>
@@ -11676,31 +11676,31 @@
         <v>255</v>
       </c>
       <c r="C256">
-        <v>1277</v>
+        <v>816</v>
       </c>
       <c r="D256">
-        <v>1655</v>
+        <v>1667</v>
       </c>
       <c r="E256">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F256">
-        <v>3019.07</v>
+        <v>2827.43</v>
       </c>
       <c r="G256">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H256">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="I256">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J256">
-        <v>3.6766</v>
+        <v>1.2732</v>
       </c>
       <c r="K256">
-        <v>1.4243</v>
+        <v>1.2732</v>
       </c>
       <c r="L256" t="s">
         <v>15</v>
@@ -11720,40 +11720,40 @@
         <v>256</v>
       </c>
       <c r="C257">
-        <v>819</v>
+        <v>1847</v>
       </c>
       <c r="D257">
-        <v>1659</v>
+        <v>1650</v>
       </c>
       <c r="E257">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F257">
-        <v>1963.5</v>
+        <v>2290.22</v>
       </c>
       <c r="G257">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H257">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I257">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J257">
-        <v>2.3428</v>
+        <v>0</v>
       </c>
       <c r="K257">
-        <v>2.3428</v>
+        <v>0</v>
       </c>
       <c r="L257" t="s">
         <v>15</v>
       </c>
       <c r="M257" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N257">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -11829,10 +11829,10 @@
         <v>256</v>
       </c>
       <c r="C2">
-        <v>1.4914</v>
+        <v>1.3952</v>
       </c>
       <c r="D2">
-        <v>11.5498</v>
+        <v>10.0678</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -11859,7 +11859,7 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Images_BGA/Results/Reports/PCBA1_08_inspection_report.xlsx
+++ b/Images_BGA/Results/Reports/PCBA1_08_inspection_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="29">
   <si>
     <t>image_name</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>PASS</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
   <si>
     <t>total_balls</t>
@@ -544,16 +547,16 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1083</v>
+        <v>1105</v>
       </c>
       <c r="D3">
-        <v>637</v>
+        <v>650</v>
       </c>
       <c r="E3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F3">
-        <v>2827.43</v>
+        <v>2123.72</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -767,28 +770,28 @@
         <v>1195</v>
       </c>
       <c r="D8">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="E8">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F8">
-        <v>2123.72</v>
+        <v>2463.01</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I8">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J8">
-        <v>2.1189</v>
+        <v>1.7052</v>
       </c>
       <c r="K8">
-        <v>2.1189</v>
+        <v>1.7052</v>
       </c>
       <c r="L8" t="s">
         <v>15</v>
@@ -852,31 +855,31 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D10">
         <v>650</v>
       </c>
       <c r="E10">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F10">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1.0186</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1.0186</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -896,16 +899,16 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>1462</v>
+        <v>1453</v>
       </c>
       <c r="D11">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="E11">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F11">
-        <v>2123.72</v>
+        <v>2642.08</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1031,13 +1034,13 @@
         <v>1730</v>
       </c>
       <c r="D14">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E14">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F14">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1049,10 +1052,10 @@
         <v>39</v>
       </c>
       <c r="J14">
-        <v>1.8364</v>
+        <v>1.9863</v>
       </c>
       <c r="K14">
-        <v>1.8364</v>
+        <v>1.9863</v>
       </c>
       <c r="L14" t="s">
         <v>15</v>
@@ -1072,16 +1075,16 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="D15">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="E15">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F15">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1116,10 +1119,10 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>2081</v>
+        <v>2089</v>
       </c>
       <c r="D16">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E16">
         <v>52</v>
@@ -1128,19 +1131,19 @@
         <v>2123.72</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>1.083</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>1.083</v>
+        <v>0</v>
       </c>
       <c r="L16" t="s">
         <v>15</v>
@@ -1204,10 +1207,10 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="D18">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="E18">
         <v>60</v>
@@ -1216,19 +1219,19 @@
         <v>2827.43</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="I18">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="J18">
-        <v>0.7427</v>
+        <v>3.6075</v>
       </c>
       <c r="K18">
-        <v>0.7427</v>
+        <v>1.5915</v>
       </c>
       <c r="L18" t="s">
         <v>15</v>
@@ -1248,31 +1251,31 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>2075</v>
+        <v>2087</v>
       </c>
       <c r="D19">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E19">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F19">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1.4004</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1.4004</v>
       </c>
       <c r="L19" t="s">
         <v>15</v>
@@ -1336,31 +1339,31 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="D21">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="E21">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F21">
-        <v>2123.72</v>
+        <v>2463.01</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I21">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J21">
-        <v>1.1301</v>
+        <v>1.0962</v>
       </c>
       <c r="K21">
-        <v>1.1301</v>
+        <v>1.0962</v>
       </c>
       <c r="L21" t="s">
         <v>15</v>
@@ -1380,16 +1383,16 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>1195</v>
+        <v>1187</v>
       </c>
       <c r="D22">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="E22">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F22">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1512,31 +1515,31 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="D25">
         <v>710</v>
       </c>
       <c r="E25">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F25">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1.5279</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1.5279</v>
       </c>
       <c r="L25" t="s">
         <v>15</v>
@@ -1644,16 +1647,16 @@
         <v>27</v>
       </c>
       <c r="C28">
-        <v>1912</v>
+        <v>1919</v>
       </c>
       <c r="D28">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="E28">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F28">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1665,10 +1668,10 @@
         <v>18</v>
       </c>
       <c r="J28">
-        <v>0.8476</v>
+        <v>0.786</v>
       </c>
       <c r="K28">
-        <v>0.8476</v>
+        <v>0.786</v>
       </c>
       <c r="L28" t="s">
         <v>15</v>
@@ -1688,16 +1691,16 @@
         <v>28</v>
       </c>
       <c r="C29">
-        <v>2158</v>
+        <v>2152</v>
       </c>
       <c r="D29">
-        <v>710</v>
+        <v>694</v>
       </c>
       <c r="E29">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F29">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1732,31 +1735,31 @@
         <v>29</v>
       </c>
       <c r="C30">
-        <v>926</v>
+        <v>915</v>
       </c>
       <c r="D30">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="E30">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F30">
-        <v>2123.72</v>
+        <v>2642.08</v>
       </c>
       <c r="G30">
         <v>2</v>
       </c>
       <c r="H30">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I30">
         <v>26</v>
       </c>
       <c r="J30">
-        <v>2.2602</v>
+        <v>1.9681</v>
       </c>
       <c r="K30">
-        <v>1.2243</v>
+        <v>0.9841</v>
       </c>
       <c r="L30" t="s">
         <v>15</v>
@@ -1776,16 +1779,16 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>1284</v>
+        <v>1270</v>
       </c>
       <c r="D31">
         <v>711</v>
       </c>
       <c r="E31">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F31">
-        <v>2123.72</v>
+        <v>2827.43</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -1864,31 +1867,31 @@
         <v>32</v>
       </c>
       <c r="C33">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="D33">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E33">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F33">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G33">
         <v>3</v>
       </c>
       <c r="H33">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I33">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J33">
-        <v>2.233</v>
+        <v>1.8391</v>
       </c>
       <c r="K33">
-        <v>0.8526</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="L33" t="s">
         <v>15</v>
@@ -1908,16 +1911,16 @@
         <v>33</v>
       </c>
       <c r="C34">
-        <v>2076</v>
+        <v>2092</v>
       </c>
       <c r="D34">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E34">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F34">
-        <v>1963.5</v>
+        <v>2642.08</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -1999,13 +2002,13 @@
         <v>833</v>
       </c>
       <c r="D36">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="E36">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F36">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2017,10 +2020,10 @@
         <v>16</v>
       </c>
       <c r="J36">
-        <v>0.6986</v>
+        <v>0.6056</v>
       </c>
       <c r="K36">
-        <v>0.6986</v>
+        <v>0.6056</v>
       </c>
       <c r="L36" t="s">
         <v>15</v>
@@ -2040,16 +2043,16 @@
         <v>36</v>
       </c>
       <c r="C37">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="D37">
         <v>771</v>
       </c>
       <c r="E37">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F37">
-        <v>2123.72</v>
+        <v>2827.43</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -2084,31 +2087,31 @@
         <v>37</v>
       </c>
       <c r="C38">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="D38">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E38">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F38">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>1.2714</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>1.2714</v>
+        <v>0</v>
       </c>
       <c r="L38" t="s">
         <v>15</v>
@@ -2128,10 +2131,10 @@
         <v>38</v>
       </c>
       <c r="C39">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="D39">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E39">
         <v>52</v>
@@ -2140,19 +2143,19 @@
         <v>2123.72</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>0.8476</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>0.8476</v>
       </c>
       <c r="L39" t="s">
         <v>15</v>
@@ -2216,7 +2219,7 @@
         <v>40</v>
       </c>
       <c r="C41">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D41">
         <v>771</v>
@@ -2231,16 +2234,16 @@
         <v>1</v>
       </c>
       <c r="H41">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I41">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J41">
-        <v>1.083</v>
+        <v>0.9417</v>
       </c>
       <c r="K41">
-        <v>1.083</v>
+        <v>0.9417</v>
       </c>
       <c r="L41" t="s">
         <v>15</v>
@@ -2392,7 +2395,7 @@
         <v>44</v>
       </c>
       <c r="C45">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="D45">
         <v>771</v>
@@ -2404,19 +2407,19 @@
         <v>2123.72</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>0.8476</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>0.8476</v>
       </c>
       <c r="L45" t="s">
         <v>15</v>
@@ -2436,16 +2439,16 @@
         <v>45</v>
       </c>
       <c r="C46">
-        <v>1826</v>
+        <v>1834</v>
       </c>
       <c r="D46">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="E46">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F46">
-        <v>2123.72</v>
+        <v>2463.01</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -2480,31 +2483,31 @@
         <v>46</v>
       </c>
       <c r="C47">
-        <v>1916</v>
+        <v>1910</v>
       </c>
       <c r="D47">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="E47">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F47">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>0.6986</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>0.6986</v>
       </c>
       <c r="L47" t="s">
         <v>15</v>
@@ -2527,13 +2530,13 @@
         <v>1285</v>
       </c>
       <c r="D48">
-        <v>772</v>
+        <v>815</v>
       </c>
       <c r="E48">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F48">
-        <v>2123.72</v>
+        <v>1520.53</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -2568,16 +2571,16 @@
         <v>48</v>
       </c>
       <c r="C49">
-        <v>2156</v>
+        <v>2148</v>
       </c>
       <c r="D49">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="E49">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F49">
-        <v>1963.5</v>
+        <v>2290.22</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -2656,31 +2659,31 @@
         <v>50</v>
       </c>
       <c r="C51">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D51">
         <v>829</v>
       </c>
       <c r="E51">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F51">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G51">
         <v>2</v>
       </c>
       <c r="H51">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I51">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J51">
-        <v>1.5834</v>
+        <v>2.0085</v>
       </c>
       <c r="K51">
-        <v>0.9338</v>
+        <v>1.1789</v>
       </c>
       <c r="L51" t="s">
         <v>15</v>
@@ -2700,31 +2703,31 @@
         <v>51</v>
       </c>
       <c r="C52">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="D52">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="E52">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F52">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I52">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J52">
-        <v>0.8296</v>
+        <v>1.2025</v>
       </c>
       <c r="K52">
-        <v>0.8296</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="L52" t="s">
         <v>15</v>
@@ -2744,16 +2747,16 @@
         <v>52</v>
       </c>
       <c r="C53">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D53">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="E53">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F53">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2835,13 +2838,13 @@
         <v>1467</v>
       </c>
       <c r="D55">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E55">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F55">
-        <v>2290.22</v>
+        <v>2123.72</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -2879,28 +2882,28 @@
         <v>1558</v>
       </c>
       <c r="D56">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E56">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F56">
-        <v>2290.22</v>
+        <v>2123.72</v>
       </c>
       <c r="G56">
         <v>3</v>
       </c>
       <c r="H56">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I56">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J56">
-        <v>3.0128</v>
+        <v>3.3903</v>
       </c>
       <c r="K56">
-        <v>1.2663</v>
+        <v>1.5068</v>
       </c>
       <c r="L56" t="s">
         <v>15</v>
@@ -2923,28 +2926,28 @@
         <v>1013</v>
       </c>
       <c r="D57">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="E57">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F57">
-        <v>2123.72</v>
+        <v>2463.01</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="I57">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J57">
-        <v>2.2131</v>
+        <v>0.7714</v>
       </c>
       <c r="K57">
-        <v>1.4597</v>
+        <v>0.7714</v>
       </c>
       <c r="L57" t="s">
         <v>15</v>
@@ -2964,31 +2967,31 @@
         <v>57</v>
       </c>
       <c r="C58">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="D58">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="E58">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F58">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="I58">
         <v>49</v>
       </c>
       <c r="J58">
-        <v>2.3073</v>
+        <v>2.8818</v>
       </c>
       <c r="K58">
-        <v>2.3073</v>
+        <v>2.1395</v>
       </c>
       <c r="L58" t="s">
         <v>15</v>
@@ -3008,31 +3011,31 @@
         <v>58</v>
       </c>
       <c r="C59">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="D59">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="E59">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F59">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I59">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J59">
-        <v>0.9417</v>
+        <v>1.1353</v>
       </c>
       <c r="K59">
-        <v>0.9417</v>
+        <v>1.1353</v>
       </c>
       <c r="L59" t="s">
         <v>15</v>
@@ -3140,10 +3143,10 @@
         <v>61</v>
       </c>
       <c r="C62">
-        <v>1742</v>
+        <v>1736</v>
       </c>
       <c r="D62">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="E62">
         <v>52</v>
@@ -3152,16 +3155,16 @@
         <v>2123.72</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="I62">
         <v>48</v>
       </c>
       <c r="J62">
-        <v>3.4845</v>
+        <v>2.2602</v>
       </c>
       <c r="K62">
         <v>2.2602</v>
@@ -3228,16 +3231,16 @@
         <v>63</v>
       </c>
       <c r="C64">
-        <v>1918</v>
+        <v>1927</v>
       </c>
       <c r="D64">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="E64">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F64">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -3272,31 +3275,31 @@
         <v>64</v>
       </c>
       <c r="C65">
-        <v>2155</v>
+        <v>2144</v>
       </c>
       <c r="D65">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="E65">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F65">
-        <v>1809.56</v>
+        <v>2290.22</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>10.6977</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>10.6977</v>
       </c>
       <c r="L65" t="s">
         <v>15</v>
@@ -3316,34 +3319,34 @@
         <v>65</v>
       </c>
       <c r="C66">
-        <v>2154</v>
+        <v>2142</v>
       </c>
       <c r="D66">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E66">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F66">
-        <v>1963.5</v>
+        <v>2642.08</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>12.1874</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>12.1874</v>
       </c>
       <c r="L66" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -3360,31 +3363,31 @@
         <v>66</v>
       </c>
       <c r="C67">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="D67">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E67">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F67">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I67">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J67">
-        <v>1.1789</v>
+        <v>0.7948</v>
       </c>
       <c r="K67">
-        <v>1.1789</v>
+        <v>0.7948</v>
       </c>
       <c r="L67" t="s">
         <v>15</v>
@@ -3404,31 +3407,31 @@
         <v>67</v>
       </c>
       <c r="C68">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D68">
         <v>895</v>
       </c>
       <c r="E68">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F68">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I68">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J68">
-        <v>1.6481</v>
+        <v>1.8335</v>
       </c>
       <c r="K68">
-        <v>1.6481</v>
+        <v>1.8335</v>
       </c>
       <c r="L68" t="s">
         <v>15</v>
@@ -3448,31 +3451,31 @@
         <v>68</v>
       </c>
       <c r="C69">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="D69">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="E69">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F69">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>2.3142</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>1.4616</v>
       </c>
       <c r="L69" t="s">
         <v>15</v>
@@ -3492,16 +3495,16 @@
         <v>69</v>
       </c>
       <c r="C70">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D70">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E70">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F70">
-        <v>2123.72</v>
+        <v>2463.01</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -3624,31 +3627,31 @@
         <v>72</v>
       </c>
       <c r="C73">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="D73">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E73">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F73">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I73">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J73">
-        <v>0.7423</v>
+        <v>0</v>
       </c>
       <c r="K73">
-        <v>0.7423</v>
+        <v>0</v>
       </c>
       <c r="L73" t="s">
         <v>15</v>
@@ -3668,31 +3671,31 @@
         <v>73</v>
       </c>
       <c r="C74">
-        <v>1286</v>
+        <v>1280</v>
       </c>
       <c r="D74">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E74">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F74">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G74">
         <v>1</v>
       </c>
       <c r="H74">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I74">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J74">
-        <v>0.7423</v>
+        <v>0.8327</v>
       </c>
       <c r="K74">
-        <v>0.7423</v>
+        <v>0.8327</v>
       </c>
       <c r="L74" t="s">
         <v>15</v>
@@ -3712,16 +3715,16 @@
         <v>74</v>
       </c>
       <c r="C75">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D75">
         <v>895</v>
       </c>
       <c r="E75">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F75">
-        <v>2290.22</v>
+        <v>2123.72</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -3844,16 +3847,16 @@
         <v>77</v>
       </c>
       <c r="C78">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="D78">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="E78">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F78">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -3888,31 +3891,31 @@
         <v>78</v>
       </c>
       <c r="C79">
-        <v>1560</v>
+        <v>1565</v>
       </c>
       <c r="D79">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="E79">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F79">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="I79">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="J79">
-        <v>1.0916</v>
+        <v>1.6654</v>
       </c>
       <c r="K79">
-        <v>1.0916</v>
+        <v>1.6654</v>
       </c>
       <c r="L79" t="s">
         <v>15</v>
@@ -3932,10 +3935,10 @@
         <v>79</v>
       </c>
       <c r="C80">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="D80">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E80">
         <v>54</v>
@@ -3947,16 +3950,16 @@
         <v>1</v>
       </c>
       <c r="H80">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I80">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J80">
-        <v>0.7423</v>
+        <v>1.3099</v>
       </c>
       <c r="K80">
-        <v>0.7423</v>
+        <v>1.3099</v>
       </c>
       <c r="L80" t="s">
         <v>15</v>
@@ -3976,31 +3979,31 @@
         <v>80</v>
       </c>
       <c r="C81">
-        <v>2040</v>
+        <v>2027</v>
       </c>
       <c r="D81">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="E81">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F81">
-        <v>1963.5</v>
+        <v>2642.08</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I81">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J81">
-        <v>1.0695</v>
+        <v>0</v>
       </c>
       <c r="K81">
-        <v>1.0695</v>
+        <v>0</v>
       </c>
       <c r="L81" t="s">
         <v>15</v>
@@ -4020,31 +4023,31 @@
         <v>81</v>
       </c>
       <c r="C82">
-        <v>2153</v>
+        <v>2140</v>
       </c>
       <c r="D82">
         <v>955</v>
       </c>
       <c r="E82">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F82">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G82">
         <v>1</v>
       </c>
       <c r="H82">
-        <v>193</v>
+        <v>291</v>
       </c>
       <c r="I82">
-        <v>193</v>
+        <v>291</v>
       </c>
       <c r="J82">
-        <v>8.427099999999999</v>
+        <v>10.292</v>
       </c>
       <c r="K82">
-        <v>8.427099999999999</v>
+        <v>10.292</v>
       </c>
       <c r="L82" t="s">
         <v>15</v>
@@ -4108,31 +4111,31 @@
         <v>83</v>
       </c>
       <c r="C84">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="D84">
         <v>958</v>
       </c>
       <c r="E84">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F84">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G84">
         <v>2</v>
       </c>
       <c r="H84">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I84">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J84">
-        <v>2.1395</v>
+        <v>1.3086</v>
       </c>
       <c r="K84">
-        <v>1.2663</v>
+        <v>0.7074</v>
       </c>
       <c r="L84" t="s">
         <v>15</v>
@@ -4152,31 +4155,31 @@
         <v>84</v>
       </c>
       <c r="C85">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D85">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="E85">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F85">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H85">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="I85">
         <v>22</v>
       </c>
       <c r="J85">
-        <v>2.9665</v>
+        <v>3.5804</v>
       </c>
       <c r="K85">
-        <v>1.0359</v>
+        <v>0.9606</v>
       </c>
       <c r="L85" t="s">
         <v>15</v>
@@ -4328,31 +4331,31 @@
         <v>88</v>
       </c>
       <c r="C89">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="D89">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="E89">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F89">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G89">
         <v>2</v>
       </c>
       <c r="H89">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I89">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J89">
-        <v>1.9212</v>
+        <v>1.7032</v>
       </c>
       <c r="K89">
-        <v>1.2226</v>
+        <v>0.9462</v>
       </c>
       <c r="L89" t="s">
         <v>15</v>
@@ -4372,16 +4375,16 @@
         <v>89</v>
       </c>
       <c r="C90">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="D90">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E90">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F90">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -4393,10 +4396,10 @@
         <v>27</v>
       </c>
       <c r="J90">
-        <v>1.1789</v>
+        <v>0.9549</v>
       </c>
       <c r="K90">
-        <v>1.1789</v>
+        <v>0.9549</v>
       </c>
       <c r="L90" t="s">
         <v>15</v>
@@ -4460,31 +4463,31 @@
         <v>91</v>
       </c>
       <c r="C92">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="D92">
         <v>959</v>
       </c>
       <c r="E92">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F92">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G92">
         <v>1</v>
       </c>
       <c r="H92">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I92">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J92">
-        <v>0.9606</v>
+        <v>0.7191</v>
       </c>
       <c r="K92">
-        <v>0.9606</v>
+        <v>0.7191</v>
       </c>
       <c r="L92" t="s">
         <v>15</v>
@@ -4504,10 +4507,10 @@
         <v>92</v>
       </c>
       <c r="C93">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="D93">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="E93">
         <v>54</v>
@@ -4592,31 +4595,31 @@
         <v>94</v>
       </c>
       <c r="C95">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="D95">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E95">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F95">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G95">
         <v>1</v>
       </c>
       <c r="H95">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I95">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J95">
-        <v>0.9606</v>
+        <v>0.7308</v>
       </c>
       <c r="K95">
-        <v>0.9606</v>
+        <v>0.7308</v>
       </c>
       <c r="L95" t="s">
         <v>15</v>
@@ -4680,31 +4683,31 @@
         <v>96</v>
       </c>
       <c r="C97">
-        <v>2043</v>
+        <v>2034</v>
       </c>
       <c r="D97">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E97">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F97">
-        <v>1963.5</v>
+        <v>2642.08</v>
       </c>
       <c r="G97">
         <v>2</v>
       </c>
       <c r="H97">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I97">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J97">
-        <v>2.6483</v>
+        <v>2.1952</v>
       </c>
       <c r="K97">
-        <v>1.6297</v>
+        <v>1.1733</v>
       </c>
       <c r="L97" t="s">
         <v>15</v>
@@ -4724,7 +4727,7 @@
         <v>97</v>
       </c>
       <c r="C98">
-        <v>2162</v>
+        <v>2152</v>
       </c>
       <c r="D98">
         <v>1020</v>
@@ -4739,16 +4742,16 @@
         <v>1</v>
       </c>
       <c r="H98">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="I98">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="J98">
-        <v>8.735799999999999</v>
+        <v>9.195600000000001</v>
       </c>
       <c r="K98">
-        <v>8.735799999999999</v>
+        <v>9.195600000000001</v>
       </c>
       <c r="L98" t="s">
         <v>15</v>
@@ -4768,31 +4771,31 @@
         <v>98</v>
       </c>
       <c r="C99">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="D99">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="E99">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F99">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G99">
         <v>1</v>
       </c>
       <c r="H99">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I99">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="J99">
-        <v>0.6986</v>
+        <v>1.2379</v>
       </c>
       <c r="K99">
-        <v>0.6986</v>
+        <v>1.2379</v>
       </c>
       <c r="L99" t="s">
         <v>15</v>
@@ -4812,31 +4815,31 @@
         <v>99</v>
       </c>
       <c r="C100">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D100">
         <v>1023</v>
       </c>
       <c r="E100">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F100">
-        <v>2290.22</v>
+        <v>2123.72</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I100">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J100">
-        <v>0</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K100">
-        <v>0</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="L100" t="s">
         <v>15</v>
@@ -4900,16 +4903,16 @@
         <v>101</v>
       </c>
       <c r="C102">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="D102">
         <v>1023</v>
       </c>
       <c r="E102">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F102">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -4944,31 +4947,31 @@
         <v>102</v>
       </c>
       <c r="C103">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="D103">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="E103">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F103">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G103">
         <v>1</v>
       </c>
       <c r="H103">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I103">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J103">
-        <v>0.7423</v>
+        <v>1.0962</v>
       </c>
       <c r="K103">
-        <v>0.7423</v>
+        <v>1.0962</v>
       </c>
       <c r="L103" t="s">
         <v>15</v>
@@ -5076,31 +5079,31 @@
         <v>105</v>
       </c>
       <c r="C106">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="D106">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="E106">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F106">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I106">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J106">
-        <v>0.7423</v>
+        <v>0</v>
       </c>
       <c r="K106">
-        <v>0.7423</v>
+        <v>0</v>
       </c>
       <c r="L106" t="s">
         <v>15</v>
@@ -5211,28 +5214,28 @@
         <v>1288</v>
       </c>
       <c r="D109">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E109">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F109">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G109">
         <v>2</v>
       </c>
       <c r="H109">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I109">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J109">
-        <v>1.5208</v>
+        <v>2.0706</v>
       </c>
       <c r="K109">
-        <v>0.8488</v>
+        <v>1.2992</v>
       </c>
       <c r="L109" t="s">
         <v>15</v>
@@ -5384,31 +5387,31 @@
         <v>112</v>
       </c>
       <c r="C113">
-        <v>2045</v>
+        <v>2039</v>
       </c>
       <c r="D113">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E113">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F113">
-        <v>1963.5</v>
+        <v>2642.08</v>
       </c>
       <c r="G113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H113">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="I113">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="J113">
-        <v>1.3751</v>
+        <v>2.9901</v>
       </c>
       <c r="K113">
-        <v>1.3751</v>
+        <v>2.1195</v>
       </c>
       <c r="L113" t="s">
         <v>15</v>
@@ -5428,31 +5431,31 @@
         <v>113</v>
       </c>
       <c r="C114">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="D114">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E114">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F114">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I114">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J114">
-        <v>0</v>
+        <v>1.3804</v>
       </c>
       <c r="K114">
-        <v>0</v>
+        <v>1.3804</v>
       </c>
       <c r="L114" t="s">
         <v>15</v>
@@ -5472,16 +5475,16 @@
         <v>114</v>
       </c>
       <c r="C115">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="D115">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="E115">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F115">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -5516,7 +5519,7 @@
         <v>115</v>
       </c>
       <c r="C116">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="D116">
         <v>1088</v>
@@ -5528,19 +5531,19 @@
         <v>2290.22</v>
       </c>
       <c r="G116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H116">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="I116">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J116">
-        <v>1.5282</v>
+        <v>2.9255</v>
       </c>
       <c r="K116">
-        <v>0.786</v>
+        <v>1.3972</v>
       </c>
       <c r="L116" t="s">
         <v>15</v>
@@ -5604,16 +5607,16 @@
         <v>117</v>
       </c>
       <c r="C118">
-        <v>1099</v>
+        <v>1086</v>
       </c>
       <c r="D118">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="E118">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F118">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -5648,31 +5651,31 @@
         <v>118</v>
       </c>
       <c r="C119">
-        <v>1754</v>
+        <v>1758</v>
       </c>
       <c r="D119">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E119">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F119">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H119">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="I119">
         <v>33</v>
       </c>
       <c r="J119">
-        <v>1.3398</v>
+        <v>1.8924</v>
       </c>
       <c r="K119">
-        <v>1.3398</v>
+        <v>1.249</v>
       </c>
       <c r="L119" t="s">
         <v>15</v>
@@ -5736,31 +5739,31 @@
         <v>120</v>
       </c>
       <c r="C121">
-        <v>1941</v>
+        <v>1947</v>
       </c>
       <c r="D121">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="E121">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F121">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G121">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H121">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I121">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J121">
-        <v>2.3579</v>
+        <v>2.5578</v>
       </c>
       <c r="K121">
-        <v>1.3972</v>
+        <v>0.9744</v>
       </c>
       <c r="L121" t="s">
         <v>15</v>
@@ -5824,31 +5827,31 @@
         <v>122</v>
       </c>
       <c r="C123">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="D123">
         <v>1090</v>
       </c>
       <c r="E123">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F123">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G123">
         <v>1</v>
       </c>
       <c r="H123">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="I123">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="J123">
-        <v>3.4058</v>
+        <v>2.4404</v>
       </c>
       <c r="K123">
-        <v>3.4058</v>
+        <v>2.4404</v>
       </c>
       <c r="L123" t="s">
         <v>15</v>
@@ -6044,31 +6047,31 @@
         <v>127</v>
       </c>
       <c r="C128">
-        <v>2045</v>
+        <v>2042</v>
       </c>
       <c r="D128">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E128">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F128">
-        <v>1963.5</v>
+        <v>2642.08</v>
       </c>
       <c r="G128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H128">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="I128">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J128">
-        <v>1.9353</v>
+        <v>0.757</v>
       </c>
       <c r="K128">
-        <v>1.1205</v>
+        <v>0.757</v>
       </c>
       <c r="L128" t="s">
         <v>15</v>
@@ -6088,10 +6091,10 @@
         <v>128</v>
       </c>
       <c r="C129">
-        <v>2159</v>
+        <v>2149</v>
       </c>
       <c r="D129">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="E129">
         <v>60</v>
@@ -6100,19 +6103,19 @@
         <v>2827.43</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="I129">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="J129">
-        <v>0</v>
+        <v>3.9612</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>3.9612</v>
       </c>
       <c r="L129" t="s">
         <v>15</v>
@@ -6176,7 +6179,7 @@
         <v>130</v>
       </c>
       <c r="C131">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D131">
         <v>1154</v>
@@ -6188,19 +6191,19 @@
         <v>2290.22</v>
       </c>
       <c r="G131">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H131">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="I131">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J131">
-        <v>2.8382</v>
+        <v>2.5325</v>
       </c>
       <c r="K131">
-        <v>1.3536</v>
+        <v>1.4846</v>
       </c>
       <c r="L131" t="s">
         <v>15</v>
@@ -6264,7 +6267,7 @@
         <v>132</v>
       </c>
       <c r="C133">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="D133">
         <v>1154</v>
@@ -6276,16 +6279,16 @@
         <v>2290.22</v>
       </c>
       <c r="G133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H133">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I133">
         <v>22</v>
       </c>
       <c r="J133">
-        <v>0.9606</v>
+        <v>1.8775</v>
       </c>
       <c r="K133">
         <v>0.9606</v>
@@ -6355,28 +6358,28 @@
         <v>1100</v>
       </c>
       <c r="D135">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="E135">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F135">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H135">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I135">
         <v>18</v>
       </c>
       <c r="J135">
-        <v>0.7308</v>
+        <v>1.4846</v>
       </c>
       <c r="K135">
-        <v>0.7308</v>
+        <v>0.786</v>
       </c>
       <c r="L135" t="s">
         <v>15</v>
@@ -6396,31 +6399,31 @@
         <v>135</v>
       </c>
       <c r="C136">
-        <v>1758</v>
+        <v>1755</v>
       </c>
       <c r="D136">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="E136">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F136">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G136">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H136">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="I136">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="J136">
-        <v>3.2748</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="K136">
-        <v>1.7029</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="L136" t="s">
         <v>15</v>
@@ -6484,7 +6487,7 @@
         <v>137</v>
       </c>
       <c r="C138">
-        <v>1946</v>
+        <v>1943</v>
       </c>
       <c r="D138">
         <v>1154</v>
@@ -6499,16 +6502,16 @@
         <v>4</v>
       </c>
       <c r="H138">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="I138">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J138">
-        <v>3.7988</v>
+        <v>3.2311</v>
       </c>
       <c r="K138">
-        <v>1.4409</v>
+        <v>0.9169</v>
       </c>
       <c r="L138" t="s">
         <v>15</v>
@@ -6619,13 +6622,13 @@
         <v>1383</v>
       </c>
       <c r="D141">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="E141">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F141">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -6637,10 +6640,10 @@
         <v>19</v>
       </c>
       <c r="J141">
-        <v>0.672</v>
+        <v>0.7714</v>
       </c>
       <c r="K141">
-        <v>0.672</v>
+        <v>0.7714</v>
       </c>
       <c r="L141" t="s">
         <v>15</v>
@@ -6663,13 +6666,13 @@
         <v>1476</v>
       </c>
       <c r="D142">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="E142">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F142">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -6704,31 +6707,31 @@
         <v>142</v>
       </c>
       <c r="C143">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="D143">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="E143">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F143">
-        <v>2827.43</v>
+        <v>2642.08</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I143">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J143">
-        <v>0</v>
+        <v>0.6056</v>
       </c>
       <c r="K143">
-        <v>0</v>
+        <v>0.6056</v>
       </c>
       <c r="L143" t="s">
         <v>15</v>
@@ -6836,31 +6839,31 @@
         <v>145</v>
       </c>
       <c r="C146">
-        <v>1298</v>
+        <v>1289</v>
       </c>
       <c r="D146">
-        <v>1216</v>
+        <v>1174</v>
       </c>
       <c r="E146">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F146">
-        <v>1963.5</v>
+        <v>1520.53</v>
       </c>
       <c r="G146">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H146">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I146">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J146">
-        <v>3.3614</v>
+        <v>0</v>
       </c>
       <c r="K146">
-        <v>1.5788</v>
+        <v>0</v>
       </c>
       <c r="L146" t="s">
         <v>15</v>
@@ -6968,7 +6971,7 @@
         <v>148</v>
       </c>
       <c r="C149">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D149">
         <v>1221</v>
@@ -6983,16 +6986,16 @@
         <v>2</v>
       </c>
       <c r="H149">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I149">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J149">
-        <v>2.4015</v>
+        <v>2.0959</v>
       </c>
       <c r="K149">
-        <v>1.5719</v>
+        <v>1.3099</v>
       </c>
       <c r="L149" t="s">
         <v>15</v>
@@ -7056,16 +7059,16 @@
         <v>150</v>
       </c>
       <c r="C151">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="D151">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E151">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F151">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -7077,10 +7080,10 @@
         <v>26</v>
       </c>
       <c r="J151">
-        <v>1.1353</v>
+        <v>0.9841</v>
       </c>
       <c r="K151">
-        <v>1.1353</v>
+        <v>0.9841</v>
       </c>
       <c r="L151" t="s">
         <v>15</v>
@@ -7100,16 +7103,16 @@
         <v>151</v>
       </c>
       <c r="C152">
-        <v>1192</v>
+        <v>1182</v>
       </c>
       <c r="D152">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E152">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F152">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -7144,16 +7147,16 @@
         <v>152</v>
       </c>
       <c r="C153">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="D153">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="E153">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F153">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -7188,16 +7191,16 @@
         <v>153</v>
       </c>
       <c r="C154">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="D154">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E154">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F154">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -7209,10 +7212,10 @@
         <v>18</v>
       </c>
       <c r="J154">
-        <v>0.7308</v>
+        <v>0.6813</v>
       </c>
       <c r="K154">
-        <v>0.7308</v>
+        <v>0.6813</v>
       </c>
       <c r="L154" t="s">
         <v>15</v>
@@ -7320,31 +7323,31 @@
         <v>156</v>
       </c>
       <c r="C157">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="D157">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="E157">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F157">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I157">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J157">
-        <v>0</v>
+        <v>1.0916</v>
       </c>
       <c r="K157">
-        <v>0</v>
+        <v>1.0916</v>
       </c>
       <c r="L157" t="s">
         <v>15</v>
@@ -7364,16 +7367,16 @@
         <v>157</v>
       </c>
       <c r="C158">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="D158">
-        <v>1221</v>
+        <v>1213</v>
       </c>
       <c r="E158">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F158">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -7408,7 +7411,7 @@
         <v>158</v>
       </c>
       <c r="C159">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="D159">
         <v>1222</v>
@@ -7452,16 +7455,16 @@
         <v>159</v>
       </c>
       <c r="C160">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="D160">
         <v>1222</v>
       </c>
       <c r="E160">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F160">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -7473,10 +7476,10 @@
         <v>19</v>
       </c>
       <c r="J160">
-        <v>0.7714</v>
+        <v>0.7191</v>
       </c>
       <c r="K160">
-        <v>0.7714</v>
+        <v>0.7191</v>
       </c>
       <c r="L160" t="s">
         <v>15</v>
@@ -7499,28 +7502,28 @@
         <v>1669</v>
       </c>
       <c r="D161">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="E161">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F161">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G161">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H161">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="I161">
         <v>56</v>
       </c>
       <c r="J161">
-        <v>2.2736</v>
+        <v>2.6172</v>
       </c>
       <c r="K161">
-        <v>2.2736</v>
+        <v>1.9806</v>
       </c>
       <c r="L161" t="s">
         <v>15</v>
@@ -7540,31 +7543,31 @@
         <v>161</v>
       </c>
       <c r="C162">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="D162">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="E162">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F162">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H162">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="I162">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J162">
-        <v>0.6902</v>
+        <v>1.733</v>
       </c>
       <c r="K162">
-        <v>0.6902</v>
+        <v>1.061</v>
       </c>
       <c r="L162" t="s">
         <v>15</v>
@@ -7584,10 +7587,10 @@
         <v>162</v>
       </c>
       <c r="C163">
-        <v>1853</v>
+        <v>1849</v>
       </c>
       <c r="D163">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="E163">
         <v>60</v>
@@ -7628,31 +7631,31 @@
         <v>163</v>
       </c>
       <c r="C164">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="D164">
-        <v>1289</v>
+        <v>1296</v>
       </c>
       <c r="E164">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F164">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I164">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J164">
-        <v>0.7714</v>
+        <v>0</v>
       </c>
       <c r="K164">
-        <v>0.7714</v>
+        <v>0</v>
       </c>
       <c r="L164" t="s">
         <v>15</v>
@@ -7672,31 +7675,31 @@
         <v>164</v>
       </c>
       <c r="C165">
-        <v>906</v>
+        <v>894</v>
       </c>
       <c r="D165">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="E165">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F165">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G165">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H165">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I165">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J165">
-        <v>2.0085</v>
+        <v>0.7427</v>
       </c>
       <c r="K165">
-        <v>1.0916</v>
+        <v>0.7427</v>
       </c>
       <c r="L165" t="s">
         <v>15</v>
@@ -7804,16 +7807,16 @@
         <v>167</v>
       </c>
       <c r="C168">
-        <v>1192</v>
+        <v>1199</v>
       </c>
       <c r="D168">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="E168">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F168">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G168">
         <v>0</v>
@@ -7851,13 +7854,13 @@
         <v>1480</v>
       </c>
       <c r="D169">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="E169">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F169">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G169">
         <v>0</v>
@@ -7892,10 +7895,10 @@
         <v>169</v>
       </c>
       <c r="C170">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="D170">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="E170">
         <v>56</v>
@@ -7907,16 +7910,16 @@
         <v>1</v>
       </c>
       <c r="H170">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I170">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J170">
-        <v>2.9639</v>
+        <v>3.0451</v>
       </c>
       <c r="K170">
-        <v>2.9639</v>
+        <v>3.0451</v>
       </c>
       <c r="L170" t="s">
         <v>15</v>
@@ -7936,16 +7939,16 @@
         <v>170</v>
       </c>
       <c r="C171">
-        <v>1766</v>
+        <v>1763</v>
       </c>
       <c r="D171">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="E171">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F171">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G171">
         <v>1</v>
@@ -7957,10 +7960,10 @@
         <v>56</v>
       </c>
       <c r="J171">
-        <v>2.4452</v>
+        <v>2.1195</v>
       </c>
       <c r="K171">
-        <v>2.4452</v>
+        <v>2.1195</v>
       </c>
       <c r="L171" t="s">
         <v>15</v>
@@ -8024,16 +8027,16 @@
         <v>172</v>
       </c>
       <c r="C173">
-        <v>2053</v>
+        <v>2049</v>
       </c>
       <c r="D173">
-        <v>1289</v>
+        <v>1280</v>
       </c>
       <c r="E173">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F173">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G173">
         <v>1</v>
@@ -8045,10 +8048,10 @@
         <v>22</v>
       </c>
       <c r="J173">
-        <v>0.8327</v>
+        <v>0.7781</v>
       </c>
       <c r="K173">
-        <v>0.8327</v>
+        <v>0.7781</v>
       </c>
       <c r="L173" t="s">
         <v>15</v>
@@ -8068,31 +8071,31 @@
         <v>173</v>
       </c>
       <c r="C174">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="D174">
-        <v>1289</v>
+        <v>1282</v>
       </c>
       <c r="E174">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F174">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H174">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="I174">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J174">
-        <v>1.7864</v>
+        <v>0.9196</v>
       </c>
       <c r="K174">
-        <v>1.015</v>
+        <v>0.9196</v>
       </c>
       <c r="L174" t="s">
         <v>15</v>
@@ -8112,16 +8115,16 @@
         <v>174</v>
       </c>
       <c r="C175">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="D175">
         <v>1290</v>
       </c>
       <c r="E175">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F175">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G175">
         <v>0</v>
@@ -8159,28 +8162,28 @@
         <v>1575</v>
       </c>
       <c r="D176">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="E176">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F176">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G176">
         <v>2</v>
       </c>
       <c r="H176">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I176">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J176">
-        <v>1.7032</v>
+        <v>1.3793</v>
       </c>
       <c r="K176">
-        <v>0.9841</v>
+        <v>0.7074</v>
       </c>
       <c r="L176" t="s">
         <v>15</v>
@@ -8200,10 +8203,10 @@
         <v>176</v>
       </c>
       <c r="C177">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="D177">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="E177">
         <v>60</v>
@@ -8464,31 +8467,31 @@
         <v>182</v>
       </c>
       <c r="C183">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D183">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="E183">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F183">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G183">
         <v>1</v>
       </c>
       <c r="H183">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I183">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J183">
-        <v>0.8120000000000001</v>
+        <v>1.2663</v>
       </c>
       <c r="K183">
-        <v>0.8120000000000001</v>
+        <v>1.2663</v>
       </c>
       <c r="L183" t="s">
         <v>15</v>
@@ -8508,31 +8511,31 @@
         <v>183</v>
       </c>
       <c r="C184">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="D184">
-        <v>1358</v>
+        <v>1351</v>
       </c>
       <c r="E184">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F184">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I184">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J184">
-        <v>0</v>
+        <v>0.7074</v>
       </c>
       <c r="K184">
-        <v>0</v>
+        <v>0.7074</v>
       </c>
       <c r="L184" t="s">
         <v>15</v>
@@ -8640,7 +8643,7 @@
         <v>186</v>
       </c>
       <c r="C187">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="D187">
         <v>1358</v>
@@ -8652,16 +8655,16 @@
         <v>2463.01</v>
       </c>
       <c r="G187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H187">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I187">
         <v>21</v>
       </c>
       <c r="J187">
-        <v>0.8526</v>
+        <v>1.624</v>
       </c>
       <c r="K187">
         <v>0.8526</v>
@@ -8684,31 +8687,31 @@
         <v>187</v>
       </c>
       <c r="C188">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="D188">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="E188">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F188">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G188">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H188">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="I188">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J188">
-        <v>0.7308</v>
+        <v>1.9303</v>
       </c>
       <c r="K188">
-        <v>0.7308</v>
+        <v>1.249</v>
       </c>
       <c r="L188" t="s">
         <v>15</v>
@@ -8816,31 +8819,31 @@
         <v>190</v>
       </c>
       <c r="C191">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="D191">
         <v>1358</v>
       </c>
       <c r="E191">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F191">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G191">
         <v>1</v>
       </c>
       <c r="H191">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I191">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J191">
-        <v>0.8932</v>
+        <v>1.0479</v>
       </c>
       <c r="K191">
-        <v>0.8932</v>
+        <v>1.0479</v>
       </c>
       <c r="L191" t="s">
         <v>15</v>
@@ -8904,31 +8907,31 @@
         <v>192</v>
       </c>
       <c r="C193">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="D193">
         <v>1359</v>
       </c>
       <c r="E193">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F193">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G193">
         <v>1</v>
       </c>
       <c r="H193">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I193">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J193">
-        <v>0.9606</v>
+        <v>1.0962</v>
       </c>
       <c r="K193">
-        <v>0.9606</v>
+        <v>1.0962</v>
       </c>
       <c r="L193" t="s">
         <v>15</v>
@@ -9168,31 +9171,31 @@
         <v>198</v>
       </c>
       <c r="C199">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D199">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="E199">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F199">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G199">
         <v>2</v>
       </c>
       <c r="H199">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="I199">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="J199">
-        <v>3.1438</v>
+        <v>1.1671</v>
       </c>
       <c r="K199">
-        <v>2.4452</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="L199" t="s">
         <v>15</v>
@@ -9300,10 +9303,10 @@
         <v>201</v>
       </c>
       <c r="C202">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="D202">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="E202">
         <v>56</v>
@@ -9315,16 +9318,16 @@
         <v>2</v>
       </c>
       <c r="H202">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I202">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J202">
-        <v>1.7052</v>
+        <v>1.827</v>
       </c>
       <c r="K202">
-        <v>0.8526</v>
+        <v>0.9744</v>
       </c>
       <c r="L202" t="s">
         <v>15</v>
@@ -9608,10 +9611,10 @@
         <v>208</v>
       </c>
       <c r="C209">
-        <v>1771</v>
+        <v>1766</v>
       </c>
       <c r="D209">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="E209">
         <v>58</v>
@@ -9652,16 +9655,16 @@
         <v>209</v>
       </c>
       <c r="C210">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="D210">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="E210">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F210">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G210">
         <v>2</v>
@@ -9673,10 +9676,10 @@
         <v>27</v>
       </c>
       <c r="J210">
-        <v>1.8924</v>
+        <v>2.03</v>
       </c>
       <c r="K210">
-        <v>1.0219</v>
+        <v>1.0962</v>
       </c>
       <c r="L210" t="s">
         <v>15</v>
@@ -9828,7 +9831,7 @@
         <v>213</v>
       </c>
       <c r="C214">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D214">
         <v>1499</v>
@@ -9843,16 +9846,16 @@
         <v>2</v>
       </c>
       <c r="H214">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I214">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J214">
-        <v>1.3804</v>
+        <v>1.7864</v>
       </c>
       <c r="K214">
-        <v>0.6902</v>
+        <v>0.9744</v>
       </c>
       <c r="L214" t="s">
         <v>15</v>
@@ -9872,31 +9875,31 @@
         <v>214</v>
       </c>
       <c r="C215">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="D215">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="E215">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F215">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G215">
         <v>2</v>
       </c>
       <c r="H215">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="I215">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J215">
-        <v>2.233</v>
+        <v>1.4004</v>
       </c>
       <c r="K215">
-        <v>1.5834</v>
+        <v>0.7191</v>
       </c>
       <c r="L215" t="s">
         <v>15</v>
@@ -9916,31 +9919,31 @@
         <v>215</v>
       </c>
       <c r="C216">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D216">
-        <v>1499</v>
+        <v>1492</v>
       </c>
       <c r="E216">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F216">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G216">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H216">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="I216">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J216">
-        <v>2.5737</v>
+        <v>1.1318</v>
       </c>
       <c r="K216">
-        <v>1.3626</v>
+        <v>1.1318</v>
       </c>
       <c r="L216" t="s">
         <v>15</v>
@@ -9963,28 +9966,28 @@
         <v>1289</v>
       </c>
       <c r="D217">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="E217">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F217">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G217">
         <v>2</v>
       </c>
       <c r="H217">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="I217">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="J217">
-        <v>2.4766</v>
+        <v>2.4757</v>
       </c>
       <c r="K217">
-        <v>1.3398</v>
+        <v>1.6269</v>
       </c>
       <c r="L217" t="s">
         <v>15</v>
@@ -10007,28 +10010,28 @@
         <v>1484</v>
       </c>
       <c r="D218">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="E218">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F218">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I218">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J218">
-        <v>0</v>
+        <v>1.3793</v>
       </c>
       <c r="K218">
-        <v>0</v>
+        <v>1.3793</v>
       </c>
       <c r="L218" t="s">
         <v>15</v>
@@ -10051,28 +10054,28 @@
         <v>1582</v>
       </c>
       <c r="D219">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="E219">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F219">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H219">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I219">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J219">
-        <v>0.7714</v>
+        <v>0</v>
       </c>
       <c r="K219">
-        <v>0.7714</v>
+        <v>0</v>
       </c>
       <c r="L219" t="s">
         <v>15</v>
@@ -10095,28 +10098,28 @@
         <v>1680</v>
       </c>
       <c r="D220">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="E220">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F220">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G220">
         <v>1</v>
       </c>
       <c r="H220">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I220">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J220">
-        <v>1.5022</v>
+        <v>1.0964</v>
       </c>
       <c r="K220">
-        <v>1.5022</v>
+        <v>1.0964</v>
       </c>
       <c r="L220" t="s">
         <v>15</v>
@@ -10136,10 +10139,10 @@
         <v>220</v>
       </c>
       <c r="C221">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="D221">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="E221">
         <v>56</v>
@@ -10151,16 +10154,16 @@
         <v>2</v>
       </c>
       <c r="H221">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I221">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J221">
-        <v>1.9082</v>
+        <v>1.7458</v>
       </c>
       <c r="K221">
-        <v>0.9744</v>
+        <v>1.0962</v>
       </c>
       <c r="L221" t="s">
         <v>15</v>
@@ -10180,10 +10183,10 @@
         <v>221</v>
       </c>
       <c r="C222">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="D222">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="E222">
         <v>58</v>
@@ -10192,19 +10195,19 @@
         <v>2642.08</v>
       </c>
       <c r="G222">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H222">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I222">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J222">
-        <v>0</v>
+        <v>2.763</v>
       </c>
       <c r="K222">
-        <v>0</v>
+        <v>1.7032</v>
       </c>
       <c r="L222" t="s">
         <v>15</v>
@@ -10312,10 +10315,10 @@
         <v>224</v>
       </c>
       <c r="C225">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="D225">
-        <v>1500</v>
+        <v>1494</v>
       </c>
       <c r="E225">
         <v>60</v>
@@ -10324,19 +10327,19 @@
         <v>2827.43</v>
       </c>
       <c r="G225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H225">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="I225">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J225">
-        <v>2.4757</v>
+        <v>3.5368</v>
       </c>
       <c r="K225">
-        <v>1.6977</v>
+        <v>1.7684</v>
       </c>
       <c r="L225" t="s">
         <v>15</v>
@@ -10400,10 +10403,10 @@
         <v>226</v>
       </c>
       <c r="C227">
-        <v>2177</v>
+        <v>2171</v>
       </c>
       <c r="D227">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="E227">
         <v>60</v>
@@ -10412,19 +10415,19 @@
         <v>2827.43</v>
       </c>
       <c r="G227">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H227">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="I227">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="J227">
-        <v>7.6041</v>
+        <v>6.7552</v>
       </c>
       <c r="K227">
-        <v>3.6075</v>
+        <v>3.8551</v>
       </c>
       <c r="L227" t="s">
         <v>15</v>
@@ -10444,31 +10447,31 @@
         <v>227</v>
       </c>
       <c r="C228">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D228">
-        <v>1571</v>
+        <v>1574</v>
       </c>
       <c r="E228">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F228">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G228">
         <v>2</v>
       </c>
       <c r="H228">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I228">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J228">
-        <v>3.1669</v>
+        <v>3.0658</v>
       </c>
       <c r="K228">
-        <v>1.6646</v>
+        <v>1.7032</v>
       </c>
       <c r="L228" t="s">
         <v>15</v>
@@ -10535,13 +10538,13 @@
         <v>895</v>
       </c>
       <c r="D230">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="E230">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F230">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G230">
         <v>2</v>
@@ -10553,10 +10556,10 @@
         <v>40</v>
       </c>
       <c r="J230">
-        <v>2.1574</v>
+        <v>2.016</v>
       </c>
       <c r="K230">
-        <v>1.514</v>
+        <v>1.4147</v>
       </c>
       <c r="L230" t="s">
         <v>15</v>
@@ -10576,16 +10579,16 @@
         <v>230</v>
       </c>
       <c r="C231">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D231">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="E231">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F231">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G231">
         <v>2</v>
@@ -10597,10 +10600,10 @@
         <v>45</v>
       </c>
       <c r="J231">
-        <v>2.6873</v>
+        <v>2.5111</v>
       </c>
       <c r="K231">
-        <v>1.7032</v>
+        <v>1.5915</v>
       </c>
       <c r="L231" t="s">
         <v>15</v>
@@ -10752,31 +10755,31 @@
         <v>234</v>
       </c>
       <c r="C235">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="D235">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="E235">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F235">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G235">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H235">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="I235">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J235">
-        <v>2.1112</v>
+        <v>1.061</v>
       </c>
       <c r="K235">
-        <v>1.2586</v>
+        <v>1.061</v>
       </c>
       <c r="L235" t="s">
         <v>15</v>
@@ -10840,10 +10843,10 @@
         <v>236</v>
       </c>
       <c r="C237">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="D237">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="E237">
         <v>56</v>
@@ -10855,16 +10858,16 @@
         <v>1</v>
       </c>
       <c r="H237">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I237">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J237">
-        <v>0.7714</v>
+        <v>0.7308</v>
       </c>
       <c r="K237">
-        <v>0.7714</v>
+        <v>0.7308</v>
       </c>
       <c r="L237" t="s">
         <v>15</v>
@@ -11019,28 +11022,28 @@
         <v>2076</v>
       </c>
       <c r="D241">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="E241">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F241">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G241">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H241">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="I241">
         <v>47</v>
       </c>
       <c r="J241">
-        <v>4.0877</v>
+        <v>3.1263</v>
       </c>
       <c r="K241">
-        <v>1.7789</v>
+        <v>1.9082</v>
       </c>
       <c r="L241" t="s">
         <v>15</v>
@@ -11104,31 +11107,31 @@
         <v>242</v>
       </c>
       <c r="C243">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="D243">
-        <v>1644</v>
+        <v>1648</v>
       </c>
       <c r="E243">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F243">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G243">
         <v>2</v>
       </c>
       <c r="H243">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="I243">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="J243">
-        <v>3.1036</v>
+        <v>2.4757</v>
       </c>
       <c r="K243">
-        <v>2.006</v>
+        <v>1.4501</v>
       </c>
       <c r="L243" t="s">
         <v>15</v>
@@ -11192,31 +11195,31 @@
         <v>244</v>
       </c>
       <c r="C245">
-        <v>2077</v>
+        <v>2086</v>
       </c>
       <c r="D245">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="E245">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F245">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G245">
         <v>2</v>
       </c>
       <c r="H245">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I245">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J245">
-        <v>2.3548</v>
+        <v>2.3088</v>
       </c>
       <c r="K245">
-        <v>1.2586</v>
+        <v>1.2112</v>
       </c>
       <c r="L245" t="s">
         <v>15</v>
@@ -11500,10 +11503,10 @@
         <v>251</v>
       </c>
       <c r="C252">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="D252">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="E252">
         <v>60</v>
@@ -11720,37 +11723,37 @@
         <v>256</v>
       </c>
       <c r="C257">
-        <v>1847</v>
+        <v>1880</v>
       </c>
       <c r="D257">
-        <v>1650</v>
+        <v>1645</v>
       </c>
       <c r="E257">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F257">
-        <v>2290.22</v>
+        <v>1809.56</v>
       </c>
       <c r="G257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I257">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J257">
-        <v>0</v>
+        <v>1.1605</v>
       </c>
       <c r="K257">
-        <v>0</v>
+        <v>1.1605</v>
       </c>
       <c r="L257" t="s">
         <v>15</v>
       </c>
       <c r="M257" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N257">
         <v>0.2</v>
@@ -11785,40 +11788,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -11829,10 +11832,10 @@
         <v>256</v>
       </c>
       <c r="C2">
-        <v>1.3952</v>
+        <v>1.5254</v>
       </c>
       <c r="D2">
-        <v>10.0678</v>
+        <v>12.1874</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -11841,7 +11844,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2">
         <v>25</v>
@@ -11850,16 +11853,16 @@
         <v>12</v>
       </c>
       <c r="J2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Images_BGA/Results/Reports/PCBA1_08_inspection_report.xlsx
+++ b/Images_BGA/Results/Reports/PCBA1_08_inspection_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="28">
   <si>
     <t>image_name</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>PASS</t>
-  </si>
-  <si>
-    <t>FAIL</t>
   </si>
   <si>
     <t>total_balls</t>
@@ -433,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N257"/>
+  <dimension ref="A1:N258"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -503,16 +500,16 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2159</v>
+        <v>1105</v>
       </c>
       <c r="D2">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="E2">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F2">
-        <v>1809.56</v>
+        <v>2123.72</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -547,16 +544,16 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1105</v>
+        <v>1821</v>
       </c>
       <c r="D3">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="E3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F3">
-        <v>2123.72</v>
+        <v>2827.43</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -591,10 +588,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>1821</v>
+        <v>812</v>
       </c>
       <c r="D4">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E4">
         <v>60</v>
@@ -635,31 +632,31 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="D5">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="E5">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F5">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="I5">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="J5">
-        <v>10.0678</v>
+        <v>9.866</v>
       </c>
       <c r="K5">
-        <v>10.0678</v>
+        <v>9.866</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -679,31 +676,31 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>750</v>
+        <v>2006</v>
       </c>
       <c r="D6">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="E6">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F6">
-        <v>2123.72</v>
+        <v>2463.01</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="I6">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J6">
-        <v>3.8141</v>
+        <v>1.9082</v>
       </c>
       <c r="K6">
-        <v>1.6481</v>
+        <v>1.1368</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -723,31 +720,31 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>1017</v>
+        <v>2092</v>
       </c>
       <c r="D7">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="E7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F7">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>1.7893</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>1.7893</v>
+        <v>0</v>
       </c>
       <c r="L7" t="s">
         <v>15</v>
@@ -767,31 +764,31 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>1195</v>
+        <v>1017</v>
       </c>
       <c r="D8">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="E8">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F8">
-        <v>2463.01</v>
+        <v>2123.72</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I8">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J8">
-        <v>1.7052</v>
+        <v>1.7893</v>
       </c>
       <c r="K8">
-        <v>1.7052</v>
+        <v>1.7893</v>
       </c>
       <c r="L8" t="s">
         <v>15</v>
@@ -811,31 +808,31 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>1284</v>
+        <v>1195</v>
       </c>
       <c r="D9">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F9">
-        <v>1963.5</v>
+        <v>2463.01</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I9">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="J9">
-        <v>1.1714</v>
+        <v>1.7052</v>
       </c>
       <c r="K9">
-        <v>1.1714</v>
+        <v>1.7052</v>
       </c>
       <c r="L9" t="s">
         <v>15</v>
@@ -855,7 +852,7 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>1372</v>
+        <v>1284</v>
       </c>
       <c r="D10">
         <v>650</v>
@@ -870,16 +867,16 @@
         <v>1</v>
       </c>
       <c r="H10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J10">
-        <v>1.0186</v>
+        <v>1.1714</v>
       </c>
       <c r="K10">
-        <v>1.0186</v>
+        <v>1.1714</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -899,31 +896,31 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>1453</v>
+        <v>1372</v>
       </c>
       <c r="D11">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="E11">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F11">
-        <v>2642.08</v>
+        <v>1963.5</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1.0186</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1.0186</v>
       </c>
       <c r="L11" t="s">
         <v>15</v>
@@ -943,31 +940,31 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>1551</v>
+        <v>1453</v>
       </c>
       <c r="D12">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="E12">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F12">
-        <v>2123.72</v>
+        <v>2642.08</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>2.4485</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>1.3184</v>
+        <v>0</v>
       </c>
       <c r="L12" t="s">
         <v>15</v>
@@ -987,7 +984,7 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>1640</v>
+        <v>1551</v>
       </c>
       <c r="D13">
         <v>650</v>
@@ -1002,16 +999,16 @@
         <v>2</v>
       </c>
       <c r="H13">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I13">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J13">
-        <v>2.4015</v>
+        <v>2.4485</v>
       </c>
       <c r="K13">
-        <v>1.5539</v>
+        <v>1.3184</v>
       </c>
       <c r="L13" t="s">
         <v>15</v>
@@ -1031,31 +1028,31 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>1730</v>
+        <v>1640</v>
       </c>
       <c r="D14">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F14">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I14">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J14">
-        <v>1.9863</v>
+        <v>2.4015</v>
       </c>
       <c r="K14">
-        <v>1.9863</v>
+        <v>1.5539</v>
       </c>
       <c r="L14" t="s">
         <v>15</v>
@@ -1075,31 +1072,31 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>1908</v>
+        <v>1730</v>
       </c>
       <c r="D15">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E15">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F15">
-        <v>2290.22</v>
+        <v>1963.5</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1.9863</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1.9863</v>
       </c>
       <c r="L15" t="s">
         <v>15</v>
@@ -1119,16 +1116,16 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>2089</v>
+        <v>1908</v>
       </c>
       <c r="D16">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E16">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F16">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1163,31 +1160,31 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>818</v>
+        <v>742</v>
       </c>
       <c r="D17">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="E17">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="F17">
-        <v>2827.43</v>
+        <v>1520.53</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17">
-        <v>226</v>
+        <v>51</v>
       </c>
       <c r="I17">
-        <v>226</v>
+        <v>51</v>
       </c>
       <c r="J17">
-        <v>7.9931</v>
+        <v>3.3541</v>
       </c>
       <c r="K17">
-        <v>7.9931</v>
+        <v>3.3541</v>
       </c>
       <c r="L17" t="s">
         <v>15</v>
@@ -1207,10 +1204,10 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D18">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E18">
         <v>60</v>
@@ -1251,31 +1248,31 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>2087</v>
+        <v>913</v>
       </c>
       <c r="D19">
         <v>706</v>
       </c>
       <c r="E19">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F19">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I19">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J19">
-        <v>1.4004</v>
+        <v>1.6269</v>
       </c>
       <c r="K19">
-        <v>1.4004</v>
+        <v>0.9196</v>
       </c>
       <c r="L19" t="s">
         <v>15</v>
@@ -1295,31 +1292,31 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>747</v>
+        <v>2111</v>
       </c>
       <c r="D20">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="E20">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F20">
-        <v>2123.72</v>
+        <v>2827.43</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="I20">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="J20">
-        <v>3.6728</v>
+        <v>8.9834</v>
       </c>
       <c r="K20">
-        <v>3.6728</v>
+        <v>7.7809</v>
       </c>
       <c r="L20" t="s">
         <v>15</v>
@@ -1339,31 +1336,31 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>1008</v>
+        <v>2007</v>
       </c>
       <c r="D21">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="E21">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F21">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>1.0962</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>1.0962</v>
+        <v>0</v>
       </c>
       <c r="L21" t="s">
         <v>15</v>
@@ -1383,31 +1380,31 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>1187</v>
+        <v>747</v>
       </c>
       <c r="D22">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="E22">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F22">
-        <v>2290.22</v>
+        <v>2123.72</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>3.6728</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>3.6728</v>
       </c>
       <c r="L22" t="s">
         <v>15</v>
@@ -1427,31 +1424,31 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>1374</v>
+        <v>1008</v>
       </c>
       <c r="D23">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="E23">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F23">
-        <v>2123.72</v>
+        <v>2463.01</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1.0962</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1.0962</v>
       </c>
       <c r="L23" t="s">
         <v>15</v>
@@ -1471,31 +1468,31 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>1464</v>
+        <v>1187</v>
       </c>
       <c r="D24">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="E24">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F24">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>0.8005</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>0.8005</v>
+        <v>0</v>
       </c>
       <c r="L24" t="s">
         <v>15</v>
@@ -1515,31 +1512,31 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>1555</v>
+        <v>1374</v>
       </c>
       <c r="D25">
         <v>710</v>
       </c>
       <c r="E25">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F25">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>1.5279</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>1.5279</v>
+        <v>0</v>
       </c>
       <c r="L25" t="s">
         <v>15</v>
@@ -1559,7 +1556,7 @@
         <v>25</v>
       </c>
       <c r="C26">
-        <v>1733</v>
+        <v>1464</v>
       </c>
       <c r="D26">
         <v>710</v>
@@ -1574,16 +1571,16 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I26">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J26">
-        <v>1.0359</v>
+        <v>0.8005</v>
       </c>
       <c r="K26">
-        <v>1.0359</v>
+        <v>0.8005</v>
       </c>
       <c r="L26" t="s">
         <v>15</v>
@@ -1603,31 +1600,31 @@
         <v>26</v>
       </c>
       <c r="C27">
-        <v>1822</v>
+        <v>1555</v>
       </c>
       <c r="D27">
         <v>710</v>
       </c>
       <c r="E27">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F27">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I27">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J27">
-        <v>0.8005</v>
+        <v>1.5279</v>
       </c>
       <c r="K27">
-        <v>0.8005</v>
+        <v>1.5279</v>
       </c>
       <c r="L27" t="s">
         <v>15</v>
@@ -1647,31 +1644,31 @@
         <v>27</v>
       </c>
       <c r="C28">
-        <v>1919</v>
+        <v>1733</v>
       </c>
       <c r="D28">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="E28">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F28">
-        <v>2290.22</v>
+        <v>2123.72</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I28">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J28">
-        <v>0.786</v>
+        <v>1.0359</v>
       </c>
       <c r="K28">
-        <v>0.786</v>
+        <v>1.0359</v>
       </c>
       <c r="L28" t="s">
         <v>15</v>
@@ -1691,31 +1688,31 @@
         <v>28</v>
       </c>
       <c r="C29">
-        <v>2152</v>
+        <v>1822</v>
       </c>
       <c r="D29">
-        <v>694</v>
+        <v>710</v>
       </c>
       <c r="E29">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F29">
-        <v>2642.08</v>
+        <v>2123.72</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>0.8005</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>0.8005</v>
       </c>
       <c r="L29" t="s">
         <v>15</v>
@@ -1735,31 +1732,31 @@
         <v>29</v>
       </c>
       <c r="C30">
-        <v>915</v>
+        <v>1919</v>
       </c>
       <c r="D30">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E30">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F30">
-        <v>2642.08</v>
+        <v>2290.22</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I30">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J30">
-        <v>1.9681</v>
+        <v>0.786</v>
       </c>
       <c r="K30">
-        <v>0.9841</v>
+        <v>0.786</v>
       </c>
       <c r="L30" t="s">
         <v>15</v>
@@ -1911,16 +1908,16 @@
         <v>33</v>
       </c>
       <c r="C34">
-        <v>2092</v>
+        <v>741</v>
       </c>
       <c r="D34">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="E34">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F34">
-        <v>2642.08</v>
+        <v>2290.22</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -1955,31 +1952,31 @@
         <v>34</v>
       </c>
       <c r="C35">
-        <v>741</v>
+        <v>833</v>
       </c>
       <c r="D35">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="E35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F35">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>0.6056</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>0.6056</v>
       </c>
       <c r="L35" t="s">
         <v>15</v>
@@ -1999,31 +1996,31 @@
         <v>35</v>
       </c>
       <c r="C36">
-        <v>833</v>
+        <v>912</v>
       </c>
       <c r="D36">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="E36">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F36">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>0.6056</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>0.6056</v>
+        <v>0</v>
       </c>
       <c r="L36" t="s">
         <v>15</v>
@@ -2043,16 +2040,16 @@
         <v>36</v>
       </c>
       <c r="C37">
-        <v>912</v>
+        <v>1010</v>
       </c>
       <c r="D37">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E37">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F37">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -2087,31 +2084,31 @@
         <v>37</v>
       </c>
       <c r="C38">
-        <v>1010</v>
+        <v>1100</v>
       </c>
       <c r="D38">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E38">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F38">
-        <v>2290.22</v>
+        <v>2123.72</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>0.8476</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>0.8476</v>
       </c>
       <c r="L38" t="s">
         <v>15</v>
@@ -2131,10 +2128,10 @@
         <v>38</v>
       </c>
       <c r="C39">
-        <v>1100</v>
+        <v>1195</v>
       </c>
       <c r="D39">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E39">
         <v>52</v>
@@ -2143,19 +2140,19 @@
         <v>2123.72</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>0.8476</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>0.8476</v>
+        <v>0</v>
       </c>
       <c r="L39" t="s">
         <v>15</v>
@@ -2175,7 +2172,7 @@
         <v>39</v>
       </c>
       <c r="C40">
-        <v>1195</v>
+        <v>1372</v>
       </c>
       <c r="D40">
         <v>771</v>
@@ -2187,19 +2184,19 @@
         <v>2123.72</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>0.9417</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>0.9417</v>
       </c>
       <c r="L40" t="s">
         <v>15</v>
@@ -2219,7 +2216,7 @@
         <v>40</v>
       </c>
       <c r="C41">
-        <v>1372</v>
+        <v>1465</v>
       </c>
       <c r="D41">
         <v>771</v>
@@ -2231,19 +2228,19 @@
         <v>2123.72</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>0.9417</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>0.9417</v>
+        <v>0</v>
       </c>
       <c r="L41" t="s">
         <v>15</v>
@@ -2263,7 +2260,7 @@
         <v>41</v>
       </c>
       <c r="C42">
-        <v>1465</v>
+        <v>1555</v>
       </c>
       <c r="D42">
         <v>771</v>
@@ -2275,19 +2272,19 @@
         <v>2123.72</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>0.8476</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>0.8476</v>
       </c>
       <c r="L42" t="s">
         <v>15</v>
@@ -2307,7 +2304,7 @@
         <v>42</v>
       </c>
       <c r="C43">
-        <v>1555</v>
+        <v>1646</v>
       </c>
       <c r="D43">
         <v>771</v>
@@ -2322,16 +2319,16 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I43">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J43">
-        <v>0.8476</v>
+        <v>0.7534</v>
       </c>
       <c r="K43">
-        <v>0.8476</v>
+        <v>0.7534</v>
       </c>
       <c r="L43" t="s">
         <v>15</v>
@@ -2351,7 +2348,7 @@
         <v>43</v>
       </c>
       <c r="C44">
-        <v>1646</v>
+        <v>1734</v>
       </c>
       <c r="D44">
         <v>771</v>
@@ -2366,16 +2363,16 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I44">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J44">
-        <v>0.7534</v>
+        <v>0.8476</v>
       </c>
       <c r="K44">
-        <v>0.7534</v>
+        <v>0.8476</v>
       </c>
       <c r="L44" t="s">
         <v>15</v>
@@ -2395,31 +2392,31 @@
         <v>44</v>
       </c>
       <c r="C45">
-        <v>1734</v>
+        <v>1834</v>
       </c>
       <c r="D45">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="E45">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F45">
-        <v>2123.72</v>
+        <v>2463.01</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I45">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J45">
-        <v>0.8476</v>
+        <v>0</v>
       </c>
       <c r="K45">
-        <v>0.8476</v>
+        <v>0</v>
       </c>
       <c r="L45" t="s">
         <v>15</v>
@@ -2439,31 +2436,31 @@
         <v>45</v>
       </c>
       <c r="C46">
-        <v>1834</v>
+        <v>1910</v>
       </c>
       <c r="D46">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E46">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F46">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>0.6986</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>0.6986</v>
       </c>
       <c r="L46" t="s">
         <v>15</v>
@@ -2483,31 +2480,31 @@
         <v>46</v>
       </c>
       <c r="C47">
-        <v>1910</v>
+        <v>2030</v>
       </c>
       <c r="D47">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="E47">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F47">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>0.6986</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>0.6986</v>
+        <v>0</v>
       </c>
       <c r="L47" t="s">
         <v>15</v>
@@ -2530,13 +2527,13 @@
         <v>1285</v>
       </c>
       <c r="D48">
-        <v>815</v>
+        <v>772</v>
       </c>
       <c r="E48">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F48">
-        <v>1520.53</v>
+        <v>2123.72</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -2571,31 +2568,31 @@
         <v>48</v>
       </c>
       <c r="C49">
-        <v>2148</v>
+        <v>2115</v>
       </c>
       <c r="D49">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="E49">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F49">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>9.160299999999999</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>9.160299999999999</v>
       </c>
       <c r="L49" t="s">
         <v>15</v>
@@ -2615,31 +2612,31 @@
         <v>49</v>
       </c>
       <c r="C50">
-        <v>2077</v>
+        <v>927</v>
       </c>
       <c r="D50">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="E50">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F50">
-        <v>1809.56</v>
+        <v>2290.22</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>2.0085</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>1.1789</v>
       </c>
       <c r="L50" t="s">
         <v>15</v>
@@ -2659,31 +2656,31 @@
         <v>50</v>
       </c>
       <c r="C51">
-        <v>927</v>
+        <v>734</v>
       </c>
       <c r="D51">
         <v>829</v>
       </c>
       <c r="E51">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F51">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G51">
         <v>2</v>
       </c>
       <c r="H51">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I51">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J51">
-        <v>2.0085</v>
+        <v>1.2025</v>
       </c>
       <c r="K51">
-        <v>1.1789</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="L51" t="s">
         <v>15</v>
@@ -2703,31 +2700,31 @@
         <v>51</v>
       </c>
       <c r="C52">
-        <v>734</v>
+        <v>829</v>
       </c>
       <c r="D52">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E52">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F52">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I52">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J52">
-        <v>1.2025</v>
+        <v>0</v>
       </c>
       <c r="K52">
-        <v>0.6366000000000001</v>
+        <v>0</v>
       </c>
       <c r="L52" t="s">
         <v>15</v>
@@ -2747,16 +2744,16 @@
         <v>52</v>
       </c>
       <c r="C53">
-        <v>829</v>
+        <v>1285</v>
       </c>
       <c r="D53">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="E53">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F53">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2791,16 +2788,16 @@
         <v>53</v>
       </c>
       <c r="C54">
-        <v>1285</v>
+        <v>1467</v>
       </c>
       <c r="D54">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E54">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F54">
-        <v>2290.22</v>
+        <v>2123.72</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -2835,7 +2832,7 @@
         <v>54</v>
       </c>
       <c r="C55">
-        <v>1467</v>
+        <v>1558</v>
       </c>
       <c r="D55">
         <v>833</v>
@@ -2847,19 +2844,19 @@
         <v>2123.72</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>3.3903</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>1.5068</v>
       </c>
       <c r="L55" t="s">
         <v>15</v>
@@ -2879,31 +2876,31 @@
         <v>55</v>
       </c>
       <c r="C56">
-        <v>1558</v>
+        <v>1013</v>
       </c>
       <c r="D56">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="E56">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F56">
-        <v>2123.72</v>
+        <v>2463.01</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="I56">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J56">
-        <v>3.3903</v>
+        <v>0.7714</v>
       </c>
       <c r="K56">
-        <v>1.5068</v>
+        <v>0.7714</v>
       </c>
       <c r="L56" t="s">
         <v>15</v>
@@ -2923,31 +2920,31 @@
         <v>56</v>
       </c>
       <c r="C57">
-        <v>1013</v>
+        <v>1100</v>
       </c>
       <c r="D57">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="E57">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F57">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="I57">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="J57">
-        <v>0.7714</v>
+        <v>2.8818</v>
       </c>
       <c r="K57">
-        <v>0.7714</v>
+        <v>2.1395</v>
       </c>
       <c r="L57" t="s">
         <v>15</v>
@@ -2967,10 +2964,10 @@
         <v>57</v>
       </c>
       <c r="C58">
-        <v>1100</v>
+        <v>1190</v>
       </c>
       <c r="D58">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="E58">
         <v>54</v>
@@ -2979,19 +2976,19 @@
         <v>2290.22</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="I58">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="J58">
-        <v>2.8818</v>
+        <v>1.1353</v>
       </c>
       <c r="K58">
-        <v>2.1395</v>
+        <v>1.1353</v>
       </c>
       <c r="L58" t="s">
         <v>15</v>
@@ -3011,10 +3008,10 @@
         <v>58</v>
       </c>
       <c r="C59">
-        <v>1190</v>
+        <v>1376</v>
       </c>
       <c r="D59">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="E59">
         <v>54</v>
@@ -3023,19 +3020,19 @@
         <v>2290.22</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I59">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J59">
-        <v>1.1353</v>
+        <v>0</v>
       </c>
       <c r="K59">
-        <v>1.1353</v>
+        <v>0</v>
       </c>
       <c r="L59" t="s">
         <v>15</v>
@@ -3055,7 +3052,7 @@
         <v>59</v>
       </c>
       <c r="C60">
-        <v>1376</v>
+        <v>1649</v>
       </c>
       <c r="D60">
         <v>833</v>
@@ -3067,19 +3064,19 @@
         <v>2290.22</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>0.6986</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>0.6986</v>
       </c>
       <c r="L60" t="s">
         <v>15</v>
@@ -3099,10 +3096,10 @@
         <v>60</v>
       </c>
       <c r="C61">
-        <v>1649</v>
+        <v>1736</v>
       </c>
       <c r="D61">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="E61">
         <v>54</v>
@@ -3114,16 +3111,16 @@
         <v>1</v>
       </c>
       <c r="H61">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I61">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="J61">
-        <v>0.6986</v>
+        <v>2.0959</v>
       </c>
       <c r="K61">
-        <v>0.6986</v>
+        <v>2.0959</v>
       </c>
       <c r="L61" t="s">
         <v>15</v>
@@ -3143,10 +3140,10 @@
         <v>61</v>
       </c>
       <c r="C62">
-        <v>1736</v>
+        <v>1830</v>
       </c>
       <c r="D62">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E62">
         <v>52</v>
@@ -3155,19 +3152,19 @@
         <v>2123.72</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I62">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J62">
-        <v>2.2602</v>
+        <v>0</v>
       </c>
       <c r="K62">
-        <v>2.2602</v>
+        <v>0</v>
       </c>
       <c r="L62" t="s">
         <v>15</v>
@@ -3187,16 +3184,16 @@
         <v>62</v>
       </c>
       <c r="C63">
-        <v>1830</v>
+        <v>1927</v>
       </c>
       <c r="D63">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="E63">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F63">
-        <v>2123.72</v>
+        <v>2642.08</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -3231,31 +3228,31 @@
         <v>63</v>
       </c>
       <c r="C64">
-        <v>1927</v>
+        <v>2020</v>
       </c>
       <c r="D64">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="E64">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F64">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>3.6947</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>3.0045</v>
       </c>
       <c r="L64" t="s">
         <v>15</v>
@@ -3275,10 +3272,10 @@
         <v>64</v>
       </c>
       <c r="C65">
-        <v>2144</v>
+        <v>2124</v>
       </c>
       <c r="D65">
-        <v>827</v>
+        <v>847</v>
       </c>
       <c r="E65">
         <v>54</v>
@@ -3287,19 +3284,19 @@
         <v>2290.22</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="I65">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="J65">
-        <v>10.6977</v>
+        <v>0</v>
       </c>
       <c r="K65">
-        <v>10.6977</v>
+        <v>0</v>
       </c>
       <c r="L65" t="s">
         <v>15</v>
@@ -3319,10 +3316,10 @@
         <v>65</v>
       </c>
       <c r="C66">
-        <v>2142</v>
+        <v>1650</v>
       </c>
       <c r="D66">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E66">
         <v>58</v>
@@ -3334,19 +3331,19 @@
         <v>1</v>
       </c>
       <c r="H66">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="I66">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="J66">
-        <v>12.1874</v>
+        <v>0.7948</v>
       </c>
       <c r="K66">
-        <v>12.1874</v>
+        <v>0.7948</v>
       </c>
       <c r="L66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -3363,31 +3360,31 @@
         <v>66</v>
       </c>
       <c r="C67">
-        <v>1650</v>
+        <v>737</v>
       </c>
       <c r="D67">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="E67">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F67">
-        <v>2642.08</v>
+        <v>1963.5</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I67">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J67">
-        <v>0.7948</v>
+        <v>1.8335</v>
       </c>
       <c r="K67">
-        <v>0.7948</v>
+        <v>1.8335</v>
       </c>
       <c r="L67" t="s">
         <v>15</v>
@@ -3407,31 +3404,31 @@
         <v>67</v>
       </c>
       <c r="C68">
-        <v>737</v>
+        <v>822</v>
       </c>
       <c r="D68">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="E68">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F68">
-        <v>1963.5</v>
+        <v>2463.01</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="I68">
         <v>36</v>
       </c>
       <c r="J68">
-        <v>1.8335</v>
+        <v>2.3142</v>
       </c>
       <c r="K68">
-        <v>1.8335</v>
+        <v>1.4616</v>
       </c>
       <c r="L68" t="s">
         <v>15</v>
@@ -3451,10 +3448,10 @@
         <v>68</v>
       </c>
       <c r="C69">
-        <v>822</v>
+        <v>918</v>
       </c>
       <c r="D69">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="E69">
         <v>56</v>
@@ -3463,19 +3460,19 @@
         <v>2463.01</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="I69">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J69">
-        <v>2.3142</v>
+        <v>0</v>
       </c>
       <c r="K69">
-        <v>1.4616</v>
+        <v>0</v>
       </c>
       <c r="L69" t="s">
         <v>15</v>
@@ -3495,31 +3492,31 @@
         <v>69</v>
       </c>
       <c r="C70">
-        <v>918</v>
+        <v>1011</v>
       </c>
       <c r="D70">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E70">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F70">
-        <v>2463.01</v>
+        <v>2123.72</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>3.767</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>3.0136</v>
       </c>
       <c r="L70" t="s">
         <v>15</v>
@@ -3539,31 +3536,31 @@
         <v>70</v>
       </c>
       <c r="C71">
-        <v>1011</v>
+        <v>1102</v>
       </c>
       <c r="D71">
         <v>895</v>
       </c>
       <c r="E71">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F71">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G71">
         <v>2</v>
       </c>
       <c r="H71">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I71">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="J71">
-        <v>3.767</v>
+        <v>2.4015</v>
       </c>
       <c r="K71">
-        <v>3.0136</v>
+        <v>1.7029</v>
       </c>
       <c r="L71" t="s">
         <v>15</v>
@@ -3583,31 +3580,31 @@
         <v>71</v>
       </c>
       <c r="C72">
-        <v>1102</v>
+        <v>1192</v>
       </c>
       <c r="D72">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E72">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F72">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I72">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J72">
-        <v>2.4015</v>
+        <v>0</v>
       </c>
       <c r="K72">
-        <v>1.7029</v>
+        <v>0</v>
       </c>
       <c r="L72" t="s">
         <v>15</v>
@@ -3627,31 +3624,31 @@
         <v>72</v>
       </c>
       <c r="C73">
-        <v>1192</v>
+        <v>1280</v>
       </c>
       <c r="D73">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="E73">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F73">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J73">
-        <v>0</v>
+        <v>0.8327</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>0.8327</v>
       </c>
       <c r="L73" t="s">
         <v>15</v>
@@ -3671,31 +3668,31 @@
         <v>73</v>
       </c>
       <c r="C74">
-        <v>1280</v>
+        <v>1376</v>
       </c>
       <c r="D74">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="E74">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F74">
-        <v>2642.08</v>
+        <v>2123.72</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I74">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J74">
-        <v>0.8327</v>
+        <v>0</v>
       </c>
       <c r="K74">
-        <v>0.8327</v>
+        <v>0</v>
       </c>
       <c r="L74" t="s">
         <v>15</v>
@@ -3715,16 +3712,16 @@
         <v>74</v>
       </c>
       <c r="C75">
-        <v>1376</v>
+        <v>1469</v>
       </c>
       <c r="D75">
         <v>895</v>
       </c>
       <c r="E75">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F75">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -3759,7 +3756,7 @@
         <v>75</v>
       </c>
       <c r="C76">
-        <v>1469</v>
+        <v>1743</v>
       </c>
       <c r="D76">
         <v>895</v>
@@ -3803,16 +3800,16 @@
         <v>76</v>
       </c>
       <c r="C77">
-        <v>1743</v>
+        <v>1834</v>
       </c>
       <c r="D77">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="E77">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F77">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -3847,10 +3844,10 @@
         <v>77</v>
       </c>
       <c r="C78">
-        <v>1834</v>
+        <v>1565</v>
       </c>
       <c r="D78">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="E78">
         <v>58</v>
@@ -3859,19 +3856,19 @@
         <v>2642.08</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I78">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J78">
-        <v>0</v>
+        <v>1.6654</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>1.6654</v>
       </c>
       <c r="L78" t="s">
         <v>15</v>
@@ -3891,31 +3888,31 @@
         <v>78</v>
       </c>
       <c r="C79">
-        <v>1565</v>
+        <v>1921</v>
       </c>
       <c r="D79">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="E79">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F79">
-        <v>2642.08</v>
+        <v>2290.22</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="I79">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="J79">
-        <v>1.6654</v>
+        <v>1.3099</v>
       </c>
       <c r="K79">
-        <v>1.6654</v>
+        <v>1.3099</v>
       </c>
       <c r="L79" t="s">
         <v>15</v>
@@ -3935,31 +3932,31 @@
         <v>79</v>
       </c>
       <c r="C80">
-        <v>1921</v>
+        <v>2026</v>
       </c>
       <c r="D80">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="E80">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F80">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I80">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J80">
-        <v>1.3099</v>
+        <v>0</v>
       </c>
       <c r="K80">
-        <v>1.3099</v>
+        <v>0</v>
       </c>
       <c r="L80" t="s">
         <v>15</v>
@@ -3979,31 +3976,31 @@
         <v>80</v>
       </c>
       <c r="C81">
-        <v>2027</v>
+        <v>2117</v>
       </c>
       <c r="D81">
-        <v>902</v>
+        <v>891</v>
       </c>
       <c r="E81">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F81">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>2.016</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>0.7427</v>
       </c>
       <c r="L81" t="s">
         <v>15</v>
@@ -4023,31 +4020,31 @@
         <v>81</v>
       </c>
       <c r="C82">
-        <v>2140</v>
+        <v>733</v>
       </c>
       <c r="D82">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="E82">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F82">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G82">
         <v>1</v>
       </c>
       <c r="H82">
-        <v>291</v>
+        <v>28</v>
       </c>
       <c r="I82">
-        <v>291</v>
+        <v>28</v>
       </c>
       <c r="J82">
-        <v>10.292</v>
+        <v>1.2226</v>
       </c>
       <c r="K82">
-        <v>10.292</v>
+        <v>1.2226</v>
       </c>
       <c r="L82" t="s">
         <v>15</v>
@@ -4067,31 +4064,31 @@
         <v>82</v>
       </c>
       <c r="C83">
-        <v>733</v>
+        <v>813</v>
       </c>
       <c r="D83">
         <v>958</v>
       </c>
       <c r="E83">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F83">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H83">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I83">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J83">
-        <v>1.2226</v>
+        <v>1.3086</v>
       </c>
       <c r="K83">
-        <v>1.2226</v>
+        <v>0.7074</v>
       </c>
       <c r="L83" t="s">
         <v>15</v>
@@ -4111,31 +4108,31 @@
         <v>83</v>
       </c>
       <c r="C84">
-        <v>813</v>
+        <v>922</v>
       </c>
       <c r="D84">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="E84">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F84">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G84">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H84">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="I84">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J84">
-        <v>1.3086</v>
+        <v>3.5804</v>
       </c>
       <c r="K84">
-        <v>0.7074</v>
+        <v>0.9606</v>
       </c>
       <c r="L84" t="s">
         <v>15</v>
@@ -4155,31 +4152,31 @@
         <v>84</v>
       </c>
       <c r="C85">
-        <v>922</v>
+        <v>1201</v>
       </c>
       <c r="D85">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E85">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F85">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G85">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H85">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="I85">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J85">
-        <v>3.5804</v>
+        <v>1.6623</v>
       </c>
       <c r="K85">
-        <v>0.9606</v>
+        <v>0.8842</v>
       </c>
       <c r="L85" t="s">
         <v>15</v>
@@ -4551,7 +4548,7 @@
         <v>93</v>
       </c>
       <c r="C94">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="D94">
         <v>959</v>
@@ -4563,16 +4560,16 @@
         <v>2290.22</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H94">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="I94">
         <v>28</v>
       </c>
       <c r="J94">
-        <v>2.7945</v>
+        <v>2.0085</v>
       </c>
       <c r="K94">
         <v>1.2226</v>
@@ -4639,31 +4636,31 @@
         <v>95</v>
       </c>
       <c r="C96">
-        <v>1195</v>
+        <v>2120</v>
       </c>
       <c r="D96">
-        <v>961</v>
+        <v>954</v>
       </c>
       <c r="E96">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F96">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I96">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J96">
-        <v>1.218</v>
+        <v>0</v>
       </c>
       <c r="K96">
-        <v>1.218</v>
+        <v>0</v>
       </c>
       <c r="L96" t="s">
         <v>15</v>
@@ -4683,10 +4680,10 @@
         <v>96</v>
       </c>
       <c r="C97">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="D97">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E97">
         <v>58</v>
@@ -4727,10 +4724,10 @@
         <v>97</v>
       </c>
       <c r="C98">
-        <v>2152</v>
+        <v>717</v>
       </c>
       <c r="D98">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="E98">
         <v>60</v>
@@ -4742,16 +4739,16 @@
         <v>1</v>
       </c>
       <c r="H98">
-        <v>260</v>
+        <v>35</v>
       </c>
       <c r="I98">
-        <v>260</v>
+        <v>35</v>
       </c>
       <c r="J98">
-        <v>9.195600000000001</v>
+        <v>1.2379</v>
       </c>
       <c r="K98">
-        <v>9.195600000000001</v>
+        <v>1.2379</v>
       </c>
       <c r="L98" t="s">
         <v>15</v>
@@ -4771,31 +4768,31 @@
         <v>98</v>
       </c>
       <c r="C99">
-        <v>717</v>
+        <v>821</v>
       </c>
       <c r="D99">
-        <v>1016</v>
+        <v>1023</v>
       </c>
       <c r="E99">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F99">
-        <v>2827.43</v>
+        <v>2123.72</v>
       </c>
       <c r="G99">
         <v>1</v>
       </c>
       <c r="H99">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I99">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="J99">
-        <v>1.2379</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K99">
-        <v>1.2379</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="L99" t="s">
         <v>15</v>
@@ -4815,31 +4812,31 @@
         <v>99</v>
       </c>
       <c r="C100">
-        <v>821</v>
+        <v>915</v>
       </c>
       <c r="D100">
         <v>1023</v>
       </c>
       <c r="E100">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F100">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I100">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J100">
-        <v>0.8947000000000001</v>
+        <v>0</v>
       </c>
       <c r="K100">
-        <v>0.8947000000000001</v>
+        <v>0</v>
       </c>
       <c r="L100" t="s">
         <v>15</v>
@@ -4859,16 +4856,16 @@
         <v>100</v>
       </c>
       <c r="C101">
-        <v>915</v>
+        <v>1098</v>
       </c>
       <c r="D101">
         <v>1023</v>
       </c>
       <c r="E101">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F101">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -4903,31 +4900,31 @@
         <v>101</v>
       </c>
       <c r="C102">
-        <v>1098</v>
+        <v>1747</v>
       </c>
       <c r="D102">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="E102">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F102">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I102">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J102">
-        <v>0</v>
+        <v>1.0962</v>
       </c>
       <c r="K102">
-        <v>0</v>
+        <v>1.0962</v>
       </c>
       <c r="L102" t="s">
         <v>15</v>
@@ -4947,31 +4944,31 @@
         <v>102</v>
       </c>
       <c r="C103">
-        <v>1747</v>
+        <v>1843</v>
       </c>
       <c r="D103">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E103">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F103">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G103">
         <v>1</v>
       </c>
       <c r="H103">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I103">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J103">
-        <v>1.0962</v>
+        <v>0.786</v>
       </c>
       <c r="K103">
-        <v>1.0962</v>
+        <v>0.786</v>
       </c>
       <c r="L103" t="s">
         <v>15</v>
@@ -4991,7 +4988,7 @@
         <v>103</v>
       </c>
       <c r="C104">
-        <v>1843</v>
+        <v>1936</v>
       </c>
       <c r="D104">
         <v>1023</v>
@@ -5003,19 +5000,19 @@
         <v>2290.22</v>
       </c>
       <c r="G104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H104">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="I104">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J104">
-        <v>0.786</v>
+        <v>3.5368</v>
       </c>
       <c r="K104">
-        <v>0.786</v>
+        <v>1.7902</v>
       </c>
       <c r="L104" t="s">
         <v>15</v>
@@ -5035,31 +5032,31 @@
         <v>104</v>
       </c>
       <c r="C105">
-        <v>1936</v>
+        <v>1014</v>
       </c>
       <c r="D105">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="E105">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F105">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G105">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="I105">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J105">
-        <v>3.5368</v>
+        <v>0</v>
       </c>
       <c r="K105">
-        <v>1.7902</v>
+        <v>0</v>
       </c>
       <c r="L105" t="s">
         <v>15</v>
@@ -5079,31 +5076,31 @@
         <v>105</v>
       </c>
       <c r="C106">
-        <v>1014</v>
+        <v>1193</v>
       </c>
       <c r="D106">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="E106">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F106">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J106">
-        <v>0</v>
+        <v>0.7423</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>0.7423</v>
       </c>
       <c r="L106" t="s">
         <v>15</v>
@@ -5123,7 +5120,7 @@
         <v>106</v>
       </c>
       <c r="C107">
-        <v>1193</v>
+        <v>1658</v>
       </c>
       <c r="D107">
         <v>1024</v>
@@ -5135,19 +5132,19 @@
         <v>2290.22</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H107">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I107">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J107">
-        <v>0.7423</v>
+        <v>1.7902</v>
       </c>
       <c r="K107">
-        <v>0.7423</v>
+        <v>1.0479</v>
       </c>
       <c r="L107" t="s">
         <v>15</v>
@@ -5167,31 +5164,31 @@
         <v>107</v>
       </c>
       <c r="C108">
-        <v>1658</v>
+        <v>2037</v>
       </c>
       <c r="D108">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="E108">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F108">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G108">
         <v>2</v>
       </c>
       <c r="H108">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="I108">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="J108">
-        <v>1.7902</v>
+        <v>2.9901</v>
       </c>
       <c r="K108">
-        <v>1.0479</v>
+        <v>2.1195</v>
       </c>
       <c r="L108" t="s">
         <v>15</v>
@@ -5387,31 +5384,31 @@
         <v>112</v>
       </c>
       <c r="C113">
-        <v>2039</v>
+        <v>2128</v>
       </c>
       <c r="D113">
-        <v>1030</v>
+        <v>1016</v>
       </c>
       <c r="E113">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F113">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G113">
         <v>2</v>
       </c>
       <c r="H113">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="I113">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="J113">
-        <v>2.9901</v>
+        <v>1.4147</v>
       </c>
       <c r="K113">
-        <v>2.1195</v>
+        <v>0.7427</v>
       </c>
       <c r="L113" t="s">
         <v>15</v>
@@ -5739,10 +5736,10 @@
         <v>120</v>
       </c>
       <c r="C121">
-        <v>1947</v>
+        <v>2041</v>
       </c>
       <c r="D121">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E121">
         <v>56</v>
@@ -5751,19 +5748,19 @@
         <v>2463.01</v>
       </c>
       <c r="G121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H121">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="I121">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J121">
-        <v>2.5578</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K121">
-        <v>0.9744</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="L121" t="s">
         <v>15</v>
@@ -5783,31 +5780,31 @@
         <v>121</v>
       </c>
       <c r="C122">
-        <v>1193</v>
+        <v>1947</v>
       </c>
       <c r="D122">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="E122">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F122">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H122">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="I122">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="J122">
-        <v>3.2311</v>
+        <v>2.5172</v>
       </c>
       <c r="K122">
-        <v>2.1832</v>
+        <v>0.9744</v>
       </c>
       <c r="L122" t="s">
         <v>15</v>
@@ -5871,10 +5868,10 @@
         <v>123</v>
       </c>
       <c r="C124">
-        <v>1288</v>
+        <v>1196</v>
       </c>
       <c r="D124">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="E124">
         <v>60</v>
@@ -5883,19 +5880,19 @@
         <v>2827.43</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="I124">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J124">
-        <v>0</v>
+        <v>2.5111</v>
       </c>
       <c r="K124">
-        <v>0</v>
+        <v>1.6623</v>
       </c>
       <c r="L124" t="s">
         <v>15</v>
@@ -5915,31 +5912,31 @@
         <v>124</v>
       </c>
       <c r="C125">
-        <v>1381</v>
+        <v>2129</v>
       </c>
       <c r="D125">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="E125">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F125">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I125">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J125">
-        <v>0</v>
+        <v>2.233</v>
       </c>
       <c r="K125">
-        <v>0</v>
+        <v>2.233</v>
       </c>
       <c r="L125" t="s">
         <v>15</v>
@@ -5959,7 +5956,7 @@
         <v>125</v>
       </c>
       <c r="C126">
-        <v>1475</v>
+        <v>1288</v>
       </c>
       <c r="D126">
         <v>1092</v>
@@ -6003,7 +6000,7 @@
         <v>126</v>
       </c>
       <c r="C127">
-        <v>1568</v>
+        <v>1381</v>
       </c>
       <c r="D127">
         <v>1092</v>
@@ -6047,31 +6044,31 @@
         <v>127</v>
       </c>
       <c r="C128">
-        <v>2042</v>
+        <v>1475</v>
       </c>
       <c r="D128">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="E128">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F128">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I128">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J128">
-        <v>0.757</v>
+        <v>0</v>
       </c>
       <c r="K128">
-        <v>0.757</v>
+        <v>0</v>
       </c>
       <c r="L128" t="s">
         <v>15</v>
@@ -6091,10 +6088,10 @@
         <v>128</v>
       </c>
       <c r="C129">
-        <v>2149</v>
+        <v>1568</v>
       </c>
       <c r="D129">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E129">
         <v>60</v>
@@ -6103,19 +6100,19 @@
         <v>2827.43</v>
       </c>
       <c r="G129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="I129">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="J129">
-        <v>3.9612</v>
+        <v>0</v>
       </c>
       <c r="K129">
-        <v>3.9612</v>
+        <v>0</v>
       </c>
       <c r="L129" t="s">
         <v>15</v>
@@ -6795,10 +6792,10 @@
         <v>144</v>
       </c>
       <c r="C145">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="D145">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="E145">
         <v>60</v>
@@ -6807,19 +6804,19 @@
         <v>2827.43</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I145">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J145">
-        <v>0</v>
+        <v>0.9196</v>
       </c>
       <c r="K145">
-        <v>0</v>
+        <v>0.9196</v>
       </c>
       <c r="L145" t="s">
         <v>15</v>
@@ -6839,31 +6836,31 @@
         <v>145</v>
       </c>
       <c r="C146">
-        <v>1289</v>
+        <v>718</v>
       </c>
       <c r="D146">
-        <v>1174</v>
+        <v>1221</v>
       </c>
       <c r="E146">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F146">
-        <v>1520.53</v>
+        <v>2290.22</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="I146">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J146">
-        <v>0</v>
+        <v>1.8775</v>
       </c>
       <c r="K146">
-        <v>0</v>
+        <v>1.0479</v>
       </c>
       <c r="L146" t="s">
         <v>15</v>
@@ -6883,7 +6880,7 @@
         <v>146</v>
       </c>
       <c r="C147">
-        <v>718</v>
+        <v>813</v>
       </c>
       <c r="D147">
         <v>1221</v>
@@ -6895,19 +6892,19 @@
         <v>2290.22</v>
       </c>
       <c r="G147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H147">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="I147">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J147">
-        <v>1.8775</v>
+        <v>1.4409</v>
       </c>
       <c r="K147">
-        <v>1.0479</v>
+        <v>1.4409</v>
       </c>
       <c r="L147" t="s">
         <v>15</v>
@@ -6927,7 +6924,7 @@
         <v>147</v>
       </c>
       <c r="C148">
-        <v>813</v>
+        <v>910</v>
       </c>
       <c r="D148">
         <v>1221</v>
@@ -6939,19 +6936,19 @@
         <v>2290.22</v>
       </c>
       <c r="G148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H148">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I148">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J148">
-        <v>1.4409</v>
+        <v>2.0959</v>
       </c>
       <c r="K148">
-        <v>1.4409</v>
+        <v>1.3099</v>
       </c>
       <c r="L148" t="s">
         <v>15</v>
@@ -6971,31 +6968,31 @@
         <v>148</v>
       </c>
       <c r="C149">
-        <v>910</v>
+        <v>1003</v>
       </c>
       <c r="D149">
         <v>1221</v>
       </c>
       <c r="E149">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F149">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G149">
         <v>2</v>
       </c>
       <c r="H149">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I149">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J149">
-        <v>2.0959</v>
+        <v>1.7052</v>
       </c>
       <c r="K149">
-        <v>1.3099</v>
+        <v>0.9338</v>
       </c>
       <c r="L149" t="s">
         <v>15</v>
@@ -7015,31 +7012,31 @@
         <v>149</v>
       </c>
       <c r="C150">
-        <v>1003</v>
+        <v>1100</v>
       </c>
       <c r="D150">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E150">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F150">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H150">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="I150">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J150">
-        <v>1.7052</v>
+        <v>0.9841</v>
       </c>
       <c r="K150">
-        <v>0.9338</v>
+        <v>0.9841</v>
       </c>
       <c r="L150" t="s">
         <v>15</v>
@@ -7059,31 +7056,31 @@
         <v>150</v>
       </c>
       <c r="C151">
-        <v>1100</v>
+        <v>1182</v>
       </c>
       <c r="D151">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E151">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F151">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H151">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I151">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J151">
-        <v>0.9841</v>
+        <v>0</v>
       </c>
       <c r="K151">
-        <v>0.9841</v>
+        <v>0</v>
       </c>
       <c r="L151" t="s">
         <v>15</v>
@@ -7103,10 +7100,10 @@
         <v>151</v>
       </c>
       <c r="C152">
-        <v>1182</v>
+        <v>1479</v>
       </c>
       <c r="D152">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="E152">
         <v>60</v>
@@ -7147,31 +7144,31 @@
         <v>152</v>
       </c>
       <c r="C153">
-        <v>1479</v>
+        <v>1763</v>
       </c>
       <c r="D153">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="E153">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F153">
-        <v>2827.43</v>
+        <v>2642.08</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I153">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J153">
-        <v>0</v>
+        <v>0.6813</v>
       </c>
       <c r="K153">
-        <v>0</v>
+        <v>0.6813</v>
       </c>
       <c r="L153" t="s">
         <v>15</v>
@@ -7191,31 +7188,31 @@
         <v>153</v>
       </c>
       <c r="C154">
-        <v>1763</v>
+        <v>1856</v>
       </c>
       <c r="D154">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="E154">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F154">
-        <v>2642.08</v>
+        <v>2290.22</v>
       </c>
       <c r="G154">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H154">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="I154">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J154">
-        <v>0.6813</v>
+        <v>2.8818</v>
       </c>
       <c r="K154">
-        <v>0.6813</v>
+        <v>1.0916</v>
       </c>
       <c r="L154" t="s">
         <v>15</v>
@@ -7235,31 +7232,31 @@
         <v>154</v>
       </c>
       <c r="C155">
-        <v>1856</v>
+        <v>1951</v>
       </c>
       <c r="D155">
         <v>1221</v>
       </c>
       <c r="E155">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F155">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G155">
         <v>3</v>
       </c>
       <c r="H155">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="I155">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J155">
-        <v>2.8818</v>
+        <v>3.7353</v>
       </c>
       <c r="K155">
-        <v>1.0916</v>
+        <v>1.5834</v>
       </c>
       <c r="L155" t="s">
         <v>15</v>
@@ -7279,31 +7276,31 @@
         <v>155</v>
       </c>
       <c r="C156">
-        <v>1951</v>
+        <v>2048</v>
       </c>
       <c r="D156">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="E156">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F156">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G156">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H156">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="I156">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J156">
-        <v>3.7353</v>
+        <v>1.0916</v>
       </c>
       <c r="K156">
-        <v>1.5834</v>
+        <v>1.0916</v>
       </c>
       <c r="L156" t="s">
         <v>15</v>
@@ -7323,31 +7320,31 @@
         <v>156</v>
       </c>
       <c r="C157">
-        <v>2048</v>
+        <v>2139</v>
       </c>
       <c r="D157">
-        <v>1222</v>
+        <v>1212</v>
       </c>
       <c r="E157">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F157">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H157">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I157">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J157">
-        <v>1.0916</v>
+        <v>0</v>
       </c>
       <c r="K157">
-        <v>1.0916</v>
+        <v>0</v>
       </c>
       <c r="L157" t="s">
         <v>15</v>
@@ -7367,10 +7364,10 @@
         <v>157</v>
       </c>
       <c r="C158">
-        <v>2142</v>
+        <v>1386</v>
       </c>
       <c r="D158">
-        <v>1213</v>
+        <v>1222</v>
       </c>
       <c r="E158">
         <v>60</v>
@@ -7411,31 +7408,31 @@
         <v>158</v>
       </c>
       <c r="C159">
-        <v>1386</v>
+        <v>1570</v>
       </c>
       <c r="D159">
         <v>1222</v>
       </c>
       <c r="E159">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F159">
-        <v>2827.43</v>
+        <v>2642.08</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I159">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J159">
-        <v>0</v>
+        <v>0.7191</v>
       </c>
       <c r="K159">
-        <v>0</v>
+        <v>0.7191</v>
       </c>
       <c r="L159" t="s">
         <v>15</v>
@@ -7455,31 +7452,31 @@
         <v>159</v>
       </c>
       <c r="C160">
-        <v>1570</v>
+        <v>1669</v>
       </c>
       <c r="D160">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="E160">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F160">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H160">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="I160">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J160">
-        <v>0.7191</v>
+        <v>2.6172</v>
       </c>
       <c r="K160">
-        <v>0.7191</v>
+        <v>1.9806</v>
       </c>
       <c r="L160" t="s">
         <v>15</v>
@@ -7499,10 +7496,10 @@
         <v>160</v>
       </c>
       <c r="C161">
-        <v>1669</v>
+        <v>1292</v>
       </c>
       <c r="D161">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="E161">
         <v>60</v>
@@ -7514,16 +7511,16 @@
         <v>2</v>
       </c>
       <c r="H161">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="I161">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J161">
-        <v>2.6172</v>
+        <v>3.077</v>
       </c>
       <c r="K161">
-        <v>1.9806</v>
+        <v>2.1574</v>
       </c>
       <c r="L161" t="s">
         <v>15</v>
@@ -8027,31 +8024,31 @@
         <v>172</v>
       </c>
       <c r="C173">
-        <v>2049</v>
+        <v>1385</v>
       </c>
       <c r="D173">
-        <v>1280</v>
+        <v>1290</v>
       </c>
       <c r="E173">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F173">
-        <v>2827.43</v>
+        <v>2642.08</v>
       </c>
       <c r="G173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H173">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I173">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J173">
-        <v>0.7781</v>
+        <v>0</v>
       </c>
       <c r="K173">
-        <v>0.7781</v>
+        <v>0</v>
       </c>
       <c r="L173" t="s">
         <v>15</v>
@@ -8071,10 +8068,10 @@
         <v>173</v>
       </c>
       <c r="C174">
-        <v>2149</v>
+        <v>1575</v>
       </c>
       <c r="D174">
-        <v>1282</v>
+        <v>1295</v>
       </c>
       <c r="E174">
         <v>60</v>
@@ -8083,19 +8080,19 @@
         <v>2827.43</v>
       </c>
       <c r="G174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H174">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="I174">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J174">
-        <v>0.9196</v>
+        <v>1.3793</v>
       </c>
       <c r="K174">
-        <v>0.9196</v>
+        <v>0.7074</v>
       </c>
       <c r="L174" t="s">
         <v>15</v>
@@ -8115,16 +8112,16 @@
         <v>174</v>
       </c>
       <c r="C175">
-        <v>1385</v>
+        <v>1284</v>
       </c>
       <c r="D175">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="E175">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F175">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G175">
         <v>0</v>
@@ -8159,10 +8156,10 @@
         <v>175</v>
       </c>
       <c r="C176">
-        <v>1575</v>
+        <v>2050</v>
       </c>
       <c r="D176">
-        <v>1295</v>
+        <v>1281</v>
       </c>
       <c r="E176">
         <v>60</v>
@@ -8174,16 +8171,16 @@
         <v>2</v>
       </c>
       <c r="H176">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I176">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J176">
-        <v>1.3793</v>
+        <v>1.4147</v>
       </c>
       <c r="K176">
-        <v>0.7074</v>
+        <v>0.7781</v>
       </c>
       <c r="L176" t="s">
         <v>15</v>
@@ -8203,10 +8200,10 @@
         <v>176</v>
       </c>
       <c r="C177">
-        <v>1284</v>
+        <v>2149</v>
       </c>
       <c r="D177">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="E177">
         <v>60</v>
@@ -8215,19 +8212,19 @@
         <v>2827.43</v>
       </c>
       <c r="G177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H177">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I177">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J177">
-        <v>0</v>
+        <v>0.9196</v>
       </c>
       <c r="K177">
-        <v>0</v>
+        <v>0.9196</v>
       </c>
       <c r="L177" t="s">
         <v>15</v>
@@ -8995,31 +8992,31 @@
         <v>194</v>
       </c>
       <c r="C195">
-        <v>2160</v>
+        <v>813</v>
       </c>
       <c r="D195">
         <v>1427</v>
       </c>
       <c r="E195">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F195">
-        <v>2642.08</v>
+        <v>1963.5</v>
       </c>
       <c r="G195">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H195">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="I195">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J195">
-        <v>3.3686</v>
+        <v>1.9353</v>
       </c>
       <c r="K195">
-        <v>1.7032</v>
+        <v>1.9353</v>
       </c>
       <c r="L195" t="s">
         <v>15</v>
@@ -9039,31 +9036,31 @@
         <v>195</v>
       </c>
       <c r="C196">
-        <v>806</v>
+        <v>2160</v>
       </c>
       <c r="D196">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="E196">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F196">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G196">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H196">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="I196">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J196">
-        <v>2.5578</v>
+        <v>3.3686</v>
       </c>
       <c r="K196">
-        <v>1.5834</v>
+        <v>1.7032</v>
       </c>
       <c r="L196" t="s">
         <v>15</v>
@@ -9171,31 +9168,31 @@
         <v>198</v>
       </c>
       <c r="C199">
-        <v>1093</v>
+        <v>1192</v>
       </c>
       <c r="D199">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="E199">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F199">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G199">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H199">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I199">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J199">
-        <v>1.1671</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K199">
-        <v>0.6012999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="L199" t="s">
         <v>15</v>
@@ -9215,7 +9212,7 @@
         <v>199</v>
       </c>
       <c r="C200">
-        <v>1192</v>
+        <v>1289</v>
       </c>
       <c r="D200">
         <v>1428</v>
@@ -9230,16 +9227,16 @@
         <v>1</v>
       </c>
       <c r="H200">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I200">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J200">
-        <v>0.8120000000000001</v>
+        <v>1.0556</v>
       </c>
       <c r="K200">
-        <v>0.8120000000000001</v>
+        <v>1.0556</v>
       </c>
       <c r="L200" t="s">
         <v>15</v>
@@ -9259,10 +9256,10 @@
         <v>200</v>
       </c>
       <c r="C201">
-        <v>1289</v>
+        <v>1384</v>
       </c>
       <c r="D201">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="E201">
         <v>56</v>
@@ -9271,19 +9268,19 @@
         <v>2463.01</v>
       </c>
       <c r="G201">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H201">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="I201">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J201">
-        <v>1.0556</v>
+        <v>1.827</v>
       </c>
       <c r="K201">
-        <v>1.0556</v>
+        <v>0.9744</v>
       </c>
       <c r="L201" t="s">
         <v>15</v>
@@ -9303,10 +9300,10 @@
         <v>201</v>
       </c>
       <c r="C202">
-        <v>1384</v>
+        <v>1482</v>
       </c>
       <c r="D202">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="E202">
         <v>56</v>
@@ -9318,16 +9315,16 @@
         <v>2</v>
       </c>
       <c r="H202">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I202">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J202">
-        <v>1.827</v>
+        <v>1.9082</v>
       </c>
       <c r="K202">
-        <v>0.9744</v>
+        <v>1.015</v>
       </c>
       <c r="L202" t="s">
         <v>15</v>
@@ -9347,7 +9344,7 @@
         <v>202</v>
       </c>
       <c r="C203">
-        <v>1482</v>
+        <v>1579</v>
       </c>
       <c r="D203">
         <v>1428</v>
@@ -9359,19 +9356,19 @@
         <v>2463.01</v>
       </c>
       <c r="G203">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H203">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="I203">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J203">
-        <v>1.9082</v>
+        <v>0.7714</v>
       </c>
       <c r="K203">
-        <v>1.015</v>
+        <v>0.7714</v>
       </c>
       <c r="L203" t="s">
         <v>15</v>
@@ -9391,7 +9388,7 @@
         <v>203</v>
       </c>
       <c r="C204">
-        <v>1579</v>
+        <v>1676</v>
       </c>
       <c r="D204">
         <v>1428</v>
@@ -9403,19 +9400,19 @@
         <v>2463.01</v>
       </c>
       <c r="G204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H204">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I204">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J204">
-        <v>0.7714</v>
+        <v>0</v>
       </c>
       <c r="K204">
-        <v>0.7714</v>
+        <v>0</v>
       </c>
       <c r="L204" t="s">
         <v>15</v>
@@ -9435,7 +9432,7 @@
         <v>204</v>
       </c>
       <c r="C205">
-        <v>1676</v>
+        <v>1870</v>
       </c>
       <c r="D205">
         <v>1428</v>
@@ -9479,7 +9476,7 @@
         <v>205</v>
       </c>
       <c r="C206">
-        <v>1870</v>
+        <v>1969</v>
       </c>
       <c r="D206">
         <v>1428</v>
@@ -9491,19 +9488,19 @@
         <v>2463.01</v>
       </c>
       <c r="G206">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="I206">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J206">
-        <v>0</v>
+        <v>2.3954</v>
       </c>
       <c r="K206">
-        <v>0</v>
+        <v>1.7052</v>
       </c>
       <c r="L206" t="s">
         <v>15</v>
@@ -9523,7 +9520,7 @@
         <v>206</v>
       </c>
       <c r="C207">
-        <v>1969</v>
+        <v>2064</v>
       </c>
       <c r="D207">
         <v>1428</v>
@@ -9535,19 +9532,19 @@
         <v>2463.01</v>
       </c>
       <c r="G207">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H207">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="I207">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J207">
-        <v>2.3954</v>
+        <v>0</v>
       </c>
       <c r="K207">
-        <v>1.7052</v>
+        <v>0</v>
       </c>
       <c r="L207" t="s">
         <v>15</v>
@@ -9567,31 +9564,31 @@
         <v>207</v>
       </c>
       <c r="C208">
-        <v>2064</v>
+        <v>1094</v>
       </c>
       <c r="D208">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="E208">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F208">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G208">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H208">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I208">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J208">
-        <v>0</v>
+        <v>1.1671</v>
       </c>
       <c r="K208">
-        <v>0</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="L208" t="s">
         <v>15</v>
@@ -9655,10 +9652,10 @@
         <v>209</v>
       </c>
       <c r="C210">
-        <v>2167</v>
+        <v>767</v>
       </c>
       <c r="D210">
-        <v>1499</v>
+        <v>1473</v>
       </c>
       <c r="E210">
         <v>56</v>
@@ -9667,19 +9664,19 @@
         <v>2463.01</v>
       </c>
       <c r="G210">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H210">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I210">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J210">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="K210">
-        <v>1.0962</v>
+        <v>0</v>
       </c>
       <c r="L210" t="s">
         <v>15</v>
@@ -9699,31 +9696,31 @@
         <v>210</v>
       </c>
       <c r="C211">
-        <v>703</v>
+        <v>1192</v>
       </c>
       <c r="D211">
-        <v>1499</v>
+        <v>1492</v>
       </c>
       <c r="E211">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F211">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G211">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H211">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="I211">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J211">
-        <v>3.0451</v>
+        <v>1.1318</v>
       </c>
       <c r="K211">
-        <v>1.3398</v>
+        <v>1.1318</v>
       </c>
       <c r="L211" t="s">
         <v>15</v>
@@ -9743,7 +9740,7 @@
         <v>211</v>
       </c>
       <c r="C212">
-        <v>800</v>
+        <v>2167</v>
       </c>
       <c r="D212">
         <v>1499</v>
@@ -9758,16 +9755,16 @@
         <v>2</v>
       </c>
       <c r="H212">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I212">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J212">
-        <v>1.7052</v>
+        <v>2.03</v>
       </c>
       <c r="K212">
-        <v>0.9338</v>
+        <v>1.0962</v>
       </c>
       <c r="L212" t="s">
         <v>15</v>
@@ -9919,10 +9916,10 @@
         <v>215</v>
       </c>
       <c r="C216">
-        <v>1190</v>
+        <v>1289</v>
       </c>
       <c r="D216">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="E216">
         <v>60</v>
@@ -9931,19 +9928,19 @@
         <v>2827.43</v>
       </c>
       <c r="G216">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H216">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="I216">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="J216">
-        <v>1.1318</v>
+        <v>2.4757</v>
       </c>
       <c r="K216">
-        <v>1.1318</v>
+        <v>1.6269</v>
       </c>
       <c r="L216" t="s">
         <v>15</v>
@@ -9963,7 +9960,7 @@
         <v>216</v>
       </c>
       <c r="C217">
-        <v>1289</v>
+        <v>1484</v>
       </c>
       <c r="D217">
         <v>1493</v>
@@ -9975,19 +9972,19 @@
         <v>2827.43</v>
       </c>
       <c r="G217">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H217">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="I217">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J217">
-        <v>2.4757</v>
+        <v>1.3793</v>
       </c>
       <c r="K217">
-        <v>1.6269</v>
+        <v>1.3793</v>
       </c>
       <c r="L217" t="s">
         <v>15</v>
@@ -10007,7 +10004,7 @@
         <v>217</v>
       </c>
       <c r="C218">
-        <v>1484</v>
+        <v>1582</v>
       </c>
       <c r="D218">
         <v>1493</v>
@@ -10019,19 +10016,19 @@
         <v>2827.43</v>
       </c>
       <c r="G218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H218">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I218">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J218">
-        <v>1.3793</v>
+        <v>0</v>
       </c>
       <c r="K218">
-        <v>1.3793</v>
+        <v>0</v>
       </c>
       <c r="L218" t="s">
         <v>15</v>
@@ -10051,7 +10048,7 @@
         <v>218</v>
       </c>
       <c r="C219">
-        <v>1582</v>
+        <v>1680</v>
       </c>
       <c r="D219">
         <v>1493</v>
@@ -10063,19 +10060,19 @@
         <v>2827.43</v>
       </c>
       <c r="G219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H219">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I219">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J219">
-        <v>0</v>
+        <v>1.0964</v>
       </c>
       <c r="K219">
-        <v>0</v>
+        <v>1.0964</v>
       </c>
       <c r="L219" t="s">
         <v>15</v>
@@ -10095,31 +10092,31 @@
         <v>219</v>
       </c>
       <c r="C220">
-        <v>1680</v>
+        <v>1776</v>
       </c>
       <c r="D220">
-        <v>1493</v>
+        <v>1500</v>
       </c>
       <c r="E220">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F220">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G220">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H220">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I220">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J220">
-        <v>1.0964</v>
+        <v>1.7458</v>
       </c>
       <c r="K220">
-        <v>1.0964</v>
+        <v>1.0962</v>
       </c>
       <c r="L220" t="s">
         <v>15</v>
@@ -10139,31 +10136,31 @@
         <v>220</v>
       </c>
       <c r="C221">
-        <v>1776</v>
+        <v>1877</v>
       </c>
       <c r="D221">
         <v>1500</v>
       </c>
       <c r="E221">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F221">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G221">
         <v>2</v>
       </c>
       <c r="H221">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="I221">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="J221">
-        <v>1.7458</v>
+        <v>2.763</v>
       </c>
       <c r="K221">
-        <v>1.0962</v>
+        <v>1.7032</v>
       </c>
       <c r="L221" t="s">
         <v>15</v>
@@ -10183,31 +10180,31 @@
         <v>221</v>
       </c>
       <c r="C222">
-        <v>1877</v>
+        <v>1972</v>
       </c>
       <c r="D222">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="E222">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F222">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G222">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H222">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="I222">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J222">
-        <v>2.763</v>
+        <v>0</v>
       </c>
       <c r="K222">
-        <v>1.7032</v>
+        <v>0</v>
       </c>
       <c r="L222" t="s">
         <v>15</v>
@@ -10227,31 +10224,31 @@
         <v>222</v>
       </c>
       <c r="C223">
-        <v>1972</v>
+        <v>2070</v>
       </c>
       <c r="D223">
         <v>1499</v>
       </c>
       <c r="E223">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F223">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G223">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="I223">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="J223">
-        <v>0</v>
+        <v>5.7152</v>
       </c>
       <c r="K223">
-        <v>0</v>
+        <v>2.0438</v>
       </c>
       <c r="L223" t="s">
         <v>15</v>
@@ -10271,31 +10268,31 @@
         <v>223</v>
       </c>
       <c r="C224">
-        <v>2070</v>
+        <v>1383</v>
       </c>
       <c r="D224">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="E224">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F224">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G224">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H224">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="I224">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J224">
-        <v>5.7152</v>
+        <v>3.5368</v>
       </c>
       <c r="K224">
-        <v>2.0438</v>
+        <v>1.7684</v>
       </c>
       <c r="L224" t="s">
         <v>15</v>
@@ -10315,31 +10312,31 @@
         <v>224</v>
       </c>
       <c r="C225">
-        <v>1383</v>
+        <v>796</v>
       </c>
       <c r="D225">
-        <v>1494</v>
+        <v>1570</v>
       </c>
       <c r="E225">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F225">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G225">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H225">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I225">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="J225">
-        <v>3.5368</v>
+        <v>4.803</v>
       </c>
       <c r="K225">
-        <v>1.7684</v>
+        <v>3.1438</v>
       </c>
       <c r="L225" t="s">
         <v>15</v>
@@ -10359,31 +10356,31 @@
         <v>225</v>
       </c>
       <c r="C226">
-        <v>1387</v>
+        <v>703</v>
       </c>
       <c r="D226">
-        <v>1568</v>
+        <v>1509</v>
       </c>
       <c r="E226">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="F226">
-        <v>2827.43</v>
+        <v>1520.53</v>
       </c>
       <c r="G226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I226">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J226">
-        <v>0</v>
+        <v>1.3153</v>
       </c>
       <c r="K226">
-        <v>0</v>
+        <v>1.3153</v>
       </c>
       <c r="L226" t="s">
         <v>15</v>
@@ -10403,31 +10400,31 @@
         <v>226</v>
       </c>
       <c r="C227">
-        <v>2171</v>
+        <v>997</v>
       </c>
       <c r="D227">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="E227">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F227">
-        <v>2827.43</v>
+        <v>2642.08</v>
       </c>
       <c r="G227">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H227">
-        <v>191</v>
+        <v>71</v>
       </c>
       <c r="I227">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="J227">
-        <v>6.7552</v>
+        <v>2.6873</v>
       </c>
       <c r="K227">
-        <v>3.8551</v>
+        <v>1.7032</v>
       </c>
       <c r="L227" t="s">
         <v>15</v>
@@ -10447,31 +10444,31 @@
         <v>227</v>
       </c>
       <c r="C228">
-        <v>694</v>
+        <v>1397</v>
       </c>
       <c r="D228">
-        <v>1574</v>
+        <v>1570</v>
       </c>
       <c r="E228">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F228">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G228">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H228">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="I228">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J228">
-        <v>3.0658</v>
+        <v>0</v>
       </c>
       <c r="K228">
-        <v>1.7032</v>
+        <v>0</v>
       </c>
       <c r="L228" t="s">
         <v>15</v>
@@ -10491,31 +10488,31 @@
         <v>228</v>
       </c>
       <c r="C229">
-        <v>797</v>
+        <v>2174</v>
       </c>
       <c r="D229">
         <v>1571</v>
       </c>
       <c r="E229">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F229">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G229">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H229">
-        <v>105</v>
+        <v>216</v>
       </c>
       <c r="I229">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="J229">
-        <v>4.2631</v>
+        <v>8.1754</v>
       </c>
       <c r="K229">
-        <v>2.7203</v>
+        <v>4.1634</v>
       </c>
       <c r="L229" t="s">
         <v>15</v>
@@ -10535,31 +10532,31 @@
         <v>229</v>
       </c>
       <c r="C230">
-        <v>895</v>
+        <v>1092</v>
       </c>
       <c r="D230">
-        <v>1568</v>
+        <v>1571</v>
       </c>
       <c r="E230">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F230">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H230">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="I230">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J230">
-        <v>2.016</v>
+        <v>1.0556</v>
       </c>
       <c r="K230">
-        <v>1.4147</v>
+        <v>1.0556</v>
       </c>
       <c r="L230" t="s">
         <v>15</v>
@@ -10579,31 +10576,31 @@
         <v>230</v>
       </c>
       <c r="C231">
-        <v>1001</v>
+        <v>1192</v>
       </c>
       <c r="D231">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="E231">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F231">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G231">
         <v>2</v>
       </c>
       <c r="H231">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="I231">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="J231">
-        <v>2.5111</v>
+        <v>2.3548</v>
       </c>
       <c r="K231">
-        <v>1.5915</v>
+        <v>1.2992</v>
       </c>
       <c r="L231" t="s">
         <v>15</v>
@@ -10623,7 +10620,7 @@
         <v>231</v>
       </c>
       <c r="C232">
-        <v>1092</v>
+        <v>1290</v>
       </c>
       <c r="D232">
         <v>1571</v>
@@ -10635,19 +10632,19 @@
         <v>2463.01</v>
       </c>
       <c r="G232">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H232">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="I232">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J232">
-        <v>1.0556</v>
+        <v>4.6285</v>
       </c>
       <c r="K232">
-        <v>1.0556</v>
+        <v>1.1368</v>
       </c>
       <c r="L232" t="s">
         <v>15</v>
@@ -10667,31 +10664,31 @@
         <v>232</v>
       </c>
       <c r="C233">
-        <v>1192</v>
+        <v>1492</v>
       </c>
       <c r="D233">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="E233">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F233">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H233">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="I233">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J233">
-        <v>2.3548</v>
+        <v>1.061</v>
       </c>
       <c r="K233">
-        <v>1.2992</v>
+        <v>1.061</v>
       </c>
       <c r="L233" t="s">
         <v>15</v>
@@ -10711,7 +10708,7 @@
         <v>233</v>
       </c>
       <c r="C234">
-        <v>1290</v>
+        <v>1585</v>
       </c>
       <c r="D234">
         <v>1571</v>
@@ -10723,19 +10720,19 @@
         <v>2463.01</v>
       </c>
       <c r="G234">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H234">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="I234">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="J234">
-        <v>4.6285</v>
+        <v>2.3548</v>
       </c>
       <c r="K234">
-        <v>1.1368</v>
+        <v>2.3548</v>
       </c>
       <c r="L234" t="s">
         <v>15</v>
@@ -10755,31 +10752,31 @@
         <v>234</v>
       </c>
       <c r="C235">
-        <v>1492</v>
+        <v>1684</v>
       </c>
       <c r="D235">
         <v>1572</v>
       </c>
       <c r="E235">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F235">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G235">
         <v>1</v>
       </c>
       <c r="H235">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I235">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J235">
-        <v>1.061</v>
+        <v>0.7308</v>
       </c>
       <c r="K235">
-        <v>1.061</v>
+        <v>0.7308</v>
       </c>
       <c r="L235" t="s">
         <v>15</v>
@@ -10799,31 +10796,31 @@
         <v>235</v>
       </c>
       <c r="C236">
-        <v>1585</v>
+        <v>1781</v>
       </c>
       <c r="D236">
         <v>1571</v>
       </c>
       <c r="E236">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F236">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H236">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="I236">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="J236">
-        <v>2.3548</v>
+        <v>0</v>
       </c>
       <c r="K236">
-        <v>2.3548</v>
+        <v>0</v>
       </c>
       <c r="L236" t="s">
         <v>15</v>
@@ -10843,31 +10840,31 @@
         <v>236</v>
       </c>
       <c r="C237">
-        <v>1684</v>
+        <v>1879</v>
       </c>
       <c r="D237">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="E237">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F237">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G237">
         <v>1</v>
       </c>
       <c r="H237">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="I237">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="J237">
-        <v>0.7308</v>
+        <v>1.6654</v>
       </c>
       <c r="K237">
-        <v>0.7308</v>
+        <v>1.6654</v>
       </c>
       <c r="L237" t="s">
         <v>15</v>
@@ -10887,7 +10884,7 @@
         <v>237</v>
       </c>
       <c r="C238">
-        <v>1781</v>
+        <v>1977</v>
       </c>
       <c r="D238">
         <v>1571</v>
@@ -10899,19 +10896,19 @@
         <v>2642.08</v>
       </c>
       <c r="G238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H238">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I238">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J238">
-        <v>0</v>
+        <v>2.3845</v>
       </c>
       <c r="K238">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="L238" t="s">
         <v>15</v>
@@ -10931,31 +10928,31 @@
         <v>238</v>
       </c>
       <c r="C239">
-        <v>1879</v>
+        <v>2076</v>
       </c>
       <c r="D239">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="E239">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F239">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H239">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="I239">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J239">
-        <v>1.6654</v>
+        <v>3.1263</v>
       </c>
       <c r="K239">
-        <v>1.6654</v>
+        <v>1.9082</v>
       </c>
       <c r="L239" t="s">
         <v>15</v>
@@ -10975,31 +10972,31 @@
         <v>239</v>
       </c>
       <c r="C240">
-        <v>1977</v>
+        <v>923</v>
       </c>
       <c r="D240">
-        <v>1571</v>
+        <v>1587</v>
       </c>
       <c r="E240">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F240">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G240">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H240">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="I240">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J240">
-        <v>2.3845</v>
+        <v>0</v>
       </c>
       <c r="K240">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="L240" t="s">
         <v>15</v>
@@ -11019,31 +11016,31 @@
         <v>240</v>
       </c>
       <c r="C241">
-        <v>2076</v>
+        <v>703</v>
       </c>
       <c r="D241">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="E241">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F241">
-        <v>2463.01</v>
+        <v>1661.9</v>
       </c>
       <c r="G241">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H241">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="I241">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J241">
-        <v>3.1263</v>
+        <v>2.2264</v>
       </c>
       <c r="K241">
-        <v>1.9082</v>
+        <v>2.2264</v>
       </c>
       <c r="L241" t="s">
         <v>15</v>
@@ -11063,31 +11060,31 @@
         <v>241</v>
       </c>
       <c r="C242">
-        <v>695</v>
+        <v>841</v>
       </c>
       <c r="D242">
-        <v>1643</v>
+        <v>1613</v>
       </c>
       <c r="E242">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F242">
-        <v>2642.08</v>
+        <v>1520.53</v>
       </c>
       <c r="G242">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H242">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="I242">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="J242">
-        <v>5.261</v>
+        <v>0</v>
       </c>
       <c r="K242">
-        <v>2.0438</v>
+        <v>0</v>
       </c>
       <c r="L242" t="s">
         <v>15</v>
@@ -11107,31 +11104,31 @@
         <v>242</v>
       </c>
       <c r="C243">
-        <v>1094</v>
+        <v>1965</v>
       </c>
       <c r="D243">
-        <v>1648</v>
+        <v>1622</v>
       </c>
       <c r="E243">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F243">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G243">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H243">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="I243">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J243">
-        <v>2.4757</v>
+        <v>0.9169</v>
       </c>
       <c r="K243">
-        <v>1.4501</v>
+        <v>0.9169</v>
       </c>
       <c r="L243" t="s">
         <v>15</v>
@@ -11151,31 +11148,31 @@
         <v>243</v>
       </c>
       <c r="C244">
-        <v>1190</v>
+        <v>1109</v>
       </c>
       <c r="D244">
-        <v>1644</v>
+        <v>1623</v>
       </c>
       <c r="E244">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F244">
-        <v>2642.08</v>
+        <v>1963.5</v>
       </c>
       <c r="G244">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H244">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="I244">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J244">
-        <v>2.9901</v>
+        <v>0</v>
       </c>
       <c r="K244">
-        <v>1.5518</v>
+        <v>0</v>
       </c>
       <c r="L244" t="s">
         <v>15</v>
@@ -11195,31 +11192,31 @@
         <v>244</v>
       </c>
       <c r="C245">
-        <v>2086</v>
+        <v>2081</v>
       </c>
       <c r="D245">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="E245">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F245">
-        <v>2642.08</v>
+        <v>2290.22</v>
       </c>
       <c r="G245">
         <v>2</v>
       </c>
       <c r="H245">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I245">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J245">
-        <v>2.3088</v>
+        <v>2.5762</v>
       </c>
       <c r="K245">
-        <v>1.2112</v>
+        <v>1.3536</v>
       </c>
       <c r="L245" t="s">
         <v>15</v>
@@ -11239,31 +11236,31 @@
         <v>245</v>
       </c>
       <c r="C246">
-        <v>2176</v>
+        <v>1046</v>
       </c>
       <c r="D246">
-        <v>1644</v>
+        <v>1626</v>
       </c>
       <c r="E246">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F246">
-        <v>2123.72</v>
+        <v>1809.56</v>
       </c>
       <c r="G246">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H246">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I246">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="J246">
-        <v>3.1078</v>
+        <v>0</v>
       </c>
       <c r="K246">
-        <v>3.1078</v>
+        <v>0</v>
       </c>
       <c r="L246" t="s">
         <v>15</v>
@@ -11283,31 +11280,31 @@
         <v>246</v>
       </c>
       <c r="C247">
-        <v>1487</v>
+        <v>2158</v>
       </c>
       <c r="D247">
-        <v>1645</v>
+        <v>1627</v>
       </c>
       <c r="E247">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F247">
-        <v>2463.01</v>
+        <v>1809.56</v>
       </c>
       <c r="G247">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H247">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="I247">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J247">
-        <v>2.4766</v>
+        <v>0</v>
       </c>
       <c r="K247">
-        <v>1.5022</v>
+        <v>0</v>
       </c>
       <c r="L247" t="s">
         <v>15</v>
@@ -11327,31 +11324,31 @@
         <v>247</v>
       </c>
       <c r="C248">
-        <v>1586</v>
+        <v>1490</v>
       </c>
       <c r="D248">
-        <v>1645</v>
+        <v>1630</v>
       </c>
       <c r="E248">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F248">
-        <v>2463.01</v>
+        <v>1809.56</v>
       </c>
       <c r="G248">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H248">
-        <v>155</v>
+        <v>24</v>
       </c>
       <c r="I248">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="J248">
-        <v>6.2931</v>
+        <v>1.3263</v>
       </c>
       <c r="K248">
-        <v>2.639</v>
+        <v>1.3263</v>
       </c>
       <c r="L248" t="s">
         <v>15</v>
@@ -11371,31 +11368,31 @@
         <v>248</v>
       </c>
       <c r="C249">
-        <v>1681</v>
+        <v>1588</v>
       </c>
       <c r="D249">
-        <v>1645</v>
+        <v>1631</v>
       </c>
       <c r="E249">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F249">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H249">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I249">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J249">
-        <v>0</v>
+        <v>1.426</v>
       </c>
       <c r="K249">
-        <v>0</v>
+        <v>1.426</v>
       </c>
       <c r="L249" t="s">
         <v>15</v>
@@ -11415,31 +11412,31 @@
         <v>249</v>
       </c>
       <c r="C250">
-        <v>1777</v>
+        <v>1685</v>
       </c>
       <c r="D250">
-        <v>1645</v>
+        <v>1631</v>
       </c>
       <c r="E250">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F250">
-        <v>1809.56</v>
+        <v>1963.5</v>
       </c>
       <c r="G250">
         <v>1</v>
       </c>
       <c r="H250">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I250">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J250">
-        <v>1.05</v>
+        <v>0.8658</v>
       </c>
       <c r="K250">
-        <v>1.05</v>
+        <v>0.8658</v>
       </c>
       <c r="L250" t="s">
         <v>15</v>
@@ -11459,31 +11456,31 @@
         <v>250</v>
       </c>
       <c r="C251">
-        <v>995</v>
+        <v>1780</v>
       </c>
       <c r="D251">
-        <v>1647</v>
+        <v>1632</v>
       </c>
       <c r="E251">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F251">
-        <v>2827.43</v>
+        <v>2123.72</v>
       </c>
       <c r="G251">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H251">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I251">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J251">
-        <v>1.3793</v>
+        <v>0.8005</v>
       </c>
       <c r="K251">
-        <v>0.7427</v>
+        <v>0.8005</v>
       </c>
       <c r="L251" t="s">
         <v>15</v>
@@ -11503,31 +11500,31 @@
         <v>251</v>
       </c>
       <c r="C252">
-        <v>1894</v>
+        <v>1390</v>
       </c>
       <c r="D252">
-        <v>1652</v>
+        <v>1635</v>
       </c>
       <c r="E252">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F252">
-        <v>2827.43</v>
+        <v>1809.56</v>
       </c>
       <c r="G252">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H252">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="I252">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="J252">
-        <v>3.2538</v>
+        <v>0</v>
       </c>
       <c r="K252">
-        <v>2.5111</v>
+        <v>0</v>
       </c>
       <c r="L252" t="s">
         <v>15</v>
@@ -11547,10 +11544,10 @@
         <v>252</v>
       </c>
       <c r="C253">
-        <v>901</v>
+        <v>1890</v>
       </c>
       <c r="D253">
-        <v>1654</v>
+        <v>1649</v>
       </c>
       <c r="E253">
         <v>60</v>
@@ -11559,19 +11556,19 @@
         <v>2827.43</v>
       </c>
       <c r="G253">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H253">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="I253">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="J253">
-        <v>2.405</v>
+        <v>3.2538</v>
       </c>
       <c r="K253">
-        <v>0.9903</v>
+        <v>2.5111</v>
       </c>
       <c r="L253" t="s">
         <v>15</v>
@@ -11591,16 +11588,16 @@
         <v>253</v>
       </c>
       <c r="C254">
-        <v>1399</v>
+        <v>2160</v>
       </c>
       <c r="D254">
-        <v>1654</v>
+        <v>650</v>
       </c>
       <c r="E254">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F254">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G254">
         <v>0</v>
@@ -11621,10 +11618,10 @@
         <v>15</v>
       </c>
       <c r="M254" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N254">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="255" spans="1:14">
@@ -11635,31 +11632,31 @@
         <v>254</v>
       </c>
       <c r="C255">
-        <v>1277</v>
+        <v>698</v>
       </c>
       <c r="D255">
-        <v>1655</v>
+        <v>1643</v>
       </c>
       <c r="E255">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F255">
-        <v>2827.43</v>
+        <v>2123.72</v>
       </c>
       <c r="G255">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H255">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="I255">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="J255">
-        <v>0.6012999999999999</v>
+        <v>5.1796</v>
       </c>
       <c r="K255">
-        <v>0.6012999999999999</v>
+        <v>2.6369</v>
       </c>
       <c r="L255" t="s">
         <v>15</v>
@@ -11668,7 +11665,7 @@
         <v>0</v>
       </c>
       <c r="N255">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="256" spans="1:14">
@@ -11679,40 +11676,40 @@
         <v>255</v>
       </c>
       <c r="C256">
-        <v>816</v>
+        <v>910</v>
       </c>
       <c r="D256">
-        <v>1667</v>
+        <v>1650</v>
       </c>
       <c r="E256">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F256">
-        <v>2827.43</v>
+        <v>2123.72</v>
       </c>
       <c r="G256">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H256">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="I256">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="J256">
-        <v>1.2732</v>
+        <v>3.767</v>
       </c>
       <c r="K256">
-        <v>1.2732</v>
+        <v>1.3184</v>
       </c>
       <c r="L256" t="s">
         <v>15</v>
       </c>
       <c r="M256" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N256">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="257" spans="1:14">
@@ -11723,31 +11720,31 @@
         <v>256</v>
       </c>
       <c r="C257">
-        <v>1880</v>
+        <v>1190</v>
       </c>
       <c r="D257">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="E257">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F257">
-        <v>1809.56</v>
+        <v>2463.01</v>
       </c>
       <c r="G257">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H257">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="I257">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J257">
-        <v>1.1605</v>
+        <v>1.7052</v>
       </c>
       <c r="K257">
-        <v>1.1605</v>
+        <v>1.015</v>
       </c>
       <c r="L257" t="s">
         <v>15</v>
@@ -11756,6 +11753,50 @@
         <v>0</v>
       </c>
       <c r="N257">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14">
+      <c r="A258" t="s">
+        <v>14</v>
+      </c>
+      <c r="B258">
+        <v>257</v>
+      </c>
+      <c r="C258">
+        <v>1288</v>
+      </c>
+      <c r="D258">
+        <v>1650</v>
+      </c>
+      <c r="E258">
+        <v>60</v>
+      </c>
+      <c r="F258">
+        <v>2827.43</v>
+      </c>
+      <c r="G258">
+        <v>1</v>
+      </c>
+      <c r="H258">
+        <v>17</v>
+      </c>
+      <c r="I258">
+        <v>17</v>
+      </c>
+      <c r="J258">
+        <v>0.6012999999999999</v>
+      </c>
+      <c r="K258">
+        <v>0.6012999999999999</v>
+      </c>
+      <c r="L258" t="s">
+        <v>15</v>
+      </c>
+      <c r="M258" t="b">
+        <v>1</v>
+      </c>
+      <c r="N258">
         <v>0.2</v>
       </c>
     </row>
@@ -11788,40 +11829,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>26</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>27</v>
-      </c>
-      <c r="M1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -11829,13 +11870,13 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C2">
-        <v>1.5254</v>
+        <v>1.3549</v>
       </c>
       <c r="D2">
-        <v>12.1874</v>
+        <v>9.866</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -11844,7 +11885,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2">
         <v>25</v>
@@ -11853,16 +11894,16 @@
         <v>12</v>
       </c>
       <c r="J2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Images_BGA/Results/Reports/PCBA1_08_inspection_report.xlsx
+++ b/Images_BGA/Results/Reports/PCBA1_08_inspection_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="28">
   <si>
     <t>image_name</t>
   </si>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N258"/>
+  <dimension ref="A1:N257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -588,16 +588,16 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>812</v>
+        <v>928</v>
       </c>
       <c r="D4">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="E4">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F4">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -632,31 +632,31 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>910</v>
+        <v>750</v>
       </c>
       <c r="D5">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="E5">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F5">
-        <v>2463.01</v>
+        <v>2123.72</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="I5">
-        <v>243</v>
+        <v>35</v>
       </c>
       <c r="J5">
-        <v>9.866</v>
+        <v>3.8141</v>
       </c>
       <c r="K5">
-        <v>9.866</v>
+        <v>1.6481</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -676,31 +676,31 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>2006</v>
+        <v>1017</v>
       </c>
       <c r="D6">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="E6">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F6">
-        <v>2463.01</v>
+        <v>2123.72</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I6">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J6">
-        <v>1.9082</v>
+        <v>1.7893</v>
       </c>
       <c r="K6">
-        <v>1.1368</v>
+        <v>1.7893</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -720,31 +720,31 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>2092</v>
+        <v>1195</v>
       </c>
       <c r="D7">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="E7">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F7">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1.5897</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1.5897</v>
       </c>
       <c r="L7" t="s">
         <v>15</v>
@@ -764,31 +764,31 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>1017</v>
+        <v>1284</v>
       </c>
       <c r="D8">
         <v>650</v>
       </c>
       <c r="E8">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F8">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I8">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J8">
-        <v>1.7893</v>
+        <v>1.1714</v>
       </c>
       <c r="K8">
-        <v>1.7893</v>
+        <v>1.1714</v>
       </c>
       <c r="L8" t="s">
         <v>15</v>
@@ -808,31 +808,31 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>1195</v>
+        <v>1372</v>
       </c>
       <c r="D9">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="E9">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>2463.01</v>
+        <v>1963.5</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I9">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="J9">
-        <v>1.7052</v>
+        <v>1.0186</v>
       </c>
       <c r="K9">
-        <v>1.7052</v>
+        <v>1.0186</v>
       </c>
       <c r="L9" t="s">
         <v>15</v>
@@ -852,31 +852,31 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>1284</v>
+        <v>1452</v>
       </c>
       <c r="D10">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F10">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>1.1714</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>1.1714</v>
+        <v>0</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -896,31 +896,31 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>1372</v>
+        <v>1551</v>
       </c>
       <c r="D11">
         <v>650</v>
       </c>
       <c r="E11">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F11">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="I11">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J11">
-        <v>1.0186</v>
+        <v>2.4485</v>
       </c>
       <c r="K11">
-        <v>1.0186</v>
+        <v>1.3184</v>
       </c>
       <c r="L11" t="s">
         <v>15</v>
@@ -940,31 +940,31 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>1453</v>
+        <v>1640</v>
       </c>
       <c r="D12">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="E12">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F12">
-        <v>2642.08</v>
+        <v>2123.72</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>2.4015</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1.5539</v>
       </c>
       <c r="L12" t="s">
         <v>15</v>
@@ -984,31 +984,31 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>1551</v>
+        <v>1730</v>
       </c>
       <c r="D13">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E13">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F13">
-        <v>2123.72</v>
+        <v>1963.5</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="I13">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="J13">
-        <v>2.4485</v>
+        <v>1.9863</v>
       </c>
       <c r="K13">
-        <v>1.3184</v>
+        <v>1.9863</v>
       </c>
       <c r="L13" t="s">
         <v>15</v>
@@ -1028,31 +1028,31 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>1640</v>
+        <v>1909</v>
       </c>
       <c r="D14">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="E14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F14">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>2.4015</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>1.5539</v>
+        <v>0</v>
       </c>
       <c r="L14" t="s">
         <v>15</v>
@@ -1072,31 +1072,31 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>1730</v>
+        <v>2091</v>
       </c>
       <c r="D15">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E15">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F15">
-        <v>1963.5</v>
+        <v>2123.72</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>1.9863</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>1.9863</v>
+        <v>0</v>
       </c>
       <c r="L15" t="s">
         <v>15</v>
@@ -1116,10 +1116,10 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>1908</v>
+        <v>839</v>
       </c>
       <c r="D16">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="E16">
         <v>54</v>
@@ -1128,19 +1128,19 @@
         <v>2290.22</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>2.2269</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1.3099</v>
       </c>
       <c r="L16" t="s">
         <v>15</v>
@@ -1160,31 +1160,31 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>742</v>
+        <v>2004</v>
       </c>
       <c r="D17">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="E17">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F17">
-        <v>1520.53</v>
+        <v>2290.22</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I17">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="J17">
-        <v>3.3541</v>
+        <v>2.0959</v>
       </c>
       <c r="K17">
-        <v>3.3541</v>
+        <v>1.2663</v>
       </c>
       <c r="L17" t="s">
         <v>15</v>
@@ -1204,31 +1204,31 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>824</v>
+        <v>2006</v>
       </c>
       <c r="D18">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E18">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F18">
-        <v>2827.43</v>
+        <v>2123.72</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>3.6075</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>1.5915</v>
+        <v>0</v>
       </c>
       <c r="L18" t="s">
         <v>15</v>
@@ -1248,31 +1248,31 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>913</v>
+        <v>747</v>
       </c>
       <c r="D19">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="E19">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F19">
-        <v>2827.43</v>
+        <v>2123.72</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="I19">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="J19">
-        <v>1.6269</v>
+        <v>3.6728</v>
       </c>
       <c r="K19">
-        <v>0.9196</v>
+        <v>3.6728</v>
       </c>
       <c r="L19" t="s">
         <v>15</v>
@@ -1292,31 +1292,31 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>2111</v>
+        <v>1015</v>
       </c>
       <c r="D20">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="E20">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F20">
-        <v>2827.43</v>
+        <v>2123.72</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>254</v>
+        <v>24</v>
       </c>
       <c r="I20">
-        <v>220</v>
+        <v>24</v>
       </c>
       <c r="J20">
-        <v>8.9834</v>
+        <v>1.1301</v>
       </c>
       <c r="K20">
-        <v>7.7809</v>
+        <v>1.1301</v>
       </c>
       <c r="L20" t="s">
         <v>15</v>
@@ -1336,16 +1336,16 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>2007</v>
+        <v>1186</v>
       </c>
       <c r="D21">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="E21">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F21">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>747</v>
+        <v>1374</v>
       </c>
       <c r="D22">
         <v>710</v>
@@ -1392,19 +1392,19 @@
         <v>2123.72</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>3.6728</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>3.6728</v>
+        <v>0</v>
       </c>
       <c r="L22" t="s">
         <v>15</v>
@@ -1424,31 +1424,31 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>1008</v>
+        <v>1464</v>
       </c>
       <c r="D23">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="E23">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F23">
-        <v>2463.01</v>
+        <v>2123.72</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I23">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J23">
-        <v>1.0962</v>
+        <v>0.8005</v>
       </c>
       <c r="K23">
-        <v>1.0962</v>
+        <v>0.8005</v>
       </c>
       <c r="L23" t="s">
         <v>15</v>
@@ -1468,31 +1468,31 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>1187</v>
+        <v>1555</v>
       </c>
       <c r="D24">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="E24">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F24">
-        <v>2290.22</v>
+        <v>1963.5</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1.5279</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1.5279</v>
       </c>
       <c r="L24" t="s">
         <v>15</v>
@@ -1512,7 +1512,7 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>1374</v>
+        <v>1733</v>
       </c>
       <c r="D25">
         <v>710</v>
@@ -1524,19 +1524,19 @@
         <v>2123.72</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1.0359</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1.0359</v>
       </c>
       <c r="L25" t="s">
         <v>15</v>
@@ -1556,7 +1556,7 @@
         <v>25</v>
       </c>
       <c r="C26">
-        <v>1464</v>
+        <v>1822</v>
       </c>
       <c r="D26">
         <v>710</v>
@@ -1600,31 +1600,31 @@
         <v>26</v>
       </c>
       <c r="C27">
-        <v>1555</v>
+        <v>1919</v>
       </c>
       <c r="D27">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="E27">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F27">
-        <v>1963.5</v>
+        <v>2463.01</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I27">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J27">
-        <v>1.5279</v>
+        <v>0.7308</v>
       </c>
       <c r="K27">
-        <v>1.5279</v>
+        <v>0.7308</v>
       </c>
       <c r="L27" t="s">
         <v>15</v>
@@ -1644,10 +1644,10 @@
         <v>27</v>
       </c>
       <c r="C28">
-        <v>1733</v>
+        <v>826</v>
       </c>
       <c r="D28">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="E28">
         <v>52</v>
@@ -1656,19 +1656,19 @@
         <v>2123.72</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="I28">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J28">
-        <v>1.0359</v>
+        <v>4.0495</v>
       </c>
       <c r="K28">
-        <v>1.0359</v>
+        <v>1.9306</v>
       </c>
       <c r="L28" t="s">
         <v>15</v>
@@ -1688,10 +1688,10 @@
         <v>28</v>
       </c>
       <c r="C29">
-        <v>1822</v>
+        <v>1645</v>
       </c>
       <c r="D29">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E29">
         <v>52</v>
@@ -1700,19 +1700,19 @@
         <v>2123.72</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>0.8005</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>0.8005</v>
+        <v>0</v>
       </c>
       <c r="L29" t="s">
         <v>15</v>
@@ -1732,31 +1732,31 @@
         <v>29</v>
       </c>
       <c r="C30">
-        <v>1919</v>
+        <v>1099</v>
       </c>
       <c r="D30">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="E30">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F30">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="I30">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J30">
-        <v>0.786</v>
+        <v>2.233</v>
       </c>
       <c r="K30">
-        <v>0.786</v>
+        <v>0.8526</v>
       </c>
       <c r="L30" t="s">
         <v>15</v>
@@ -1776,31 +1776,31 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>1270</v>
+        <v>926</v>
       </c>
       <c r="D31">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E31">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F31">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>2.1112</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1.0556</v>
       </c>
       <c r="L31" t="s">
         <v>15</v>
@@ -1820,16 +1820,16 @@
         <v>31</v>
       </c>
       <c r="C32">
-        <v>1645</v>
+        <v>1285</v>
       </c>
       <c r="D32">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E32">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F32">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1864,10 +1864,10 @@
         <v>32</v>
       </c>
       <c r="C33">
-        <v>1096</v>
+        <v>2098</v>
       </c>
       <c r="D33">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="E33">
         <v>60</v>
@@ -1876,19 +1876,19 @@
         <v>2827.43</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="I33">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="J33">
-        <v>1.8391</v>
+        <v>1.2025</v>
       </c>
       <c r="K33">
-        <v>0.6366000000000001</v>
+        <v>1.2025</v>
       </c>
       <c r="L33" t="s">
         <v>15</v>
@@ -1908,10 +1908,10 @@
         <v>33</v>
       </c>
       <c r="C34">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="D34">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="E34">
         <v>54</v>
@@ -1955,13 +1955,13 @@
         <v>833</v>
       </c>
       <c r="D35">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="E35">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F35">
-        <v>2642.08</v>
+        <v>2290.22</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -1973,10 +1973,10 @@
         <v>16</v>
       </c>
       <c r="J35">
-        <v>0.6056</v>
+        <v>0.6986</v>
       </c>
       <c r="K35">
-        <v>0.6056</v>
+        <v>0.6986</v>
       </c>
       <c r="L35" t="s">
         <v>15</v>
@@ -1996,16 +1996,16 @@
         <v>35</v>
       </c>
       <c r="C36">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D36">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E36">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F36">
-        <v>2827.43</v>
+        <v>2123.72</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>36</v>
       </c>
       <c r="C37">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="D37">
         <v>768</v>
@@ -2084,16 +2084,16 @@
         <v>37</v>
       </c>
       <c r="C38">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D38">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E38">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F38">
-        <v>2123.72</v>
+        <v>2290.22</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2105,10 +2105,10 @@
         <v>18</v>
       </c>
       <c r="J38">
-        <v>0.8476</v>
+        <v>0.786</v>
       </c>
       <c r="K38">
-        <v>0.8476</v>
+        <v>0.786</v>
       </c>
       <c r="L38" t="s">
         <v>15</v>
@@ -2392,16 +2392,16 @@
         <v>44</v>
       </c>
       <c r="C45">
-        <v>1834</v>
+        <v>1826</v>
       </c>
       <c r="D45">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="E45">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F45">
-        <v>2463.01</v>
+        <v>2123.72</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -2436,16 +2436,16 @@
         <v>45</v>
       </c>
       <c r="C46">
-        <v>1910</v>
+        <v>1906</v>
       </c>
       <c r="D46">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="E46">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F46">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2457,10 +2457,10 @@
         <v>16</v>
       </c>
       <c r="J46">
-        <v>0.6986</v>
+        <v>0.6496</v>
       </c>
       <c r="K46">
-        <v>0.6986</v>
+        <v>0.6496</v>
       </c>
       <c r="L46" t="s">
         <v>15</v>
@@ -2480,16 +2480,16 @@
         <v>46</v>
       </c>
       <c r="C47">
-        <v>2030</v>
+        <v>2103</v>
       </c>
       <c r="D47">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="E47">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F47">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -2568,31 +2568,31 @@
         <v>48</v>
       </c>
       <c r="C49">
-        <v>2115</v>
+        <v>2006</v>
       </c>
       <c r="D49">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="E49">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F49">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>9.160299999999999</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>9.160299999999999</v>
+        <v>0</v>
       </c>
       <c r="L49" t="s">
         <v>15</v>
@@ -2700,31 +2700,31 @@
         <v>51</v>
       </c>
       <c r="C52">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="D52">
         <v>828</v>
       </c>
       <c r="E52">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F52">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>0.8733</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>0.8733</v>
       </c>
       <c r="L52" t="s">
         <v>15</v>
@@ -2879,7 +2879,7 @@
         <v>1013</v>
       </c>
       <c r="D56">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E56">
         <v>56</v>
@@ -2920,7 +2920,7 @@
         <v>56</v>
       </c>
       <c r="C57">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D57">
         <v>831</v>
@@ -2935,13 +2935,13 @@
         <v>2</v>
       </c>
       <c r="H57">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I57">
         <v>49</v>
       </c>
       <c r="J57">
-        <v>2.8818</v>
+        <v>2.9691</v>
       </c>
       <c r="K57">
         <v>2.1395</v>
@@ -2967,7 +2967,7 @@
         <v>1190</v>
       </c>
       <c r="D58">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E58">
         <v>54</v>
@@ -3099,7 +3099,7 @@
         <v>1736</v>
       </c>
       <c r="D61">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E61">
         <v>54</v>
@@ -3187,7 +3187,7 @@
         <v>1927</v>
       </c>
       <c r="D63">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E63">
         <v>58</v>
@@ -3228,31 +3228,31 @@
         <v>63</v>
       </c>
       <c r="C64">
-        <v>2020</v>
+        <v>2107</v>
       </c>
       <c r="D64">
-        <v>839</v>
+        <v>828</v>
       </c>
       <c r="E64">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F64">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="I64">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="J64">
-        <v>3.6947</v>
+        <v>0</v>
       </c>
       <c r="K64">
-        <v>3.0045</v>
+        <v>0</v>
       </c>
       <c r="L64" t="s">
         <v>15</v>
@@ -3272,31 +3272,31 @@
         <v>64</v>
       </c>
       <c r="C65">
-        <v>2124</v>
+        <v>2017</v>
       </c>
       <c r="D65">
-        <v>847</v>
+        <v>838</v>
       </c>
       <c r="E65">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F65">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>3.6947</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>3.0045</v>
       </c>
       <c r="L65" t="s">
         <v>15</v>
@@ -3448,7 +3448,7 @@
         <v>68</v>
       </c>
       <c r="C69">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="D69">
         <v>894</v>
@@ -3536,10 +3536,10 @@
         <v>70</v>
       </c>
       <c r="C71">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="D71">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E71">
         <v>54</v>
@@ -3551,16 +3551,16 @@
         <v>2</v>
       </c>
       <c r="H71">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I71">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="J71">
-        <v>2.4015</v>
+        <v>3.6241</v>
       </c>
       <c r="K71">
-        <v>1.7029</v>
+        <v>2.0522</v>
       </c>
       <c r="L71" t="s">
         <v>15</v>
@@ -3583,7 +3583,7 @@
         <v>1192</v>
       </c>
       <c r="D72">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E72">
         <v>56</v>
@@ -3624,31 +3624,31 @@
         <v>72</v>
       </c>
       <c r="C73">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="D73">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="E73">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F73">
-        <v>2642.08</v>
+        <v>2290.22</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I73">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J73">
-        <v>0.8327</v>
+        <v>0.7423</v>
       </c>
       <c r="K73">
-        <v>0.8327</v>
+        <v>0.7423</v>
       </c>
       <c r="L73" t="s">
         <v>15</v>
@@ -3800,16 +3800,16 @@
         <v>76</v>
       </c>
       <c r="C77">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="D77">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="E77">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F77">
-        <v>2642.08</v>
+        <v>2290.22</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -3844,31 +3844,31 @@
         <v>77</v>
       </c>
       <c r="C78">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="D78">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="E78">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F78">
-        <v>2642.08</v>
+        <v>2290.22</v>
       </c>
       <c r="G78">
         <v>1</v>
       </c>
       <c r="H78">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="I78">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="J78">
-        <v>1.6654</v>
+        <v>1.0916</v>
       </c>
       <c r="K78">
-        <v>1.6654</v>
+        <v>1.0916</v>
       </c>
       <c r="L78" t="s">
         <v>15</v>
@@ -3888,10 +3888,10 @@
         <v>78</v>
       </c>
       <c r="C79">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="D79">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E79">
         <v>54</v>
@@ -3903,16 +3903,16 @@
         <v>1</v>
       </c>
       <c r="H79">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I79">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J79">
-        <v>1.3099</v>
+        <v>1.2226</v>
       </c>
       <c r="K79">
-        <v>1.3099</v>
+        <v>1.2226</v>
       </c>
       <c r="L79" t="s">
         <v>15</v>
@@ -3976,10 +3976,10 @@
         <v>80</v>
       </c>
       <c r="C81">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="D81">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E81">
         <v>60</v>
@@ -4064,31 +4064,31 @@
         <v>82</v>
       </c>
       <c r="C83">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="D83">
         <v>958</v>
       </c>
       <c r="E83">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F83">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G83">
         <v>2</v>
       </c>
       <c r="H83">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I83">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J83">
-        <v>1.3086</v>
+        <v>2.1395</v>
       </c>
       <c r="K83">
-        <v>0.7074</v>
+        <v>1.2663</v>
       </c>
       <c r="L83" t="s">
         <v>15</v>
@@ -4108,7 +4108,7 @@
         <v>83</v>
       </c>
       <c r="C84">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D84">
         <v>960</v>
@@ -4120,16 +4120,16 @@
         <v>2290.22</v>
       </c>
       <c r="G84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H84">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="I84">
         <v>22</v>
       </c>
       <c r="J84">
-        <v>3.5804</v>
+        <v>2.7508</v>
       </c>
       <c r="K84">
         <v>0.9606</v>
@@ -4152,31 +4152,31 @@
         <v>84</v>
       </c>
       <c r="C85">
-        <v>1201</v>
+        <v>1838</v>
       </c>
       <c r="D85">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="E85">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F85">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H85">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="I85">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J85">
-        <v>1.6623</v>
+        <v>4.1044</v>
       </c>
       <c r="K85">
-        <v>0.8842</v>
+        <v>1.7029</v>
       </c>
       <c r="L85" t="s">
         <v>15</v>
@@ -4196,7 +4196,7 @@
         <v>85</v>
       </c>
       <c r="C86">
-        <v>1838</v>
+        <v>1931</v>
       </c>
       <c r="D86">
         <v>958</v>
@@ -4208,19 +4208,19 @@
         <v>2290.22</v>
       </c>
       <c r="G86">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="I86">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J86">
-        <v>4.1044</v>
+        <v>0</v>
       </c>
       <c r="K86">
-        <v>1.7029</v>
+        <v>0</v>
       </c>
       <c r="L86" t="s">
         <v>15</v>
@@ -4240,10 +4240,10 @@
         <v>86</v>
       </c>
       <c r="C87">
-        <v>1931</v>
+        <v>1010</v>
       </c>
       <c r="D87">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="E87">
         <v>54</v>
@@ -4284,31 +4284,31 @@
         <v>87</v>
       </c>
       <c r="C88">
-        <v>1010</v>
+        <v>1105</v>
       </c>
       <c r="D88">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="E88">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F88">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I88">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>1.7864</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>1.015</v>
       </c>
       <c r="L88" t="s">
         <v>15</v>
@@ -4328,31 +4328,31 @@
         <v>88</v>
       </c>
       <c r="C89">
-        <v>1109</v>
+        <v>1288</v>
       </c>
       <c r="D89">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="E89">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F89">
-        <v>2642.08</v>
+        <v>2290.22</v>
       </c>
       <c r="G89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H89">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I89">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J89">
-        <v>1.7032</v>
+        <v>1.1789</v>
       </c>
       <c r="K89">
-        <v>0.9462</v>
+        <v>1.1789</v>
       </c>
       <c r="L89" t="s">
         <v>15</v>
@@ -4372,31 +4372,31 @@
         <v>89</v>
       </c>
       <c r="C90">
-        <v>1286</v>
+        <v>1379</v>
       </c>
       <c r="D90">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E90">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F90">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I90">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J90">
-        <v>0.9549</v>
+        <v>0</v>
       </c>
       <c r="K90">
-        <v>0.9549</v>
+        <v>0</v>
       </c>
       <c r="L90" t="s">
         <v>15</v>
@@ -4416,31 +4416,31 @@
         <v>90</v>
       </c>
       <c r="C91">
-        <v>1379</v>
+        <v>1473</v>
       </c>
       <c r="D91">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E91">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F91">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I91">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J91">
-        <v>0</v>
+        <v>0.7191</v>
       </c>
       <c r="K91">
-        <v>0</v>
+        <v>0.7191</v>
       </c>
       <c r="L91" t="s">
         <v>15</v>
@@ -4460,31 +4460,31 @@
         <v>91</v>
       </c>
       <c r="C92">
-        <v>1473</v>
+        <v>1565</v>
       </c>
       <c r="D92">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="E92">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F92">
-        <v>2642.08</v>
+        <v>2290.22</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I92">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J92">
-        <v>0.7191</v>
+        <v>0</v>
       </c>
       <c r="K92">
-        <v>0.7191</v>
+        <v>0</v>
       </c>
       <c r="L92" t="s">
         <v>15</v>
@@ -4504,10 +4504,10 @@
         <v>92</v>
       </c>
       <c r="C93">
-        <v>1565</v>
+        <v>1655</v>
       </c>
       <c r="D93">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="E93">
         <v>54</v>
@@ -4516,19 +4516,19 @@
         <v>2290.22</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I93">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J93">
-        <v>0</v>
+        <v>2.7945</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>1.2226</v>
       </c>
       <c r="L93" t="s">
         <v>15</v>
@@ -4548,31 +4548,31 @@
         <v>93</v>
       </c>
       <c r="C94">
-        <v>1654</v>
+        <v>1747</v>
       </c>
       <c r="D94">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E94">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F94">
-        <v>2290.22</v>
+        <v>2463.01</v>
       </c>
       <c r="G94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H94">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="I94">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J94">
-        <v>2.0085</v>
+        <v>0.7308</v>
       </c>
       <c r="K94">
-        <v>1.2226</v>
+        <v>0.7308</v>
       </c>
       <c r="L94" t="s">
         <v>15</v>
@@ -4592,10 +4592,10 @@
         <v>94</v>
       </c>
       <c r="C95">
-        <v>1747</v>
+        <v>1196</v>
       </c>
       <c r="D95">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="E95">
         <v>56</v>
@@ -4607,16 +4607,16 @@
         <v>1</v>
       </c>
       <c r="H95">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="I95">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J95">
-        <v>0.7308</v>
+        <v>1.218</v>
       </c>
       <c r="K95">
-        <v>0.7308</v>
+        <v>1.218</v>
       </c>
       <c r="L95" t="s">
         <v>15</v>
@@ -4636,10 +4636,10 @@
         <v>95</v>
       </c>
       <c r="C96">
-        <v>2120</v>
+        <v>2028</v>
       </c>
       <c r="D96">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="E96">
         <v>60</v>
@@ -4648,19 +4648,19 @@
         <v>2827.43</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I96">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J96">
-        <v>0</v>
+        <v>1.8391</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>1.061</v>
       </c>
       <c r="L96" t="s">
         <v>15</v>
@@ -4680,31 +4680,31 @@
         <v>96</v>
       </c>
       <c r="C97">
-        <v>2033</v>
+        <v>2120</v>
       </c>
       <c r="D97">
-        <v>966</v>
+        <v>953</v>
       </c>
       <c r="E97">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F97">
-        <v>2642.08</v>
+        <v>2827.43</v>
       </c>
       <c r="G97">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="I97">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J97">
-        <v>2.1952</v>
+        <v>0</v>
       </c>
       <c r="K97">
-        <v>1.1733</v>
+        <v>0</v>
       </c>
       <c r="L97" t="s">
         <v>15</v>
@@ -4724,31 +4724,31 @@
         <v>97</v>
       </c>
       <c r="C98">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="D98">
-        <v>1016</v>
+        <v>1023</v>
       </c>
       <c r="E98">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F98">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G98">
         <v>1</v>
       </c>
       <c r="H98">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="I98">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="J98">
-        <v>1.2379</v>
+        <v>0.6986</v>
       </c>
       <c r="K98">
-        <v>1.2379</v>
+        <v>0.6986</v>
       </c>
       <c r="L98" t="s">
         <v>15</v>
@@ -4812,16 +4812,16 @@
         <v>99</v>
       </c>
       <c r="C100">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D100">
         <v>1023</v>
       </c>
       <c r="E100">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F100">
-        <v>2290.22</v>
+        <v>2123.72</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -4856,7 +4856,7 @@
         <v>100</v>
       </c>
       <c r="C101">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D101">
         <v>1023</v>
@@ -5032,10 +5032,10 @@
         <v>104</v>
       </c>
       <c r="C105">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D105">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="E105">
         <v>56</v>
@@ -5164,10 +5164,10 @@
         <v>107</v>
       </c>
       <c r="C108">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="D108">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E108">
         <v>58</v>
@@ -5384,7 +5384,7 @@
         <v>112</v>
       </c>
       <c r="C113">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="D113">
         <v>1016</v>
@@ -5399,13 +5399,13 @@
         <v>2</v>
       </c>
       <c r="H113">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I113">
         <v>21</v>
       </c>
       <c r="J113">
-        <v>1.4147</v>
+        <v>1.344</v>
       </c>
       <c r="K113">
         <v>0.7427</v>
@@ -5472,16 +5472,16 @@
         <v>114</v>
       </c>
       <c r="C115">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="D115">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="E115">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F115">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -5604,16 +5604,16 @@
         <v>117</v>
       </c>
       <c r="C118">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="D118">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="E118">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F118">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -5648,7 +5648,7 @@
         <v>118</v>
       </c>
       <c r="C119">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="D119">
         <v>1089</v>
@@ -5663,13 +5663,13 @@
         <v>2</v>
       </c>
       <c r="H119">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I119">
         <v>33</v>
       </c>
       <c r="J119">
-        <v>1.8924</v>
+        <v>2.0817</v>
       </c>
       <c r="K119">
         <v>1.249</v>
@@ -5736,31 +5736,31 @@
         <v>120</v>
       </c>
       <c r="C121">
-        <v>2041</v>
+        <v>1200</v>
       </c>
       <c r="D121">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="E121">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F121">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G121">
         <v>1</v>
       </c>
       <c r="H121">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I121">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J121">
-        <v>0.8120000000000001</v>
+        <v>2.1832</v>
       </c>
       <c r="K121">
-        <v>0.8120000000000001</v>
+        <v>2.1832</v>
       </c>
       <c r="L121" t="s">
         <v>15</v>
@@ -5780,31 +5780,31 @@
         <v>121</v>
       </c>
       <c r="C122">
-        <v>1947</v>
+        <v>2132</v>
       </c>
       <c r="D122">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="E122">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F122">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G122">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H122">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I122">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="J122">
-        <v>2.5172</v>
+        <v>2.5325</v>
       </c>
       <c r="K122">
-        <v>0.9744</v>
+        <v>2.5325</v>
       </c>
       <c r="L122" t="s">
         <v>15</v>
@@ -5827,28 +5827,28 @@
         <v>1658</v>
       </c>
       <c r="D123">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="E123">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F123">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G123">
         <v>1</v>
       </c>
       <c r="H123">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="I123">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="J123">
-        <v>2.4404</v>
+        <v>3.7988</v>
       </c>
       <c r="K123">
-        <v>2.4404</v>
+        <v>3.7988</v>
       </c>
       <c r="L123" t="s">
         <v>15</v>
@@ -5868,31 +5868,31 @@
         <v>123</v>
       </c>
       <c r="C124">
-        <v>1196</v>
+        <v>1948</v>
       </c>
       <c r="D124">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="E124">
+        <v>56</v>
+      </c>
+      <c r="F124">
+        <v>2463.01</v>
+      </c>
+      <c r="G124">
+        <v>3</v>
+      </c>
+      <c r="H124">
         <v>60</v>
       </c>
-      <c r="F124">
-        <v>2827.43</v>
-      </c>
-      <c r="G124">
-        <v>2</v>
-      </c>
-      <c r="H124">
-        <v>71</v>
-      </c>
       <c r="I124">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="J124">
-        <v>2.5111</v>
+        <v>2.436</v>
       </c>
       <c r="K124">
-        <v>1.6623</v>
+        <v>0.9744</v>
       </c>
       <c r="L124" t="s">
         <v>15</v>
@@ -5912,31 +5912,31 @@
         <v>124</v>
       </c>
       <c r="C125">
-        <v>2129</v>
+        <v>2043</v>
       </c>
       <c r="D125">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="E125">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F125">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G125">
         <v>1</v>
       </c>
       <c r="H125">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="I125">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="J125">
-        <v>2.233</v>
+        <v>0.757</v>
       </c>
       <c r="K125">
-        <v>2.233</v>
+        <v>0.757</v>
       </c>
       <c r="L125" t="s">
         <v>15</v>
@@ -6264,7 +6264,7 @@
         <v>132</v>
       </c>
       <c r="C133">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D133">
         <v>1154</v>
@@ -6279,13 +6279,13 @@
         <v>2</v>
       </c>
       <c r="H133">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I133">
         <v>22</v>
       </c>
       <c r="J133">
-        <v>1.8775</v>
+        <v>1.8339</v>
       </c>
       <c r="K133">
         <v>0.9606</v>
@@ -6484,7 +6484,7 @@
         <v>137</v>
       </c>
       <c r="C138">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="D138">
         <v>1154</v>
@@ -6499,13 +6499,13 @@
         <v>4</v>
       </c>
       <c r="H138">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I138">
         <v>21</v>
       </c>
       <c r="J138">
-        <v>3.2311</v>
+        <v>3.2748</v>
       </c>
       <c r="K138">
         <v>0.9169</v>
@@ -6572,10 +6572,10 @@
         <v>139</v>
       </c>
       <c r="C140">
-        <v>1663</v>
+        <v>1657</v>
       </c>
       <c r="D140">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="E140">
         <v>54</v>
@@ -6584,19 +6584,19 @@
         <v>2290.22</v>
       </c>
       <c r="G140">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H140">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="I140">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J140">
-        <v>1.5719</v>
+        <v>2.7508</v>
       </c>
       <c r="K140">
-        <v>0.786</v>
+        <v>1.1789</v>
       </c>
       <c r="L140" t="s">
         <v>15</v>
@@ -6792,10 +6792,10 @@
         <v>144</v>
       </c>
       <c r="C145">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="D145">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="E145">
         <v>60</v>
@@ -6804,19 +6804,19 @@
         <v>2827.43</v>
       </c>
       <c r="G145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I145">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J145">
-        <v>0.9196</v>
+        <v>0</v>
       </c>
       <c r="K145">
-        <v>0.9196</v>
+        <v>0</v>
       </c>
       <c r="L145" t="s">
         <v>15</v>
@@ -6836,31 +6836,31 @@
         <v>145</v>
       </c>
       <c r="C146">
-        <v>718</v>
+        <v>1298</v>
       </c>
       <c r="D146">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="E146">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F146">
-        <v>2290.22</v>
+        <v>1963.5</v>
       </c>
       <c r="G146">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H146">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="I146">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J146">
-        <v>1.8775</v>
+        <v>3.3614</v>
       </c>
       <c r="K146">
-        <v>1.0479</v>
+        <v>1.5788</v>
       </c>
       <c r="L146" t="s">
         <v>15</v>
@@ -6880,7 +6880,7 @@
         <v>146</v>
       </c>
       <c r="C147">
-        <v>813</v>
+        <v>718</v>
       </c>
       <c r="D147">
         <v>1221</v>
@@ -6892,19 +6892,19 @@
         <v>2290.22</v>
       </c>
       <c r="G147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H147">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I147">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J147">
-        <v>1.4409</v>
+        <v>1.8775</v>
       </c>
       <c r="K147">
-        <v>1.4409</v>
+        <v>1.0479</v>
       </c>
       <c r="L147" t="s">
         <v>15</v>
@@ -6924,10 +6924,10 @@
         <v>147</v>
       </c>
       <c r="C148">
-        <v>910</v>
+        <v>804</v>
       </c>
       <c r="D148">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="E148">
         <v>54</v>
@@ -6936,19 +6936,19 @@
         <v>2290.22</v>
       </c>
       <c r="G148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H148">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="I148">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J148">
-        <v>2.0959</v>
+        <v>1.2663</v>
       </c>
       <c r="K148">
-        <v>1.3099</v>
+        <v>1.2663</v>
       </c>
       <c r="L148" t="s">
         <v>15</v>
@@ -6968,31 +6968,31 @@
         <v>148</v>
       </c>
       <c r="C149">
-        <v>1003</v>
+        <v>911</v>
       </c>
       <c r="D149">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E149">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F149">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G149">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H149">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I149">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J149">
-        <v>1.7052</v>
+        <v>1.4846</v>
       </c>
       <c r="K149">
-        <v>0.9338</v>
+        <v>1.4846</v>
       </c>
       <c r="L149" t="s">
         <v>15</v>
@@ -7012,31 +7012,31 @@
         <v>149</v>
       </c>
       <c r="C150">
-        <v>1100</v>
+        <v>1003</v>
       </c>
       <c r="D150">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="E150">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F150">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H150">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I150">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J150">
-        <v>0.9841</v>
+        <v>1.7052</v>
       </c>
       <c r="K150">
-        <v>0.9841</v>
+        <v>0.9338</v>
       </c>
       <c r="L150" t="s">
         <v>15</v>
@@ -7056,31 +7056,31 @@
         <v>150</v>
       </c>
       <c r="C151">
-        <v>1182</v>
+        <v>1100</v>
       </c>
       <c r="D151">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="E151">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F151">
-        <v>2827.43</v>
+        <v>2642.08</v>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I151">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J151">
-        <v>0</v>
+        <v>0.9841</v>
       </c>
       <c r="K151">
-        <v>0</v>
+        <v>0.9841</v>
       </c>
       <c r="L151" t="s">
         <v>15</v>
@@ -7100,16 +7100,16 @@
         <v>151</v>
       </c>
       <c r="C152">
-        <v>1479</v>
+        <v>1192</v>
       </c>
       <c r="D152">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="E152">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F152">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -7320,16 +7320,16 @@
         <v>156</v>
       </c>
       <c r="C157">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="D157">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="E157">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F157">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -7455,28 +7455,28 @@
         <v>1669</v>
       </c>
       <c r="D160">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E160">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F160">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H160">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I160">
         <v>56</v>
       </c>
       <c r="J160">
-        <v>2.6172</v>
+        <v>2.2736</v>
       </c>
       <c r="K160">
-        <v>1.9806</v>
+        <v>2.2736</v>
       </c>
       <c r="L160" t="s">
         <v>15</v>
@@ -7496,10 +7496,10 @@
         <v>160</v>
       </c>
       <c r="C161">
-        <v>1292</v>
+        <v>1482</v>
       </c>
       <c r="D161">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="E161">
         <v>60</v>
@@ -7508,19 +7508,19 @@
         <v>2827.43</v>
       </c>
       <c r="G161">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H161">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="I161">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J161">
-        <v>3.077</v>
+        <v>0</v>
       </c>
       <c r="K161">
-        <v>2.1574</v>
+        <v>0</v>
       </c>
       <c r="L161" t="s">
         <v>15</v>
@@ -7540,10 +7540,10 @@
         <v>161</v>
       </c>
       <c r="C162">
-        <v>707</v>
+        <v>2148</v>
       </c>
       <c r="D162">
-        <v>1293</v>
+        <v>1282</v>
       </c>
       <c r="E162">
         <v>60</v>
@@ -7552,19 +7552,19 @@
         <v>2827.43</v>
       </c>
       <c r="G162">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H162">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="I162">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J162">
-        <v>1.733</v>
+        <v>0.9196</v>
       </c>
       <c r="K162">
-        <v>1.061</v>
+        <v>0.9196</v>
       </c>
       <c r="L162" t="s">
         <v>15</v>
@@ -7584,10 +7584,10 @@
         <v>162</v>
       </c>
       <c r="C163">
-        <v>1849</v>
+        <v>707</v>
       </c>
       <c r="D163">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="E163">
         <v>60</v>
@@ -7596,19 +7596,19 @@
         <v>2827.43</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I163">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J163">
-        <v>0</v>
+        <v>1.6623</v>
       </c>
       <c r="K163">
-        <v>0</v>
+        <v>1.0257</v>
       </c>
       <c r="L163" t="s">
         <v>15</v>
@@ -7628,10 +7628,10 @@
         <v>163</v>
       </c>
       <c r="C164">
-        <v>800</v>
+        <v>1853</v>
       </c>
       <c r="D164">
-        <v>1296</v>
+        <v>1288</v>
       </c>
       <c r="E164">
         <v>60</v>
@@ -7672,31 +7672,31 @@
         <v>164</v>
       </c>
       <c r="C165">
-        <v>894</v>
+        <v>810</v>
       </c>
       <c r="D165">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="E165">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F165">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G165">
         <v>1</v>
       </c>
       <c r="H165">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I165">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J165">
-        <v>0.7427</v>
+        <v>0.7714</v>
       </c>
       <c r="K165">
-        <v>0.7427</v>
+        <v>0.7714</v>
       </c>
       <c r="L165" t="s">
         <v>15</v>
@@ -7716,31 +7716,31 @@
         <v>165</v>
       </c>
       <c r="C166">
-        <v>1001</v>
+        <v>895</v>
       </c>
       <c r="D166">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="E166">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F166">
-        <v>2463.01</v>
+        <v>2290.22</v>
       </c>
       <c r="G166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H166">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="I166">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J166">
-        <v>1.624</v>
+        <v>0.9169</v>
       </c>
       <c r="K166">
-        <v>0.8932</v>
+        <v>0.9169</v>
       </c>
       <c r="L166" t="s">
         <v>15</v>
@@ -7760,7 +7760,7 @@
         <v>166</v>
       </c>
       <c r="C167">
-        <v>1097</v>
+        <v>1001</v>
       </c>
       <c r="D167">
         <v>1289</v>
@@ -7772,19 +7772,19 @@
         <v>2463.01</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I167">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J167">
-        <v>0</v>
+        <v>1.624</v>
       </c>
       <c r="K167">
-        <v>0</v>
+        <v>0.8932</v>
       </c>
       <c r="L167" t="s">
         <v>15</v>
@@ -7804,16 +7804,16 @@
         <v>167</v>
       </c>
       <c r="C168">
-        <v>1199</v>
+        <v>1097</v>
       </c>
       <c r="D168">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="E168">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F168">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G168">
         <v>0</v>
@@ -7848,10 +7848,10 @@
         <v>168</v>
       </c>
       <c r="C169">
-        <v>1480</v>
+        <v>1199</v>
       </c>
       <c r="D169">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="E169">
         <v>58</v>
@@ -7892,31 +7892,31 @@
         <v>169</v>
       </c>
       <c r="C170">
-        <v>1665</v>
+        <v>1481</v>
       </c>
       <c r="D170">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="E170">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F170">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H170">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I170">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J170">
-        <v>3.0451</v>
+        <v>0</v>
       </c>
       <c r="K170">
-        <v>3.0451</v>
+        <v>0</v>
       </c>
       <c r="L170" t="s">
         <v>15</v>
@@ -7936,31 +7936,31 @@
         <v>170</v>
       </c>
       <c r="C171">
-        <v>1763</v>
+        <v>1665</v>
       </c>
       <c r="D171">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="E171">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F171">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G171">
         <v>1</v>
       </c>
       <c r="H171">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="I171">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="J171">
-        <v>2.1195</v>
+        <v>3.0451</v>
       </c>
       <c r="K171">
-        <v>2.1195</v>
+        <v>3.0451</v>
       </c>
       <c r="L171" t="s">
         <v>15</v>
@@ -7980,31 +7980,31 @@
         <v>171</v>
       </c>
       <c r="C172">
-        <v>1956</v>
+        <v>1763</v>
       </c>
       <c r="D172">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="E172">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F172">
-        <v>2290.22</v>
+        <v>2642.08</v>
       </c>
       <c r="G172">
         <v>1</v>
       </c>
       <c r="H172">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I172">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J172">
-        <v>2.0959</v>
+        <v>2.1195</v>
       </c>
       <c r="K172">
-        <v>2.0959</v>
+        <v>2.1195</v>
       </c>
       <c r="L172" t="s">
         <v>15</v>
@@ -8024,31 +8024,31 @@
         <v>172</v>
       </c>
       <c r="C173">
-        <v>1385</v>
+        <v>1956</v>
       </c>
       <c r="D173">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="E173">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F173">
-        <v>2642.08</v>
+        <v>2290.22</v>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H173">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I173">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J173">
-        <v>0</v>
+        <v>2.0959</v>
       </c>
       <c r="K173">
-        <v>0</v>
+        <v>2.0959</v>
       </c>
       <c r="L173" t="s">
         <v>15</v>
@@ -8068,31 +8068,31 @@
         <v>173</v>
       </c>
       <c r="C174">
-        <v>1575</v>
+        <v>1385</v>
       </c>
       <c r="D174">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="E174">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F174">
-        <v>2827.43</v>
+        <v>2642.08</v>
       </c>
       <c r="G174">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H174">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I174">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J174">
-        <v>1.3793</v>
+        <v>0</v>
       </c>
       <c r="K174">
-        <v>0.7074</v>
+        <v>0</v>
       </c>
       <c r="L174" t="s">
         <v>15</v>
@@ -8112,7 +8112,7 @@
         <v>174</v>
       </c>
       <c r="C175">
-        <v>1284</v>
+        <v>1575</v>
       </c>
       <c r="D175">
         <v>1295</v>
@@ -8124,19 +8124,19 @@
         <v>2827.43</v>
       </c>
       <c r="G175">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H175">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I175">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J175">
-        <v>0</v>
+        <v>1.3793</v>
       </c>
       <c r="K175">
-        <v>0</v>
+        <v>0.7074</v>
       </c>
       <c r="L175" t="s">
         <v>15</v>
@@ -8156,10 +8156,10 @@
         <v>175</v>
       </c>
       <c r="C176">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="D176">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="E176">
         <v>60</v>
@@ -8168,16 +8168,16 @@
         <v>2827.43</v>
       </c>
       <c r="G176">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H176">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I176">
         <v>22</v>
       </c>
       <c r="J176">
-        <v>1.4147</v>
+        <v>0.7781</v>
       </c>
       <c r="K176">
         <v>0.7781</v>
@@ -8200,10 +8200,10 @@
         <v>176</v>
       </c>
       <c r="C177">
-        <v>2149</v>
+        <v>1286</v>
       </c>
       <c r="D177">
-        <v>1282</v>
+        <v>1292</v>
       </c>
       <c r="E177">
         <v>60</v>
@@ -8212,19 +8212,19 @@
         <v>2827.43</v>
       </c>
       <c r="G177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H177">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I177">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J177">
-        <v>0.9196</v>
+        <v>0</v>
       </c>
       <c r="K177">
-        <v>0.9196</v>
+        <v>0</v>
       </c>
       <c r="L177" t="s">
         <v>15</v>
@@ -8508,16 +8508,16 @@
         <v>183</v>
       </c>
       <c r="C184">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D184">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="E184">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F184">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -8529,10 +8529,10 @@
         <v>20</v>
       </c>
       <c r="J184">
-        <v>0.7074</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K184">
-        <v>0.7074</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="L184" t="s">
         <v>15</v>
@@ -8904,7 +8904,7 @@
         <v>192</v>
       </c>
       <c r="C193">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="D193">
         <v>1359</v>
@@ -8919,16 +8919,16 @@
         <v>1</v>
       </c>
       <c r="H193">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I193">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J193">
-        <v>1.0962</v>
+        <v>0.9338</v>
       </c>
       <c r="K193">
-        <v>1.0962</v>
+        <v>0.9338</v>
       </c>
       <c r="L193" t="s">
         <v>15</v>
@@ -8992,31 +8992,31 @@
         <v>194</v>
       </c>
       <c r="C195">
-        <v>813</v>
+        <v>2160</v>
       </c>
       <c r="D195">
         <v>1427</v>
       </c>
       <c r="E195">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F195">
-        <v>1963.5</v>
+        <v>2642.08</v>
       </c>
       <c r="G195">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H195">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="I195">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J195">
-        <v>1.9353</v>
+        <v>3.3686</v>
       </c>
       <c r="K195">
-        <v>1.9353</v>
+        <v>1.7032</v>
       </c>
       <c r="L195" t="s">
         <v>15</v>
@@ -9036,31 +9036,31 @@
         <v>195</v>
       </c>
       <c r="C196">
-        <v>2160</v>
+        <v>901</v>
       </c>
       <c r="D196">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="E196">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F196">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G196">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H196">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="I196">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J196">
-        <v>3.3686</v>
+        <v>2.8015</v>
       </c>
       <c r="K196">
-        <v>1.7032</v>
+        <v>1.5428</v>
       </c>
       <c r="L196" t="s">
         <v>15</v>
@@ -9080,7 +9080,7 @@
         <v>196</v>
       </c>
       <c r="C197">
-        <v>901</v>
+        <v>998</v>
       </c>
       <c r="D197">
         <v>1428</v>
@@ -9092,19 +9092,19 @@
         <v>2463.01</v>
       </c>
       <c r="G197">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H197">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I197">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J197">
-        <v>2.8015</v>
+        <v>3.2075</v>
       </c>
       <c r="K197">
-        <v>1.5428</v>
+        <v>1.2992</v>
       </c>
       <c r="L197" t="s">
         <v>15</v>
@@ -9124,7 +9124,7 @@
         <v>197</v>
       </c>
       <c r="C198">
-        <v>998</v>
+        <v>1192</v>
       </c>
       <c r="D198">
         <v>1428</v>
@@ -9136,19 +9136,19 @@
         <v>2463.01</v>
       </c>
       <c r="G198">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H198">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="I198">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J198">
-        <v>3.2075</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K198">
-        <v>1.2992</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="L198" t="s">
         <v>15</v>
@@ -9168,7 +9168,7 @@
         <v>198</v>
       </c>
       <c r="C199">
-        <v>1192</v>
+        <v>1289</v>
       </c>
       <c r="D199">
         <v>1428</v>
@@ -9183,16 +9183,16 @@
         <v>1</v>
       </c>
       <c r="H199">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I199">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J199">
-        <v>0.8120000000000001</v>
+        <v>1.0556</v>
       </c>
       <c r="K199">
-        <v>0.8120000000000001</v>
+        <v>1.0556</v>
       </c>
       <c r="L199" t="s">
         <v>15</v>
@@ -9212,10 +9212,10 @@
         <v>199</v>
       </c>
       <c r="C200">
-        <v>1289</v>
+        <v>1384</v>
       </c>
       <c r="D200">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="E200">
         <v>56</v>
@@ -9224,19 +9224,19 @@
         <v>2463.01</v>
       </c>
       <c r="G200">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H200">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="I200">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J200">
-        <v>1.0556</v>
+        <v>1.827</v>
       </c>
       <c r="K200">
-        <v>1.0556</v>
+        <v>0.9744</v>
       </c>
       <c r="L200" t="s">
         <v>15</v>
@@ -9256,10 +9256,10 @@
         <v>200</v>
       </c>
       <c r="C201">
-        <v>1384</v>
+        <v>1482</v>
       </c>
       <c r="D201">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="E201">
         <v>56</v>
@@ -9271,16 +9271,16 @@
         <v>2</v>
       </c>
       <c r="H201">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I201">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J201">
-        <v>1.827</v>
+        <v>1.9082</v>
       </c>
       <c r="K201">
-        <v>0.9744</v>
+        <v>1.015</v>
       </c>
       <c r="L201" t="s">
         <v>15</v>
@@ -9300,7 +9300,7 @@
         <v>201</v>
       </c>
       <c r="C202">
-        <v>1482</v>
+        <v>1579</v>
       </c>
       <c r="D202">
         <v>1428</v>
@@ -9312,19 +9312,19 @@
         <v>2463.01</v>
       </c>
       <c r="G202">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H202">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="I202">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J202">
-        <v>1.9082</v>
+        <v>0.7714</v>
       </c>
       <c r="K202">
-        <v>1.015</v>
+        <v>0.7714</v>
       </c>
       <c r="L202" t="s">
         <v>15</v>
@@ -9344,7 +9344,7 @@
         <v>202</v>
       </c>
       <c r="C203">
-        <v>1579</v>
+        <v>1676</v>
       </c>
       <c r="D203">
         <v>1428</v>
@@ -9356,19 +9356,19 @@
         <v>2463.01</v>
       </c>
       <c r="G203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H203">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I203">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J203">
-        <v>0.7714</v>
+        <v>0</v>
       </c>
       <c r="K203">
-        <v>0.7714</v>
+        <v>0</v>
       </c>
       <c r="L203" t="s">
         <v>15</v>
@@ -9388,7 +9388,7 @@
         <v>203</v>
       </c>
       <c r="C204">
-        <v>1676</v>
+        <v>1870</v>
       </c>
       <c r="D204">
         <v>1428</v>
@@ -9432,7 +9432,7 @@
         <v>204</v>
       </c>
       <c r="C205">
-        <v>1870</v>
+        <v>1969</v>
       </c>
       <c r="D205">
         <v>1428</v>
@@ -9444,19 +9444,19 @@
         <v>2463.01</v>
       </c>
       <c r="G205">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H205">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="I205">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J205">
-        <v>0</v>
+        <v>2.3954</v>
       </c>
       <c r="K205">
-        <v>0</v>
+        <v>1.7052</v>
       </c>
       <c r="L205" t="s">
         <v>15</v>
@@ -9476,7 +9476,7 @@
         <v>205</v>
       </c>
       <c r="C206">
-        <v>1969</v>
+        <v>2064</v>
       </c>
       <c r="D206">
         <v>1428</v>
@@ -9488,19 +9488,19 @@
         <v>2463.01</v>
       </c>
       <c r="G206">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H206">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="I206">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J206">
-        <v>2.3954</v>
+        <v>0</v>
       </c>
       <c r="K206">
-        <v>1.7052</v>
+        <v>0</v>
       </c>
       <c r="L206" t="s">
         <v>15</v>
@@ -9520,7 +9520,7 @@
         <v>206</v>
       </c>
       <c r="C207">
-        <v>2064</v>
+        <v>791</v>
       </c>
       <c r="D207">
         <v>1428</v>
@@ -9532,19 +9532,19 @@
         <v>2463.01</v>
       </c>
       <c r="G207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H207">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I207">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J207">
-        <v>0</v>
+        <v>1.015</v>
       </c>
       <c r="K207">
-        <v>0</v>
+        <v>1.015</v>
       </c>
       <c r="L207" t="s">
         <v>15</v>
@@ -9564,31 +9564,31 @@
         <v>207</v>
       </c>
       <c r="C208">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D208">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="E208">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F208">
-        <v>2827.43</v>
+        <v>2290.22</v>
       </c>
       <c r="G208">
         <v>2</v>
       </c>
       <c r="H208">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="I208">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="J208">
-        <v>1.1671</v>
+        <v>2.8382</v>
       </c>
       <c r="K208">
-        <v>0.6012999999999999</v>
+        <v>2.1395</v>
       </c>
       <c r="L208" t="s">
         <v>15</v>
@@ -9652,10 +9652,10 @@
         <v>209</v>
       </c>
       <c r="C210">
-        <v>767</v>
+        <v>2167</v>
       </c>
       <c r="D210">
-        <v>1473</v>
+        <v>1499</v>
       </c>
       <c r="E210">
         <v>56</v>
@@ -9664,19 +9664,19 @@
         <v>2463.01</v>
       </c>
       <c r="G210">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H210">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I210">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J210">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="K210">
-        <v>0</v>
+        <v>1.0962</v>
       </c>
       <c r="L210" t="s">
         <v>15</v>
@@ -9696,31 +9696,31 @@
         <v>210</v>
       </c>
       <c r="C211">
-        <v>1192</v>
+        <v>703</v>
       </c>
       <c r="D211">
-        <v>1492</v>
+        <v>1499</v>
       </c>
       <c r="E211">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F211">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G211">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H211">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="I211">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J211">
-        <v>1.1318</v>
+        <v>3.0451</v>
       </c>
       <c r="K211">
-        <v>1.1318</v>
+        <v>1.3398</v>
       </c>
       <c r="L211" t="s">
         <v>15</v>
@@ -9740,10 +9740,10 @@
         <v>211</v>
       </c>
       <c r="C212">
-        <v>2167</v>
+        <v>790</v>
       </c>
       <c r="D212">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="E212">
         <v>56</v>
@@ -9752,19 +9752,19 @@
         <v>2463.01</v>
       </c>
       <c r="G212">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H212">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="I212">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J212">
-        <v>2.03</v>
+        <v>0.9338</v>
       </c>
       <c r="K212">
-        <v>1.0962</v>
+        <v>0.9338</v>
       </c>
       <c r="L212" t="s">
         <v>15</v>
@@ -9784,10 +9784,10 @@
         <v>212</v>
       </c>
       <c r="C213">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="D213">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="E213">
         <v>56</v>
@@ -9799,16 +9799,16 @@
         <v>2</v>
       </c>
       <c r="H213">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I213">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J213">
-        <v>1.9894</v>
+        <v>2.0706</v>
       </c>
       <c r="K213">
-        <v>1.015</v>
+        <v>1.0962</v>
       </c>
       <c r="L213" t="s">
         <v>15</v>
@@ -9916,10 +9916,10 @@
         <v>215</v>
       </c>
       <c r="C216">
-        <v>1289</v>
+        <v>1190</v>
       </c>
       <c r="D216">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="E216">
         <v>60</v>
@@ -9928,19 +9928,19 @@
         <v>2827.43</v>
       </c>
       <c r="G216">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H216">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="I216">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="J216">
-        <v>2.4757</v>
+        <v>1.1318</v>
       </c>
       <c r="K216">
-        <v>1.6269</v>
+        <v>1.1318</v>
       </c>
       <c r="L216" t="s">
         <v>15</v>
@@ -9960,7 +9960,7 @@
         <v>216</v>
       </c>
       <c r="C217">
-        <v>1484</v>
+        <v>1288</v>
       </c>
       <c r="D217">
         <v>1493</v>
@@ -9972,19 +9972,19 @@
         <v>2827.43</v>
       </c>
       <c r="G217">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H217">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="I217">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J217">
-        <v>1.3793</v>
+        <v>3.0416</v>
       </c>
       <c r="K217">
-        <v>1.3793</v>
+        <v>1.5208</v>
       </c>
       <c r="L217" t="s">
         <v>15</v>
@@ -10004,10 +10004,10 @@
         <v>217</v>
       </c>
       <c r="C218">
-        <v>1582</v>
+        <v>1484</v>
       </c>
       <c r="D218">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="E218">
         <v>60</v>
@@ -10016,19 +10016,19 @@
         <v>2827.43</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I218">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J218">
-        <v>0</v>
+        <v>1.2379</v>
       </c>
       <c r="K218">
-        <v>0</v>
+        <v>1.2379</v>
       </c>
       <c r="L218" t="s">
         <v>15</v>
@@ -10048,7 +10048,7 @@
         <v>218</v>
       </c>
       <c r="C219">
-        <v>1680</v>
+        <v>1582</v>
       </c>
       <c r="D219">
         <v>1493</v>
@@ -10060,19 +10060,19 @@
         <v>2827.43</v>
       </c>
       <c r="G219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H219">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I219">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J219">
-        <v>1.0964</v>
+        <v>0</v>
       </c>
       <c r="K219">
-        <v>1.0964</v>
+        <v>0</v>
       </c>
       <c r="L219" t="s">
         <v>15</v>
@@ -10092,31 +10092,31 @@
         <v>219</v>
       </c>
       <c r="C220">
-        <v>1776</v>
+        <v>1681</v>
       </c>
       <c r="D220">
-        <v>1500</v>
+        <v>1493</v>
       </c>
       <c r="E220">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F220">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G220">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H220">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="I220">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J220">
-        <v>1.7458</v>
+        <v>0.8842</v>
       </c>
       <c r="K220">
-        <v>1.0962</v>
+        <v>0.8842</v>
       </c>
       <c r="L220" t="s">
         <v>15</v>
@@ -10136,31 +10136,31 @@
         <v>220</v>
       </c>
       <c r="C221">
-        <v>1877</v>
+        <v>1776</v>
       </c>
       <c r="D221">
         <v>1500</v>
       </c>
       <c r="E221">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F221">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G221">
         <v>2</v>
       </c>
       <c r="H221">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="I221">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="J221">
-        <v>2.763</v>
+        <v>1.7458</v>
       </c>
       <c r="K221">
-        <v>1.7032</v>
+        <v>1.0962</v>
       </c>
       <c r="L221" t="s">
         <v>15</v>
@@ -10180,31 +10180,31 @@
         <v>221</v>
       </c>
       <c r="C222">
-        <v>1972</v>
+        <v>1877</v>
       </c>
       <c r="D222">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="E222">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F222">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G222">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H222">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I222">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J222">
-        <v>0</v>
+        <v>2.763</v>
       </c>
       <c r="K222">
-        <v>0</v>
+        <v>1.7032</v>
       </c>
       <c r="L222" t="s">
         <v>15</v>
@@ -10224,31 +10224,31 @@
         <v>222</v>
       </c>
       <c r="C223">
-        <v>2070</v>
+        <v>1972</v>
       </c>
       <c r="D223">
         <v>1499</v>
       </c>
       <c r="E223">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F223">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G223">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H223">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="I223">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="J223">
-        <v>5.7152</v>
+        <v>0</v>
       </c>
       <c r="K223">
-        <v>2.0438</v>
+        <v>0</v>
       </c>
       <c r="L223" t="s">
         <v>15</v>
@@ -10268,31 +10268,31 @@
         <v>223</v>
       </c>
       <c r="C224">
-        <v>1383</v>
+        <v>2070</v>
       </c>
       <c r="D224">
-        <v>1494</v>
+        <v>1499</v>
       </c>
       <c r="E224">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F224">
-        <v>2827.43</v>
+        <v>2642.08</v>
       </c>
       <c r="G224">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H224">
-        <v>100</v>
+        <v>151</v>
       </c>
       <c r="I224">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J224">
-        <v>3.5368</v>
+        <v>5.7152</v>
       </c>
       <c r="K224">
-        <v>1.7684</v>
+        <v>2.0438</v>
       </c>
       <c r="L224" t="s">
         <v>15</v>
@@ -10312,31 +10312,31 @@
         <v>224</v>
       </c>
       <c r="C225">
-        <v>796</v>
+        <v>1383</v>
       </c>
       <c r="D225">
-        <v>1570</v>
+        <v>1494</v>
       </c>
       <c r="E225">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F225">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H225">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="I225">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="J225">
-        <v>4.803</v>
+        <v>3.5368</v>
       </c>
       <c r="K225">
-        <v>3.1438</v>
+        <v>1.7684</v>
       </c>
       <c r="L225" t="s">
         <v>15</v>
@@ -10356,31 +10356,31 @@
         <v>225</v>
       </c>
       <c r="C226">
-        <v>703</v>
+        <v>2171</v>
       </c>
       <c r="D226">
-        <v>1509</v>
+        <v>1573</v>
       </c>
       <c r="E226">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F226">
-        <v>1520.53</v>
+        <v>2827.43</v>
       </c>
       <c r="G226">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H226">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="I226">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="J226">
-        <v>1.3153</v>
+        <v>6.7552</v>
       </c>
       <c r="K226">
-        <v>1.3153</v>
+        <v>3.8551</v>
       </c>
       <c r="L226" t="s">
         <v>15</v>
@@ -10400,10 +10400,10 @@
         <v>226</v>
       </c>
       <c r="C227">
-        <v>997</v>
+        <v>694</v>
       </c>
       <c r="D227">
-        <v>1571</v>
+        <v>1574</v>
       </c>
       <c r="E227">
         <v>58</v>
@@ -10415,13 +10415,13 @@
         <v>2</v>
       </c>
       <c r="H227">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="I227">
         <v>45</v>
       </c>
       <c r="J227">
-        <v>2.6873</v>
+        <v>3.0658</v>
       </c>
       <c r="K227">
         <v>1.7032</v>
@@ -10444,31 +10444,31 @@
         <v>227</v>
       </c>
       <c r="C228">
-        <v>1397</v>
+        <v>797</v>
       </c>
       <c r="D228">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="E228">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F228">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G228">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H228">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I228">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="J228">
-        <v>0</v>
+        <v>4.2631</v>
       </c>
       <c r="K228">
-        <v>0</v>
+        <v>2.7203</v>
       </c>
       <c r="L228" t="s">
         <v>15</v>
@@ -10488,10 +10488,10 @@
         <v>228</v>
       </c>
       <c r="C229">
-        <v>2174</v>
+        <v>895</v>
       </c>
       <c r="D229">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="E229">
         <v>58</v>
@@ -10500,19 +10500,19 @@
         <v>2642.08</v>
       </c>
       <c r="G229">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H229">
-        <v>216</v>
+        <v>73</v>
       </c>
       <c r="I229">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="J229">
-        <v>8.1754</v>
+        <v>2.763</v>
       </c>
       <c r="K229">
-        <v>4.1634</v>
+        <v>1.514</v>
       </c>
       <c r="L229" t="s">
         <v>15</v>
@@ -10532,31 +10532,31 @@
         <v>229</v>
       </c>
       <c r="C230">
-        <v>1092</v>
+        <v>1001</v>
       </c>
       <c r="D230">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="E230">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F230">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G230">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H230">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="I230">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="J230">
-        <v>1.0556</v>
+        <v>2.5111</v>
       </c>
       <c r="K230">
-        <v>1.0556</v>
+        <v>1.5915</v>
       </c>
       <c r="L230" t="s">
         <v>15</v>
@@ -10576,7 +10576,7 @@
         <v>230</v>
       </c>
       <c r="C231">
-        <v>1192</v>
+        <v>1092</v>
       </c>
       <c r="D231">
         <v>1571</v>
@@ -10588,19 +10588,19 @@
         <v>2463.01</v>
       </c>
       <c r="G231">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H231">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="I231">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J231">
-        <v>2.3548</v>
+        <v>1.0556</v>
       </c>
       <c r="K231">
-        <v>1.2992</v>
+        <v>1.0556</v>
       </c>
       <c r="L231" t="s">
         <v>15</v>
@@ -10620,7 +10620,7 @@
         <v>231</v>
       </c>
       <c r="C232">
-        <v>1290</v>
+        <v>1192</v>
       </c>
       <c r="D232">
         <v>1571</v>
@@ -10632,19 +10632,19 @@
         <v>2463.01</v>
       </c>
       <c r="G232">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H232">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="I232">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J232">
-        <v>4.6285</v>
+        <v>2.3548</v>
       </c>
       <c r="K232">
-        <v>1.1368</v>
+        <v>1.2992</v>
       </c>
       <c r="L232" t="s">
         <v>15</v>
@@ -10664,31 +10664,31 @@
         <v>232</v>
       </c>
       <c r="C233">
-        <v>1492</v>
+        <v>1290</v>
       </c>
       <c r="D233">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="E233">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F233">
-        <v>2827.43</v>
+        <v>2463.01</v>
       </c>
       <c r="G233">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H233">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="I233">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J233">
-        <v>1.061</v>
+        <v>4.6285</v>
       </c>
       <c r="K233">
-        <v>1.061</v>
+        <v>1.1368</v>
       </c>
       <c r="L233" t="s">
         <v>15</v>
@@ -10708,31 +10708,31 @@
         <v>233</v>
       </c>
       <c r="C234">
-        <v>1585</v>
+        <v>1387</v>
       </c>
       <c r="D234">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="E234">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F234">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H234">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="I234">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="J234">
-        <v>2.3548</v>
+        <v>0</v>
       </c>
       <c r="K234">
-        <v>2.3548</v>
+        <v>0</v>
       </c>
       <c r="L234" t="s">
         <v>15</v>
@@ -10752,31 +10752,31 @@
         <v>234</v>
       </c>
       <c r="C235">
-        <v>1684</v>
+        <v>1492</v>
       </c>
       <c r="D235">
         <v>1572</v>
       </c>
       <c r="E235">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F235">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G235">
         <v>1</v>
       </c>
       <c r="H235">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="I235">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J235">
-        <v>0.7308</v>
+        <v>1.061</v>
       </c>
       <c r="K235">
-        <v>0.7308</v>
+        <v>1.061</v>
       </c>
       <c r="L235" t="s">
         <v>15</v>
@@ -10796,31 +10796,31 @@
         <v>235</v>
       </c>
       <c r="C236">
-        <v>1781</v>
+        <v>1585</v>
       </c>
       <c r="D236">
         <v>1571</v>
       </c>
       <c r="E236">
+        <v>56</v>
+      </c>
+      <c r="F236">
+        <v>2463.01</v>
+      </c>
+      <c r="G236">
+        <v>1</v>
+      </c>
+      <c r="H236">
         <v>58</v>
       </c>
-      <c r="F236">
-        <v>2642.08</v>
-      </c>
-      <c r="G236">
-        <v>0</v>
-      </c>
-      <c r="H236">
-        <v>0</v>
-      </c>
       <c r="I236">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J236">
-        <v>0</v>
+        <v>2.3548</v>
       </c>
       <c r="K236">
-        <v>0</v>
+        <v>2.3548</v>
       </c>
       <c r="L236" t="s">
         <v>15</v>
@@ -10840,31 +10840,31 @@
         <v>236</v>
       </c>
       <c r="C237">
-        <v>1879</v>
+        <v>1684</v>
       </c>
       <c r="D237">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="E237">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F237">
-        <v>2642.08</v>
+        <v>2463.01</v>
       </c>
       <c r="G237">
         <v>1</v>
       </c>
       <c r="H237">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="I237">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="J237">
-        <v>1.6654</v>
+        <v>0.7308</v>
       </c>
       <c r="K237">
-        <v>1.6654</v>
+        <v>0.7308</v>
       </c>
       <c r="L237" t="s">
         <v>15</v>
@@ -10884,7 +10884,7 @@
         <v>237</v>
       </c>
       <c r="C238">
-        <v>1977</v>
+        <v>1781</v>
       </c>
       <c r="D238">
         <v>1571</v>
@@ -10896,19 +10896,19 @@
         <v>2642.08</v>
       </c>
       <c r="G238">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H238">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="I238">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J238">
-        <v>2.3845</v>
+        <v>0</v>
       </c>
       <c r="K238">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="L238" t="s">
         <v>15</v>
@@ -10928,31 +10928,31 @@
         <v>238</v>
       </c>
       <c r="C239">
-        <v>2076</v>
+        <v>1879</v>
       </c>
       <c r="D239">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="E239">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F239">
-        <v>2463.01</v>
+        <v>2642.08</v>
       </c>
       <c r="G239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H239">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="I239">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J239">
-        <v>3.1263</v>
+        <v>1.6654</v>
       </c>
       <c r="K239">
-        <v>1.9082</v>
+        <v>1.6654</v>
       </c>
       <c r="L239" t="s">
         <v>15</v>
@@ -10972,31 +10972,31 @@
         <v>239</v>
       </c>
       <c r="C240">
-        <v>923</v>
+        <v>1977</v>
       </c>
       <c r="D240">
-        <v>1587</v>
+        <v>1571</v>
       </c>
       <c r="E240">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F240">
-        <v>2827.43</v>
+        <v>2642.08</v>
       </c>
       <c r="G240">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H240">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I240">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J240">
-        <v>0</v>
+        <v>2.3845</v>
       </c>
       <c r="K240">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="L240" t="s">
         <v>15</v>
@@ -11016,31 +11016,31 @@
         <v>240</v>
       </c>
       <c r="C241">
-        <v>703</v>
+        <v>2076</v>
       </c>
       <c r="D241">
-        <v>1574</v>
+        <v>1570</v>
       </c>
       <c r="E241">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F241">
-        <v>1661.9</v>
+        <v>2463.01</v>
       </c>
       <c r="G241">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H241">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="I241">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J241">
-        <v>2.2264</v>
+        <v>3.1263</v>
       </c>
       <c r="K241">
-        <v>2.2264</v>
+        <v>1.9082</v>
       </c>
       <c r="L241" t="s">
         <v>15</v>
@@ -11060,31 +11060,31 @@
         <v>241</v>
       </c>
       <c r="C242">
-        <v>841</v>
+        <v>2087</v>
       </c>
       <c r="D242">
-        <v>1613</v>
+        <v>1641</v>
       </c>
       <c r="E242">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F242">
-        <v>1520.53</v>
+        <v>2827.43</v>
       </c>
       <c r="G242">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H242">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I242">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J242">
-        <v>0</v>
+        <v>2.1221</v>
       </c>
       <c r="K242">
-        <v>0</v>
+        <v>1.1671</v>
       </c>
       <c r="L242" t="s">
         <v>15</v>
@@ -11104,31 +11104,31 @@
         <v>242</v>
       </c>
       <c r="C243">
-        <v>1965</v>
+        <v>2182</v>
       </c>
       <c r="D243">
-        <v>1622</v>
+        <v>1636</v>
       </c>
       <c r="E243">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F243">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G243">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H243">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="I243">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="J243">
-        <v>0.9169</v>
+        <v>4.8808</v>
       </c>
       <c r="K243">
-        <v>0.9169</v>
+        <v>2.3343</v>
       </c>
       <c r="L243" t="s">
         <v>15</v>
@@ -11148,31 +11148,31 @@
         <v>243</v>
       </c>
       <c r="C244">
-        <v>1109</v>
+        <v>695</v>
       </c>
       <c r="D244">
-        <v>1623</v>
+        <v>1643</v>
       </c>
       <c r="E244">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F244">
-        <v>1963.5</v>
+        <v>2642.08</v>
       </c>
       <c r="G244">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H244">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="I244">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="J244">
-        <v>0</v>
+        <v>5.261</v>
       </c>
       <c r="K244">
-        <v>0</v>
+        <v>2.0438</v>
       </c>
       <c r="L244" t="s">
         <v>15</v>
@@ -11192,31 +11192,31 @@
         <v>244</v>
       </c>
       <c r="C245">
-        <v>2081</v>
+        <v>1094</v>
       </c>
       <c r="D245">
-        <v>1644</v>
+        <v>1648</v>
       </c>
       <c r="E245">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F245">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G245">
         <v>2</v>
       </c>
       <c r="H245">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="I245">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J245">
-        <v>2.5762</v>
+        <v>2.4757</v>
       </c>
       <c r="K245">
-        <v>1.3536</v>
+        <v>1.4501</v>
       </c>
       <c r="L245" t="s">
         <v>15</v>
@@ -11236,31 +11236,31 @@
         <v>245</v>
       </c>
       <c r="C246">
-        <v>1046</v>
+        <v>1190</v>
       </c>
       <c r="D246">
-        <v>1626</v>
+        <v>1644</v>
       </c>
       <c r="E246">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F246">
-        <v>1809.56</v>
+        <v>2642.08</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="I246">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J246">
-        <v>0</v>
+        <v>2.9901</v>
       </c>
       <c r="K246">
-        <v>0</v>
+        <v>1.5518</v>
       </c>
       <c r="L246" t="s">
         <v>15</v>
@@ -11280,31 +11280,31 @@
         <v>246</v>
       </c>
       <c r="C247">
-        <v>2158</v>
+        <v>1593</v>
       </c>
       <c r="D247">
-        <v>1627</v>
+        <v>1645</v>
       </c>
       <c r="E247">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F247">
-        <v>1809.56</v>
+        <v>2463.01</v>
       </c>
       <c r="G247">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="I247">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J247">
-        <v>0</v>
+        <v>5.0345</v>
       </c>
       <c r="K247">
-        <v>0</v>
+        <v>2.5578</v>
       </c>
       <c r="L247" t="s">
         <v>15</v>
@@ -11324,31 +11324,31 @@
         <v>247</v>
       </c>
       <c r="C248">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="D248">
-        <v>1630</v>
+        <v>1643</v>
       </c>
       <c r="E248">
+        <v>56</v>
+      </c>
+      <c r="F248">
+        <v>2463.01</v>
+      </c>
+      <c r="G248">
+        <v>2</v>
+      </c>
+      <c r="H248">
         <v>48</v>
-      </c>
-      <c r="F248">
-        <v>1809.56</v>
-      </c>
-      <c r="G248">
-        <v>1</v>
-      </c>
-      <c r="H248">
-        <v>24</v>
       </c>
       <c r="I248">
         <v>24</v>
       </c>
       <c r="J248">
-        <v>1.3263</v>
+        <v>1.9488</v>
       </c>
       <c r="K248">
-        <v>1.3263</v>
+        <v>0.9744</v>
       </c>
       <c r="L248" t="s">
         <v>15</v>
@@ -11368,31 +11368,31 @@
         <v>248</v>
       </c>
       <c r="C249">
-        <v>1588</v>
+        <v>1792</v>
       </c>
       <c r="D249">
-        <v>1631</v>
+        <v>1643</v>
       </c>
       <c r="E249">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F249">
-        <v>1963.5</v>
+        <v>2463.01</v>
       </c>
       <c r="G249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H249">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I249">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J249">
-        <v>1.426</v>
+        <v>0</v>
       </c>
       <c r="K249">
-        <v>1.426</v>
+        <v>0</v>
       </c>
       <c r="L249" t="s">
         <v>15</v>
@@ -11412,31 +11412,31 @@
         <v>249</v>
       </c>
       <c r="C250">
-        <v>1685</v>
+        <v>798</v>
       </c>
       <c r="D250">
-        <v>1631</v>
+        <v>1653</v>
       </c>
       <c r="E250">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F250">
-        <v>1963.5</v>
+        <v>2642.08</v>
       </c>
       <c r="G250">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H250">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="I250">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="J250">
-        <v>0.8658</v>
+        <v>2.4223</v>
       </c>
       <c r="K250">
-        <v>0.8658</v>
+        <v>1.2869</v>
       </c>
       <c r="L250" t="s">
         <v>15</v>
@@ -11456,31 +11456,31 @@
         <v>250</v>
       </c>
       <c r="C251">
-        <v>1780</v>
+        <v>996</v>
       </c>
       <c r="D251">
-        <v>1632</v>
+        <v>1649</v>
       </c>
       <c r="E251">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F251">
-        <v>2123.72</v>
+        <v>2827.43</v>
       </c>
       <c r="G251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H251">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="I251">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J251">
-        <v>0.8005</v>
+        <v>1.3793</v>
       </c>
       <c r="K251">
-        <v>0.8005</v>
+        <v>0.7427</v>
       </c>
       <c r="L251" t="s">
         <v>15</v>
@@ -11500,31 +11500,31 @@
         <v>251</v>
       </c>
       <c r="C252">
-        <v>1390</v>
+        <v>1693</v>
       </c>
       <c r="D252">
-        <v>1635</v>
+        <v>1645</v>
       </c>
       <c r="E252">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F252">
-        <v>1809.56</v>
+        <v>2827.43</v>
       </c>
       <c r="G252">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H252">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I252">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J252">
-        <v>0</v>
+        <v>2.2989</v>
       </c>
       <c r="K252">
-        <v>0</v>
+        <v>1.061</v>
       </c>
       <c r="L252" t="s">
         <v>15</v>
@@ -11544,10 +11544,10 @@
         <v>252</v>
       </c>
       <c r="C253">
-        <v>1890</v>
+        <v>1991</v>
       </c>
       <c r="D253">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="E253">
         <v>60</v>
@@ -11556,19 +11556,19 @@
         <v>2827.43</v>
       </c>
       <c r="G253">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H253">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="I253">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="J253">
-        <v>3.2538</v>
+        <v>1.733</v>
       </c>
       <c r="K253">
-        <v>2.5111</v>
+        <v>1.733</v>
       </c>
       <c r="L253" t="s">
         <v>15</v>
@@ -11588,40 +11588,40 @@
         <v>253</v>
       </c>
       <c r="C254">
-        <v>2160</v>
+        <v>1894</v>
       </c>
       <c r="D254">
-        <v>650</v>
+        <v>1652</v>
       </c>
       <c r="E254">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F254">
-        <v>2290.22</v>
+        <v>2827.43</v>
       </c>
       <c r="G254">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H254">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="I254">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="J254">
-        <v>0</v>
+        <v>3.2538</v>
       </c>
       <c r="K254">
-        <v>0</v>
+        <v>2.5111</v>
       </c>
       <c r="L254" t="s">
         <v>15</v>
       </c>
       <c r="M254" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N254">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:14">
@@ -11632,31 +11632,31 @@
         <v>254</v>
       </c>
       <c r="C255">
-        <v>698</v>
+        <v>901</v>
       </c>
       <c r="D255">
-        <v>1643</v>
+        <v>1654</v>
       </c>
       <c r="E255">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F255">
-        <v>2123.72</v>
+        <v>2827.43</v>
       </c>
       <c r="G255">
         <v>3</v>
       </c>
       <c r="H255">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="I255">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="J255">
-        <v>5.1796</v>
+        <v>2.405</v>
       </c>
       <c r="K255">
-        <v>2.6369</v>
+        <v>0.9903</v>
       </c>
       <c r="L255" t="s">
         <v>15</v>
@@ -11665,7 +11665,7 @@
         <v>0</v>
       </c>
       <c r="N255">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:14">
@@ -11676,40 +11676,40 @@
         <v>255</v>
       </c>
       <c r="C256">
-        <v>910</v>
+        <v>1393</v>
       </c>
       <c r="D256">
-        <v>1650</v>
+        <v>1669</v>
       </c>
       <c r="E256">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F256">
-        <v>2123.72</v>
+        <v>2827.43</v>
       </c>
       <c r="G256">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H256">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I256">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J256">
-        <v>3.767</v>
+        <v>0</v>
       </c>
       <c r="K256">
-        <v>1.3184</v>
+        <v>0</v>
       </c>
       <c r="L256" t="s">
         <v>15</v>
       </c>
       <c r="M256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N256">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:14">
@@ -11720,31 +11720,31 @@
         <v>256</v>
       </c>
       <c r="C257">
-        <v>1190</v>
+        <v>1277</v>
       </c>
       <c r="D257">
-        <v>1644</v>
+        <v>1655</v>
       </c>
       <c r="E257">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F257">
-        <v>2463.01</v>
+        <v>2827.43</v>
       </c>
       <c r="G257">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H257">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I257">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J257">
-        <v>1.7052</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="K257">
-        <v>1.015</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="L257" t="s">
         <v>15</v>
@@ -11753,51 +11753,7 @@
         <v>0</v>
       </c>
       <c r="N257">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="258" spans="1:14">
-      <c r="A258" t="s">
-        <v>14</v>
-      </c>
-      <c r="B258">
-        <v>257</v>
-      </c>
-      <c r="C258">
-        <v>1288</v>
-      </c>
-      <c r="D258">
-        <v>1650</v>
-      </c>
-      <c r="E258">
-        <v>60</v>
-      </c>
-      <c r="F258">
-        <v>2827.43</v>
-      </c>
-      <c r="G258">
-        <v>1</v>
-      </c>
-      <c r="H258">
-        <v>17</v>
-      </c>
-      <c r="I258">
-        <v>17</v>
-      </c>
-      <c r="J258">
-        <v>0.6012999999999999</v>
-      </c>
-      <c r="K258">
-        <v>0.6012999999999999</v>
-      </c>
-      <c r="L258" t="s">
-        <v>15</v>
-      </c>
-      <c r="M258" t="b">
-        <v>1</v>
-      </c>
-      <c r="N258">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -11870,13 +11826,13 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C2">
-        <v>1.3549</v>
+        <v>1.3637</v>
       </c>
       <c r="D2">
-        <v>9.866</v>
+        <v>6.7552</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -11894,7 +11850,7 @@
         <v>12</v>
       </c>
       <c r="J2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -11903,7 +11859,7 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
